--- a/engineering_basics/dsp_windows/dsp_windows.xlsx
+++ b/engineering_basics/dsp_windows/dsp_windows.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="229">
   <si>
     <t xml:space="preserve">Line Num</t>
   </si>
@@ -70,6 +70,9 @@
     <t xml:space="preserve">Comment</t>
   </si>
   <si>
+    <t xml:space="preserve">42 21 11</t>
+  </si>
+  <si>
     <t xml:space="preserve">LBL A</t>
   </si>
   <si>
@@ -79,28 +82,773 @@
     <t xml:space="preserve">Main entry point</t>
   </si>
   <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43 35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43 4 8</t>
+  </si>
+  <si>
     <t xml:space="preserve">SF 8</t>
   </si>
   <si>
     <t xml:space="preserve">Get into complex mode</t>
   </si>
   <si>
+    <t xml:space="preserve">43 8</t>
+  </si>
+  <si>
     <t xml:space="preserve">RAD</t>
   </si>
   <si>
     <t xml:space="preserve">Clear matrices</t>
   </si>
   <si>
+    <t xml:space="preserve">32 .0</t>
+  </si>
+  <si>
     <t xml:space="preserve">GSB .0</t>
   </si>
   <si>
     <t xml:space="preserve">Kick off calculations</t>
   </si>
   <si>
+    <t xml:space="preserve">42 16 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATRIX 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42 23 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIM E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42 16 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATRIX 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 .3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL .3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">∑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">w(n)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">45 10 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL/ 3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">∑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">w(n)/N</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">44 15 u</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uSTO E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Store COHERENT GAIN E[1]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 .4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL .4</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">∑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">w</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(n)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">45 10 .3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL/ .3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">∑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">w</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(n)/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">∑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">w(n)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">∑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">w</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(n)/(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">∑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">w(n))</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">45 20 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL* 3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">N*∑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">w</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(n)/(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">∑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">w(n))</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Store EQNBW E[2]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/x</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">1/(N*∑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">w</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(n)/(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">∑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">w(n))</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Store PG E[3]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 .5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL .5</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">Re[ ∑w(n)e</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">jw </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">]</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">45 .6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL .6</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">Im[ ∑w(n)e</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">jw </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">]</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">42 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">[ ∑w(n)e</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">jw </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">]</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">43 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABS</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">|∑w(n)e</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">jw</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> ∑w(n)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">|∑w(n)e</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">jw</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">| / ∑w(n)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Store SCALLOP E[4]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x^2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">(|∑w(n)e</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">jw</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">| / ∑w(n))</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">*</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">∑w(n)e</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">jw</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> / ∑w(n)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">44 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO E</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">[∑w(n)e</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">jw</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> / ∑w(n)]*[∑w(n)/∑w</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">(n)]</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Store WORSTCASE E[5]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSB D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43 32</t>
+  </si>
+  <si>
     <t xml:space="preserve">RTN</t>
   </si>
   <si>
-    <t xml:space="preserve">DONE!</t>
+    <t xml:space="preserve">42 21 .0</t>
   </si>
   <si>
     <t xml:space="preserve">LBL .0</t>
@@ -109,28 +857,58 @@
     <t xml:space="preserve">Parameter calculation program</t>
   </si>
   <si>
+    <t xml:space="preserve">44 .1</t>
+  </si>
+  <si>
     <t xml:space="preserve">STO .1</t>
   </si>
   <si>
     <t xml:space="preserve">Store N-1 in .6 for ISG instruction</t>
   </si>
   <si>
+    <t xml:space="preserve">44 .3</t>
+  </si>
+  <si>
     <t xml:space="preserve">STO .3</t>
   </si>
   <si>
+    <t xml:space="preserve">44 .4</t>
+  </si>
+  <si>
     <t xml:space="preserve">STO .4</t>
   </si>
   <si>
-    <t xml:space="preserve">RCL 0</t>
+    <t xml:space="preserve">44 .5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO .5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 .6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO .6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL 2</t>
   </si>
   <si>
     <t xml:space="preserve">window selected</t>
   </si>
   <si>
+    <t xml:space="preserve">44 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO I</t>
+  </si>
+  <si>
     <t xml:space="preserve">Point to weighting function</t>
   </si>
   <si>
-    <t xml:space="preserve">STO I</t>
+    <t xml:space="preserve">42 21 .1</t>
   </si>
   <si>
     <t xml:space="preserve">LBL .1</t>
@@ -139,19 +917,28 @@
     <t xml:space="preserve">Top of calculation loop</t>
   </si>
   <si>
+    <t xml:space="preserve">32 25</t>
+  </si>
+  <si>
     <t xml:space="preserve">GSB I</t>
   </si>
   <si>
     <t xml:space="preserve">w(n)</t>
   </si>
   <si>
+    <t xml:space="preserve">44 40 .3</t>
+  </si>
+  <si>
     <t xml:space="preserve">STO+ .3</t>
   </si>
   <si>
-    <t xml:space="preserve">ENTER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*</t>
+    <t xml:space="preserve">∑w(n)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 .7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO .7</t>
   </si>
   <si>
     <r>
@@ -184,142 +971,234 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">44 40 .4</t>
+  </si>
+  <si>
     <t xml:space="preserve">STO+ .4</t>
   </si>
   <si>
+    <t xml:space="preserve">45 .1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL .1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43 26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pi*n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pi*n/N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-pi*n/N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-j*pi*n/N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e^x</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">e</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-j*pi*n/N</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">45 .7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL .7</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">w(n)e</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-j*pi*n/N</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">44 40 .5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO+ .5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42 30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re&lt;&gt;Im</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 40 .6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO+ .6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 40 .1</t>
+  </si>
+  <si>
     <t xml:space="preserve">RCL+ .1</t>
   </si>
   <si>
     <t xml:space="preserve">n+1</t>
   </si>
   <si>
-    <t xml:space="preserve">RCL 1</t>
+    <t xml:space="preserve">45 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL 3</t>
   </si>
   <si>
     <t xml:space="preserve">N</t>
   </si>
   <si>
+    <t xml:space="preserve">43 30 6</t>
+  </si>
+  <si>
     <t xml:space="preserve">x!=y</t>
   </si>
   <si>
+    <t xml:space="preserve">22 .1</t>
+  </si>
+  <si>
     <t xml:space="preserve">GTO .1</t>
   </si>
   <si>
+    <t xml:space="preserve">42 21 0</t>
+  </si>
+  <si>
     <t xml:space="preserve">LBL 0</t>
   </si>
   <si>
     <t xml:space="preserve">Rectangular</t>
   </si>
   <si>
+    <t xml:space="preserve">42 21 1</t>
+  </si>
+  <si>
     <t xml:space="preserve">LBL 1</t>
   </si>
   <si>
     <t xml:space="preserve">Triangular</t>
   </si>
   <si>
-    <t xml:space="preserve">RCL .1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n</t>
-  </si>
-  <si>
     <t xml:space="preserve">Load n</t>
   </si>
   <si>
-    <t xml:space="preserve">/</t>
-  </si>
-  <si>
     <t xml:space="preserve">N/2</t>
   </si>
   <si>
     <t xml:space="preserve">n-N/2</t>
   </si>
   <si>
-    <t xml:space="preserve">RCL/ 1</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">n-N/2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)/N</t>
-    </r>
+    <t xml:space="preserve">(n-N/2)/N</t>
   </si>
   <si>
     <t xml:space="preserve">(n/2)/N</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">n-N/2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)/(2*N)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">ABS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">|(n)/N|</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">|(n)/N|</t>
-    </r>
+    <t xml:space="preserve">2*(n-N/2)/N</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">2*(n-N/2)/N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1-|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">2*(n-N/2)/N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">42 21 2</t>
   </si>
   <si>
     <t xml:space="preserve">LBL 2</t>
@@ -361,19 +1240,16 @@
     <t xml:space="preserve">PI</t>
   </si>
   <si>
-    <t xml:space="preserve">pi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pi*n/N</t>
-  </si>
-  <si>
     <t xml:space="preserve">COS</t>
   </si>
   <si>
     <t xml:space="preserve">cos(pi*n/N)</t>
   </si>
   <si>
-    <t xml:space="preserve">RCL 2</t>
+    <t xml:space="preserve">45 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL 4</t>
   </si>
   <si>
     <t xml:space="preserve">alpha</t>
@@ -412,13 +1288,19 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">42 21 3</t>
+  </si>
+  <si>
     <t xml:space="preserve">LBL 3</t>
   </si>
   <si>
     <t xml:space="preserve">Hamming</t>
   </si>
   <si>
-    <t xml:space="preserve">RCL- 2</t>
+    <t xml:space="preserve">45 30 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL- 4</t>
   </si>
   <si>
     <t xml:space="preserve">1-alpha</t>
@@ -430,91 +1312,46 @@
     <t xml:space="preserve">cos</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">cos(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">2*pi*n/N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(1-alpha)(cos(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">2*pi*n/N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">cos(2*pi*n/N)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1-alpha)(cos(2*pi*n/N)</t>
   </si>
   <si>
     <t xml:space="preserve">+</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(1-a)(cos(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">2*pi*n/N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)+a</t>
-    </r>
+    <t xml:space="preserve">(1-a)(cos(2*pi*n/N)+a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42 21 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LBL D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43 13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 20 .7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL* .7</t>
   </si>
   <si>
     <t xml:space="preserve">PROGRAM A</t>
@@ -981,7 +1818,7 @@
     <numFmt numFmtId="165" formatCode="000"/>
     <numFmt numFmtId="166" formatCode="@"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="33">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1157,11 +1994,21 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FFC5000B"/>
       <name val="Courier New"/>
       <family val="3"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Courier New"/>
+      <family val="3"/>
     </font>
     <font>
       <vertAlign val="superscript"/>
@@ -1171,6 +2018,7 @@
       <charset val="1"/>
     </font>
     <font>
+      <vertAlign val="superscript"/>
       <sz val="10"/>
       <name val="Courier New"/>
       <family val="3"/>
@@ -1196,7 +2044,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1260,7 +2108,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF339966"/>
-        <bgColor rgb="FF008080"/>
+        <bgColor rgb="FF5C8526"/>
       </patternFill>
     </fill>
     <fill>
@@ -1303,6 +2151,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7DA647"/>
+        <bgColor rgb="FF969696"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5C8526"/>
+        <bgColor rgb="FF7DA647"/>
       </patternFill>
     </fill>
   </fills>
@@ -1631,7 +2491,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="35">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1664,28 +2524,76 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="18" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="14" xfId="61" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="19" borderId="14" xfId="61" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="19" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="18" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="18" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="22" fillId="18" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="27" fillId="18" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="14" xfId="61" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="19" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="22" fillId="20" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="20" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1696,14 +2604,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1720,7 +2620,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1860,7 +2760,7 @@
       <rgbColor rgb="FFC5000B"/>
       <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF5C8526"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFC0C0C0"/>
@@ -1891,7 +2791,7 @@
       <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FF7DA647"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
@@ -2021,7 +2921,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H1048576"/>
+  <dimension ref="A1:H335"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="14.65" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.76"/>
@@ -2060,1724 +2960,3382 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="9" t="s">
+    <row r="2" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="C2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="F2" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="12" t="s">
+      <c r="B10" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="11" t="s">
+      <c r="B12" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="n">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="12" t="s">
+      <c r="B13" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="11" t="s">
+      <c r="B14" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="n">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="12" t="s">
+      <c r="B15" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="11" t="s">
+      <c r="B16" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="n">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="12" t="s">
+      <c r="B17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="D6" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="11" t="s">
+      <c r="B18" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8" t="n">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="9" t="s">
+      <c r="B19" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="D7" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="11" t="s">
+      <c r="B20" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8" t="n">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="12" t="n">
+      <c r="B21" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="8" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="8" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G44" s="14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D45" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="11"/>
-    </row>
-    <row r="9" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="10" t="n">
+      <c r="C46" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="11"/>
-    </row>
-    <row r="11" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="12" t="s">
+      <c r="D46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="8" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="8" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="8" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="8" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="8" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D54" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E54" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F54" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G54" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C55" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C56" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H56" s="17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="C57" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="H57" s="17"/>
+    </row>
+    <row r="58" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="8" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="C58" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="8" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H60" s="18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H61" s="17"/>
+    </row>
+    <row r="62" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="8" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H62" s="19"/>
+    </row>
+    <row r="63" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H63" s="19"/>
+    </row>
+    <row r="64" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="8" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H64" s="19"/>
+    </row>
+    <row r="65" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H65" s="19"/>
+    </row>
+    <row r="66" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="C66" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H66" s="19"/>
+    </row>
+    <row r="67" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="8" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C67" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H67" s="19"/>
+    </row>
+    <row r="68" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="8" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="C68" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H68" s="19"/>
+    </row>
+    <row r="69" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="8" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C69" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H69" s="19"/>
+    </row>
+    <row r="70" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="8" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H70" s="19"/>
+    </row>
+    <row r="71" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="C71" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H71" s="19"/>
+    </row>
+    <row r="72" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="8" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H72" s="19"/>
+    </row>
+    <row r="73" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="8" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H73" s="19"/>
+    </row>
+    <row r="74" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="8" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C76" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="8" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C77" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="8" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C78" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="8" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="8" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C80" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="C81" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="D81" s="15"/>
+      <c r="E81" s="15"/>
+      <c r="F81" s="15"/>
+      <c r="G81" s="15"/>
+      <c r="H81" s="20" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="8" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="8" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C83" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D83" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E83" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F83" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G83" s="14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="8" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="C84" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="D84" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E84" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F84" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G84" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H84" s="20" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="8" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H85" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="8" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C86" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H86" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="8" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C87" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="8" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C88" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="8" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="C89" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="8" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C90" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C91" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="8" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C92" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="8" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C93" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="8" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C94" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="8" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C95" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="8" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C96" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D96" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="E96" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F96" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="G96" s="23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="8" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C97" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="D97" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E97" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F97" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G97" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H97" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="8" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C98" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="8" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C99" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="8" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C100" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C101" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="8" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="11"/>
-    </row>
-    <row r="12" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="11"/>
-    </row>
-    <row r="16" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8" t="s">
+      <c r="C102" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="8" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="C103" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="8" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="C104" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="8" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C105" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D105" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E105" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F105" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="G105" s="23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="8" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="C106" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="D106" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E106" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F106" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G106" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H106" s="20" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="8" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="C107" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="8" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C108" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="8" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="C109" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="8" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C110" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="8" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C111" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="8" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C112" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="8" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C113" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H113" s="24"/>
+    </row>
+    <row r="114" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="8" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C114" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="8" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C115" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="8" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="C116" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="8" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C117" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="8" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="C118" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="8" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C119" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D119" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E119" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F119" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="G119" s="23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="8" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="C120" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="H120" s="25"/>
+    </row>
+    <row r="121" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="8" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C121" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H121" s="25"/>
+    </row>
+    <row r="122" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="8" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" s="25"/>
+    </row>
+    <row r="123" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="8" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="C123" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="11"/>
-    </row>
-    <row r="17" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="11"/>
-    </row>
-    <row r="18" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="11"/>
-    </row>
-    <row r="19" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E19" s="13"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="11"/>
-    </row>
-    <row r="20" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="11"/>
-    </row>
-    <row r="21" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="11"/>
-    </row>
-    <row r="22" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E22" s="10"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="11"/>
-    </row>
-    <row r="23" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="11"/>
-    </row>
-    <row r="24" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="11"/>
-    </row>
-    <row r="25" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="11"/>
-    </row>
-    <row r="26" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="11"/>
-    </row>
-    <row r="27" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="11"/>
-    </row>
-    <row r="28" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="11"/>
-    </row>
-    <row r="29" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="9" t="s">
+      <c r="H123" s="25"/>
+    </row>
+    <row r="124" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="8" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="C124" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="H124" s="25"/>
+    </row>
+    <row r="125" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="8" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C125" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H125" s="25"/>
+    </row>
+    <row r="126" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="8" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="C126" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="H126" s="25"/>
+    </row>
+    <row r="127" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="8" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="C127" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="H127" s="25"/>
+    </row>
+    <row r="128" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="8" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="C128" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="H128" s="25"/>
+    </row>
+    <row r="129" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="8" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="C129" s="16" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="8" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="11" t="s">
+      <c r="C130" s="16" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="11"/>
-    </row>
-    <row r="31" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="11"/>
-    </row>
-    <row r="32" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="8"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="E34" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="F35" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="10"/>
-      <c r="H35" s="11"/>
-    </row>
-    <row r="36" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8" t="n">
+    <row r="131" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="8" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="C131" s="16" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="8" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="C132" s="16" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="8" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="C133" s="16" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="8" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D36" s="10" t="n">
+      <c r="C134" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E36" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="F36" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G36" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" s="11"/>
-    </row>
-    <row r="37" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="8"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="F37" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="10"/>
-      <c r="H37" s="11"/>
-    </row>
-    <row r="38" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="8"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="11"/>
-    </row>
-    <row r="39" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="8"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="8"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D40" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E40" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="F40" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="10"/>
-      <c r="H40" s="11"/>
-    </row>
-    <row r="41" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="8"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D41" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="10"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="11"/>
-    </row>
-    <row r="42" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="8"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E42" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="11"/>
-    </row>
-    <row r="43" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="8"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="11"/>
-    </row>
-    <row r="44" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="8"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D44" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="11"/>
-    </row>
-    <row r="45" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="8"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="8"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D46" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="11"/>
-    </row>
-    <row r="47" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="8"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D47" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="11"/>
-    </row>
-    <row r="48" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="8"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D48" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="F48" s="10"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="11"/>
-    </row>
-    <row r="49" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="8"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D49" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="11"/>
-    </row>
-    <row r="50" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="8"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D50" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="E50" s="10"/>
-      <c r="F50" s="10"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="11"/>
-    </row>
-    <row r="51" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="8"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D51" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="E51" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="F51" s="10"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="11"/>
-    </row>
-    <row r="52" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="8"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D52" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="E52" s="10"/>
-      <c r="F52" s="10"/>
-      <c r="G52" s="10"/>
-      <c r="H52" s="11"/>
-    </row>
-    <row r="53" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="8"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D53" s="10"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="11"/>
-    </row>
-    <row r="54" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="14"/>
-      <c r="B54" s="15"/>
-      <c r="C54" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="H54" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="14"/>
-      <c r="B55" s="15"/>
-      <c r="C55" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="14"/>
-      <c r="B56" s="15"/>
-      <c r="C56" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="14"/>
-      <c r="B57" s="15"/>
-      <c r="C57" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="14"/>
-      <c r="B58" s="15"/>
-      <c r="C58" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="14"/>
-      <c r="B59" s="15"/>
-      <c r="C59" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="14"/>
-      <c r="B60" s="15"/>
-      <c r="C60" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="14"/>
-      <c r="B61" s="15"/>
-      <c r="C61" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H61" s="16"/>
-    </row>
-    <row r="62" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="14"/>
-      <c r="B62" s="15"/>
-      <c r="C62" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D62" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="14"/>
-      <c r="B63" s="15"/>
-      <c r="C63" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="14"/>
-      <c r="B64" s="15"/>
-      <c r="C64" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="14"/>
-      <c r="B65" s="15"/>
-      <c r="C65" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D65" s="2" t="s">
+    </row>
+    <row r="135" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="8" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C135" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="E65" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="14"/>
-      <c r="B66" s="15"/>
-      <c r="C66" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D66" s="2" t="s">
+    </row>
+    <row r="136" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="8" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C136" s="16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="8" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="C137" s="16" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="8" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="C138" s="16" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="8" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="C139" s="16" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="8" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="9" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="67" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="14"/>
-      <c r="B67" s="15"/>
-      <c r="C67" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="14"/>
-      <c r="B68" s="15"/>
-      <c r="C68" s="8"/>
-      <c r="H68" s="17"/>
-    </row>
-    <row r="69" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="14"/>
-      <c r="B69" s="15"/>
-      <c r="C69" s="8"/>
-      <c r="H69" s="17"/>
-    </row>
-    <row r="70" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="14"/>
-      <c r="B70" s="15"/>
-      <c r="C70" s="8"/>
-      <c r="H70" s="17"/>
-    </row>
-    <row r="71" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="14"/>
-      <c r="B71" s="15"/>
-      <c r="C71" s="8"/>
-      <c r="H71" s="17"/>
-    </row>
-    <row r="72" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="14"/>
-      <c r="C72" s="8"/>
-      <c r="H72" s="17"/>
-    </row>
-    <row r="73" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="14"/>
-      <c r="C73" s="8"/>
-    </row>
-    <row r="74" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="14"/>
-      <c r="C74" s="8"/>
-    </row>
-    <row r="75" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="14"/>
-      <c r="C75" s="8"/>
-    </row>
-    <row r="76" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="14"/>
-      <c r="C76" s="8"/>
-    </row>
-    <row r="77" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="14"/>
-      <c r="C77" s="8"/>
-    </row>
-    <row r="78" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="14"/>
-      <c r="C78" s="8"/>
-    </row>
-    <row r="79" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="14"/>
-      <c r="C79" s="8"/>
-    </row>
-    <row r="80" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="14"/>
-      <c r="C80" s="8"/>
-    </row>
-    <row r="81" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="14"/>
-      <c r="C81" s="8"/>
-    </row>
-    <row r="82" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="14"/>
-      <c r="C82" s="8"/>
-    </row>
-    <row r="83" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="14"/>
-      <c r="C83" s="8"/>
-    </row>
-    <row r="84" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="14"/>
-      <c r="C84" s="8"/>
-    </row>
-    <row r="85" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="14"/>
-      <c r="C85" s="8"/>
-    </row>
-    <row r="86" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="14"/>
-      <c r="C86" s="8"/>
-    </row>
-    <row r="87" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="14"/>
-      <c r="C87" s="8"/>
-    </row>
-    <row r="88" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="14"/>
-      <c r="C88" s="8"/>
-    </row>
-    <row r="89" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="14"/>
-      <c r="C89" s="8"/>
-    </row>
-    <row r="90" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="14"/>
-      <c r="C90" s="8"/>
-    </row>
-    <row r="91" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="14"/>
-      <c r="C91" s="8"/>
-    </row>
-    <row r="92" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="14"/>
-      <c r="C92" s="8"/>
-    </row>
-    <row r="93" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="14"/>
-      <c r="C93" s="8"/>
-    </row>
-    <row r="94" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="14"/>
-      <c r="B94" s="15"/>
-      <c r="C94" s="8"/>
-    </row>
-    <row r="95" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="14"/>
-      <c r="C95" s="8"/>
-    </row>
-    <row r="96" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C96" s="8"/>
-    </row>
-    <row r="97" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C97" s="8"/>
-    </row>
-    <row r="98" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C98" s="8"/>
-    </row>
-    <row r="99" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C99" s="8"/>
-    </row>
-    <row r="100" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C100" s="8"/>
-    </row>
-    <row r="101" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C101" s="8"/>
-    </row>
-    <row r="102" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C102" s="8"/>
-    </row>
-    <row r="103" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C103" s="8"/>
-    </row>
-    <row r="104" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C104" s="8"/>
-    </row>
-    <row r="105" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C105" s="8"/>
-    </row>
-    <row r="106" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C106" s="8"/>
-    </row>
-    <row r="107" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C107" s="8"/>
-    </row>
-    <row r="108" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C108" s="8"/>
-    </row>
-    <row r="109" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C109" s="8"/>
-    </row>
-    <row r="110" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C110" s="8"/>
-    </row>
-    <row r="111" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C111" s="8"/>
-    </row>
-    <row r="112" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C112" s="8"/>
-    </row>
-    <row r="113" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C113" s="8"/>
-    </row>
-    <row r="114" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C114" s="8"/>
-    </row>
-    <row r="115" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C115" s="8"/>
-    </row>
-    <row r="116" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C116" s="8"/>
-    </row>
-    <row r="117" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C117" s="8"/>
-    </row>
-    <row r="118" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C118" s="8"/>
-    </row>
-    <row r="119" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C119" s="8"/>
-    </row>
-    <row r="120" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C120" s="8"/>
-    </row>
-    <row r="121" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C121" s="8"/>
-    </row>
-    <row r="122" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C122" s="8"/>
-    </row>
-    <row r="123" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C123" s="8"/>
-    </row>
-    <row r="124" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C124" s="8"/>
-    </row>
-    <row r="125" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C125" s="8"/>
-    </row>
-    <row r="126" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C126" s="8"/>
-    </row>
-    <row r="127" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C127" s="8"/>
-    </row>
-    <row r="128" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C128" s="8"/>
-    </row>
-    <row r="129" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C129" s="8"/>
-    </row>
-    <row r="130" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C130" s="8"/>
-    </row>
-    <row r="131" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C131" s="8"/>
-    </row>
-    <row r="132" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C132" s="8"/>
-    </row>
-    <row r="133" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C133" s="8"/>
-    </row>
-    <row r="134" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C134" s="8"/>
-    </row>
-    <row r="135" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C135" s="8"/>
-    </row>
-    <row r="136" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C136" s="8"/>
-    </row>
-    <row r="137" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C137" s="8"/>
-    </row>
-    <row r="138" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C138" s="8"/>
-    </row>
-    <row r="139" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C139" s="8"/>
-    </row>
-    <row r="140" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C140" s="8"/>
-    </row>
-    <row r="141" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C141" s="8"/>
-    </row>
-    <row r="142" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C142" s="8"/>
-    </row>
-    <row r="143" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C143" s="8"/>
-    </row>
-    <row r="144" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C144" s="8"/>
-    </row>
-    <row r="145" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C145" s="8"/>
-    </row>
-    <row r="146" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C146" s="8"/>
-    </row>
-    <row r="147" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C147" s="8"/>
-    </row>
-    <row r="148" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C148" s="8"/>
-    </row>
-    <row r="149" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C149" s="8"/>
-    </row>
-    <row r="150" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C150" s="8"/>
-    </row>
-    <row r="151" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C151" s="8"/>
-    </row>
-    <row r="152" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C152" s="8"/>
+      <c r="C140" s="16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="8" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C141" s="16" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="26"/>
+      <c r="C142" s="16"/>
+    </row>
+    <row r="143" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="26"/>
+      <c r="C143" s="16"/>
+    </row>
+    <row r="144" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="26"/>
+      <c r="C144" s="16"/>
+    </row>
+    <row r="145" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="26"/>
+      <c r="C145" s="16"/>
+    </row>
+    <row r="146" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="26"/>
+      <c r="C146" s="16"/>
+    </row>
+    <row r="147" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="26"/>
+      <c r="C147" s="16"/>
+    </row>
+    <row r="148" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="26"/>
+      <c r="C148" s="16"/>
+    </row>
+    <row r="149" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="26"/>
+      <c r="C149" s="16"/>
+    </row>
+    <row r="150" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="26"/>
+      <c r="C150" s="16"/>
+    </row>
+    <row r="151" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="26"/>
+      <c r="B151" s="27"/>
+      <c r="C151" s="16"/>
+    </row>
+    <row r="152" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="26"/>
+      <c r="C152" s="16"/>
     </row>
     <row r="153" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C153" s="8"/>
+      <c r="C153" s="16"/>
     </row>
     <row r="154" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C154" s="8"/>
+      <c r="C154" s="16"/>
     </row>
     <row r="155" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C155" s="8"/>
+      <c r="C155" s="16"/>
     </row>
     <row r="156" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C156" s="8"/>
+      <c r="C156" s="16"/>
     </row>
     <row r="157" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C157" s="8"/>
+      <c r="C157" s="16"/>
     </row>
     <row r="158" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C158" s="8"/>
+      <c r="C158" s="16"/>
     </row>
     <row r="159" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C159" s="8"/>
+      <c r="C159" s="16"/>
     </row>
     <row r="160" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C160" s="8"/>
+      <c r="C160" s="16"/>
     </row>
     <row r="161" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C161" s="8"/>
+      <c r="C161" s="16"/>
     </row>
     <row r="162" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C162" s="8"/>
+      <c r="C162" s="16"/>
     </row>
     <row r="163" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C163" s="8"/>
+      <c r="C163" s="16"/>
     </row>
     <row r="164" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C164" s="8"/>
+      <c r="C164" s="16"/>
     </row>
     <row r="165" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C165" s="8"/>
+      <c r="C165" s="16"/>
     </row>
     <row r="166" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C166" s="8"/>
+      <c r="C166" s="16"/>
     </row>
     <row r="167" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C167" s="8"/>
+      <c r="C167" s="16"/>
     </row>
     <row r="168" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C168" s="8"/>
+      <c r="C168" s="16"/>
     </row>
     <row r="169" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C169" s="8"/>
+      <c r="C169" s="16"/>
     </row>
     <row r="170" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C170" s="8"/>
+      <c r="C170" s="16"/>
     </row>
     <row r="171" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C171" s="8"/>
+      <c r="C171" s="16"/>
     </row>
     <row r="172" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C172" s="8"/>
+      <c r="C172" s="16"/>
     </row>
     <row r="173" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C173" s="8"/>
+      <c r="C173" s="16"/>
     </row>
     <row r="174" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C174" s="8"/>
+      <c r="C174" s="16"/>
     </row>
     <row r="175" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C175" s="8"/>
+      <c r="C175" s="16"/>
     </row>
     <row r="176" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C176" s="8"/>
+      <c r="C176" s="16"/>
     </row>
     <row r="177" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C177" s="8"/>
+      <c r="C177" s="16"/>
     </row>
     <row r="178" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C178" s="8"/>
+      <c r="C178" s="16"/>
     </row>
     <row r="179" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C179" s="8"/>
+      <c r="C179" s="16"/>
     </row>
     <row r="180" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C180" s="8"/>
+      <c r="C180" s="16"/>
     </row>
     <row r="181" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C181" s="8"/>
+      <c r="C181" s="16"/>
     </row>
     <row r="182" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C182" s="8"/>
+      <c r="C182" s="16"/>
     </row>
     <row r="183" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C183" s="8"/>
+      <c r="C183" s="16"/>
     </row>
     <row r="184" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C184" s="8"/>
+      <c r="C184" s="16"/>
     </row>
     <row r="185" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C185" s="8"/>
+      <c r="C185" s="16"/>
     </row>
     <row r="186" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C186" s="8"/>
+      <c r="C186" s="16"/>
     </row>
     <row r="187" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C187" s="8"/>
+      <c r="C187" s="16"/>
     </row>
     <row r="188" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C188" s="8"/>
+      <c r="C188" s="16"/>
     </row>
     <row r="189" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C189" s="8"/>
+      <c r="C189" s="16"/>
     </row>
     <row r="190" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C190" s="8"/>
+      <c r="C190" s="16"/>
     </row>
     <row r="191" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C191" s="8"/>
+      <c r="C191" s="16"/>
     </row>
     <row r="192" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C192" s="8"/>
+      <c r="C192" s="16"/>
     </row>
     <row r="193" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C193" s="8"/>
+      <c r="C193" s="16"/>
     </row>
     <row r="194" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C194" s="8"/>
+      <c r="C194" s="16"/>
     </row>
     <row r="195" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C195" s="8"/>
+      <c r="C195" s="16"/>
     </row>
     <row r="196" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C196" s="8"/>
+      <c r="C196" s="16"/>
     </row>
     <row r="197" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C197" s="8"/>
+      <c r="C197" s="16"/>
     </row>
     <row r="198" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C198" s="8"/>
+      <c r="C198" s="16"/>
     </row>
     <row r="199" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C199" s="8"/>
+      <c r="C199" s="16"/>
     </row>
     <row r="200" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C200" s="8"/>
+      <c r="C200" s="16"/>
     </row>
     <row r="201" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C201" s="8"/>
+      <c r="C201" s="16"/>
     </row>
     <row r="202" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C202" s="8"/>
+      <c r="C202" s="16"/>
     </row>
     <row r="203" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C203" s="8"/>
+      <c r="C203" s="16"/>
     </row>
     <row r="204" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C204" s="8"/>
+      <c r="C204" s="16"/>
     </row>
     <row r="205" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C205" s="8"/>
+      <c r="C205" s="16"/>
     </row>
     <row r="206" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C206" s="8"/>
+      <c r="C206" s="16"/>
     </row>
     <row r="207" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C207" s="8"/>
+      <c r="C207" s="16"/>
     </row>
     <row r="208" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C208" s="8"/>
+      <c r="C208" s="16"/>
     </row>
     <row r="209" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C209" s="8"/>
+      <c r="C209" s="16"/>
     </row>
     <row r="210" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C210" s="8"/>
+      <c r="C210" s="16"/>
     </row>
     <row r="211" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C211" s="8"/>
+      <c r="C211" s="16"/>
     </row>
     <row r="212" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C212" s="8"/>
+      <c r="C212" s="16"/>
     </row>
     <row r="213" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C213" s="8"/>
+      <c r="C213" s="16"/>
     </row>
     <row r="214" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C214" s="8"/>
+      <c r="C214" s="16"/>
     </row>
     <row r="215" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C215" s="8"/>
+      <c r="C215" s="16"/>
     </row>
     <row r="216" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C216" s="8"/>
+      <c r="C216" s="16"/>
     </row>
     <row r="217" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C217" s="8"/>
+      <c r="C217" s="16"/>
     </row>
     <row r="218" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C218" s="8"/>
+      <c r="C218" s="16"/>
     </row>
     <row r="219" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C219" s="8"/>
+      <c r="C219" s="16"/>
     </row>
     <row r="220" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C220" s="8"/>
+      <c r="C220" s="16"/>
     </row>
     <row r="221" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C221" s="8"/>
+      <c r="C221" s="16"/>
     </row>
     <row r="222" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C222" s="8"/>
+      <c r="C222" s="16"/>
     </row>
     <row r="223" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C223" s="8"/>
+      <c r="C223" s="16"/>
     </row>
     <row r="224" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C224" s="8"/>
+      <c r="C224" s="16"/>
     </row>
     <row r="225" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C225" s="8"/>
+      <c r="C225" s="16"/>
     </row>
     <row r="226" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C226" s="8"/>
+      <c r="C226" s="16"/>
     </row>
     <row r="227" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C227" s="8"/>
+      <c r="C227" s="16"/>
     </row>
     <row r="228" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C228" s="8"/>
+      <c r="C228" s="16"/>
     </row>
     <row r="229" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C229" s="8"/>
+      <c r="C229" s="16"/>
     </row>
     <row r="230" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C230" s="8"/>
+      <c r="C230" s="16"/>
     </row>
     <row r="231" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C231" s="8"/>
+      <c r="C231" s="16"/>
     </row>
     <row r="232" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C232" s="8"/>
+      <c r="C232" s="16"/>
     </row>
     <row r="233" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C233" s="8"/>
+      <c r="C233" s="16"/>
     </row>
     <row r="234" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C234" s="8"/>
+      <c r="C234" s="16"/>
     </row>
     <row r="235" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C235" s="8"/>
+      <c r="C235" s="16"/>
     </row>
     <row r="236" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C236" s="8"/>
+      <c r="C236" s="16"/>
     </row>
     <row r="237" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C237" s="8"/>
+      <c r="C237" s="16"/>
     </row>
     <row r="238" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C238" s="8"/>
+      <c r="C238" s="16"/>
     </row>
     <row r="239" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C239" s="8"/>
+      <c r="C239" s="16"/>
     </row>
     <row r="240" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C240" s="8"/>
+      <c r="C240" s="16"/>
     </row>
     <row r="241" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C241" s="8"/>
+      <c r="C241" s="16"/>
     </row>
     <row r="242" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C242" s="8"/>
+      <c r="C242" s="16"/>
     </row>
     <row r="243" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C243" s="8"/>
+      <c r="C243" s="16"/>
     </row>
     <row r="244" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C244" s="8"/>
+      <c r="C244" s="16"/>
     </row>
     <row r="245" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C245" s="8"/>
+      <c r="C245" s="16"/>
     </row>
     <row r="246" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C246" s="8"/>
+      <c r="C246" s="16"/>
     </row>
     <row r="247" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C247" s="8"/>
+      <c r="C247" s="16"/>
     </row>
     <row r="248" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C248" s="8"/>
+      <c r="C248" s="16"/>
     </row>
     <row r="249" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C249" s="8"/>
+      <c r="C249" s="16"/>
     </row>
     <row r="250" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C250" s="8"/>
+      <c r="C250" s="16"/>
     </row>
     <row r="251" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C251" s="8"/>
+      <c r="C251" s="16"/>
     </row>
     <row r="252" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C252" s="8"/>
+      <c r="C252" s="16"/>
     </row>
     <row r="253" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C253" s="8"/>
+      <c r="C253" s="16"/>
     </row>
     <row r="254" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C254" s="8"/>
+      <c r="C254" s="16"/>
     </row>
     <row r="255" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C255" s="8"/>
+      <c r="C255" s="16"/>
     </row>
     <row r="256" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C256" s="8"/>
+      <c r="C256" s="16"/>
     </row>
     <row r="257" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C257" s="8"/>
+      <c r="C257" s="16"/>
     </row>
     <row r="258" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C258" s="8"/>
+      <c r="C258" s="16"/>
     </row>
     <row r="259" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C259" s="8"/>
+      <c r="C259" s="16"/>
     </row>
     <row r="260" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C260" s="8"/>
+      <c r="C260" s="16"/>
     </row>
     <row r="261" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C261" s="8"/>
+      <c r="C261" s="16"/>
     </row>
     <row r="262" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C262" s="8"/>
+      <c r="C262" s="16"/>
     </row>
     <row r="263" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C263" s="8"/>
+      <c r="C263" s="16"/>
     </row>
     <row r="264" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C264" s="8"/>
+      <c r="C264" s="16"/>
     </row>
     <row r="265" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C265" s="8"/>
+      <c r="C265" s="16"/>
     </row>
     <row r="266" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C266" s="8"/>
+      <c r="C266" s="16"/>
     </row>
     <row r="267" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C267" s="8"/>
+      <c r="C267" s="16"/>
     </row>
     <row r="268" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C268" s="8"/>
+      <c r="C268" s="16"/>
     </row>
     <row r="269" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C269" s="8"/>
+      <c r="C269" s="16"/>
     </row>
     <row r="270" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C270" s="8"/>
+      <c r="C270" s="16"/>
     </row>
     <row r="271" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C271" s="8"/>
+      <c r="C271" s="16"/>
     </row>
     <row r="272" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C272" s="8"/>
+      <c r="C272" s="16"/>
     </row>
     <row r="273" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C273" s="8"/>
+      <c r="C273" s="16"/>
     </row>
     <row r="274" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C274" s="8"/>
+      <c r="C274" s="16"/>
     </row>
     <row r="275" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C275" s="8"/>
+      <c r="C275" s="16"/>
     </row>
     <row r="276" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C276" s="8"/>
+      <c r="C276" s="16"/>
     </row>
     <row r="277" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C277" s="8"/>
+      <c r="C277" s="16"/>
     </row>
     <row r="278" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C278" s="8"/>
-    </row>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="C278" s="16"/>
+    </row>
+    <row r="279" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C279" s="16"/>
+    </row>
+    <row r="280" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C280" s="16"/>
+    </row>
+    <row r="281" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C281" s="16"/>
+    </row>
+    <row r="282" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C282" s="16"/>
+    </row>
+    <row r="283" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C283" s="16"/>
+    </row>
+    <row r="284" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C284" s="16"/>
+    </row>
+    <row r="285" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C285" s="16"/>
+    </row>
+    <row r="286" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C286" s="16"/>
+    </row>
+    <row r="287" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C287" s="16"/>
+    </row>
+    <row r="288" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C288" s="16"/>
+    </row>
+    <row r="289" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C289" s="16"/>
+    </row>
+    <row r="290" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C290" s="16"/>
+    </row>
+    <row r="291" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C291" s="16"/>
+    </row>
+    <row r="292" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C292" s="16"/>
+    </row>
+    <row r="293" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C293" s="16"/>
+    </row>
+    <row r="294" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C294" s="16"/>
+    </row>
+    <row r="295" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C295" s="16"/>
+    </row>
+    <row r="296" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C296" s="16"/>
+    </row>
+    <row r="297" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C297" s="16"/>
+    </row>
+    <row r="298" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C298" s="16"/>
+    </row>
+    <row r="299" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C299" s="16"/>
+    </row>
+    <row r="300" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C300" s="16"/>
+    </row>
+    <row r="301" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C301" s="16"/>
+    </row>
+    <row r="302" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C302" s="16"/>
+    </row>
+    <row r="303" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C303" s="16"/>
+    </row>
+    <row r="304" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C304" s="16"/>
+    </row>
+    <row r="305" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C305" s="16"/>
+    </row>
+    <row r="306" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C306" s="16"/>
+    </row>
+    <row r="307" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C307" s="16"/>
+    </row>
+    <row r="308" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C308" s="16"/>
+    </row>
+    <row r="309" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C309" s="16"/>
+    </row>
+    <row r="310" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C310" s="16"/>
+    </row>
+    <row r="311" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C311" s="16"/>
+    </row>
+    <row r="312" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C312" s="16"/>
+    </row>
+    <row r="313" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C313" s="16"/>
+    </row>
+    <row r="314" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C314" s="16"/>
+    </row>
+    <row r="315" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C315" s="16"/>
+    </row>
+    <row r="316" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C316" s="16"/>
+    </row>
+    <row r="317" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C317" s="16"/>
+    </row>
+    <row r="318" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C318" s="16"/>
+    </row>
+    <row r="319" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C319" s="16"/>
+    </row>
+    <row r="320" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C320" s="16"/>
+    </row>
+    <row r="321" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C321" s="16"/>
+    </row>
+    <row r="322" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C322" s="16"/>
+    </row>
+    <row r="323" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C323" s="16"/>
+    </row>
+    <row r="324" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C324" s="16"/>
+    </row>
+    <row r="325" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C325" s="16"/>
+    </row>
+    <row r="326" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C326" s="16"/>
+    </row>
+    <row r="327" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C327" s="16"/>
+    </row>
+    <row r="328" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C328" s="16"/>
+    </row>
+    <row r="329" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C329" s="16"/>
+    </row>
+    <row r="330" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C330" s="16"/>
+    </row>
+    <row r="331" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C331" s="16"/>
+    </row>
+    <row r="332" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C332" s="16"/>
+    </row>
+    <row r="333" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C333" s="16"/>
+    </row>
+    <row r="334" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C334" s="16"/>
+    </row>
+    <row r="335" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C335" s="16"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C1:C2 C14:C17 A2:B53 C7 C28:C741">
+  <conditionalFormatting sqref="C1:C12 C54:C58 C45 C67 C80:C798">
     <cfRule type="containsText" priority="2" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO C" dxfId="0">
-      <formula>NOT(ISERROR(SEARCH("uSTO C",A1)))</formula>
+      <formula>NOT(ISERROR(SEARCH("uSTO C",C1)))</formula>
     </cfRule>
     <cfRule type="containsText" priority="3" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO B" dxfId="1">
-      <formula>NOT(ISERROR(SEARCH("uSTO B",A1)))</formula>
+      <formula>NOT(ISERROR(SEARCH("uSTO B",C1)))</formula>
     </cfRule>
     <cfRule type="containsText" priority="4" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO B" dxfId="2">
-      <formula>NOT(ISERROR(SEARCH("uSTO B",A1)))</formula>
+      <formula>NOT(ISERROR(SEARCH("uSTO B",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C2 C14:C17 A2:B53 C7 C28:C750">
+  <conditionalFormatting sqref="C1:C12 C54:C58 C45 C67 C80:C807">
     <cfRule type="containsText" priority="5" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO A" dxfId="0">
-      <formula>NOT(ISERROR(SEARCH("uSTO A",A1)))</formula>
+      <formula>NOT(ISERROR(SEARCH("uSTO A",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A35:B53 C35:C278 A2:C34">
+  <conditionalFormatting sqref="C2:C26 C27:C335">
     <cfRule type="containsText" priority="6" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO C" dxfId="0">
-      <formula>NOT(ISERROR(SEARCH("uSTO C",A2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("uSTO C",C2)))</formula>
     </cfRule>
     <cfRule type="containsText" priority="7" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO B" dxfId="1">
-      <formula>NOT(ISERROR(SEARCH("uSTO B",A2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("uSTO B",C2)))</formula>
     </cfRule>
     <cfRule type="containsText" priority="8" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO B" dxfId="2">
-      <formula>NOT(ISERROR(SEARCH("uSTO B",A2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("uSTO B",C2)))</formula>
     </cfRule>
     <cfRule type="containsText" priority="9" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO A" dxfId="0">
-      <formula>NOT(ISERROR(SEARCH("uSTO A",A2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("uSTO A",C2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3798,88 +6356,88 @@
   <dimension ref="A1:L1048576"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="14.65" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="18" width="36.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="18" width="12.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="18" width="16.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="18" width="10.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="19" width="10.01"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="19" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="28" width="36.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="28" width="12.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="28" width="16.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="28" width="10.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="29" width="10.01"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="29" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
+      <c r="A1" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
     </row>
     <row r="2" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
+      <c r="A2" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
     </row>
     <row r="3" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>88</v>
+      <c r="A3" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>206</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>90</v>
+      <c r="A4" s="32" t="s">
+        <v>209</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>92</v>
+      <c r="A5" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="22" t="s">
-        <v>93</v>
+      <c r="A6" s="32" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
-        <v>94</v>
+      <c r="A8" s="28" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
-        <v>95</v>
+      <c r="A9" s="28" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
-        <v>96</v>
+      <c r="A10" s="28" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
-        <v>97</v>
+      <c r="A11" s="28" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -3910,104 +6468,104 @@
   <dimension ref="A1:L1048576"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="14.65" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="18" width="36.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="18" width="12.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="18" width="19.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="18" width="10.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="19" width="10.01"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="19" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="28" width="36.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="28" width="12.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="28" width="19.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="28" width="10.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="29" width="10.01"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="29" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
+      <c r="A1" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
     </row>
     <row r="2" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="C2" s="23"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
+      <c r="A2" s="28" t="s">
+        <v>219</v>
+      </c>
+      <c r="C2" s="33"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
     </row>
     <row r="3" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>88</v>
+      <c r="A3" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>206</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>90</v>
+      <c r="A4" s="28" t="s">
+        <v>220</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>102</v>
+      <c r="A5" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
-        <v>103</v>
+      <c r="A6" s="28" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
-        <v>94</v>
+      <c r="A8" s="28" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
-        <v>95</v>
+      <c r="A9" s="28" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
-        <v>104</v>
+      <c r="A10" s="28" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
-        <v>105</v>
+      <c r="A11" s="28" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="24" t="s">
-        <v>106</v>
+      <c r="B12" s="34" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="23" t="s">
-        <v>107</v>
+      <c r="B13" s="33" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="23" t="s">
-        <v>108</v>
+      <c r="B14" s="33" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/engineering_basics/dsp_windows/dsp_windows.xlsx
+++ b/engineering_basics/dsp_windows/dsp_windows.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="221">
   <si>
     <t xml:space="preserve">Line Num</t>
   </si>
@@ -82,36 +82,6 @@
     <t xml:space="preserve">Main entry point</t>
   </si>
   <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STO 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STO 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STO 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43 35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clx</t>
-  </si>
-  <si>
     <t xml:space="preserve">43 4 8</t>
   </si>
   <si>
@@ -166,23 +136,7 @@
     <t xml:space="preserve">RCL .3</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">∑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">w(n)</t>
-    </r>
+    <t xml:space="preserve">∑w(n)</t>
   </si>
   <si>
     <t xml:space="preserve">45 10 3</t>
@@ -191,23 +145,7 @@
     <t xml:space="preserve">RCL/ 3</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">∑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">w(n)/N</t>
-    </r>
+    <t xml:space="preserve">∑w(n)/N</t>
   </si>
   <si>
     <t xml:space="preserve">44 15 u</t>
@@ -230,9 +168,633 @@
         <sz val="10"/>
         <rFont val="Courier New"/>
         <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">∑</t>
-    </r>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">∑w</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(n)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">45 10 .3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL/ .3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">∑w</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(n)/∑w(n)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">∑w</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(n)/(∑w(n))</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">45 20 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL* 3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">N*∑w</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(n)/(∑w(n))</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Store EQNBW E[2]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/x</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1/(N*∑w</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(n)/(∑w(n))</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Store PG E[3]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 .5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL .5</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Re[ ∑w(n)e</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">jw </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">45 .6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL .6</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Im[ ∑w(n)e</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">jw </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">42 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[ ∑w(n)e</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">jw </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">43 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABS</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|∑w(n)e</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">jw</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> ∑w(n)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|∑w(n)e</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">jw</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">| / ∑w(n)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Store SCALLOP E[4]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x^2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(|∑w(n)e</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">jw</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">| / ∑w(n))</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">*</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">∑w(n)e</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">jw</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> / ∑w(n)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">44 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO E</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[∑w(n)e</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">jw</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> / ∑w(n)]*[∑w(n)/∑w</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(n)]</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Store WORSTCASE E[5]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSB D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43 32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42 21 .0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LBL .0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parameter calculation program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 .1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO .1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Store N-1 in .6 for ISG instruction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 .3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO .3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 .4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO .4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 .5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO .5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 .6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO .6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">window selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Point to weighting function</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42 21 .1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LBL .1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top of calculation loop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSB I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w(n)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 40 .3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO+ .3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 .7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO .7</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -263,28 +825,53 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">45 10 .3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RCL/ .3</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">∑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">w</t>
+    <t xml:space="preserve">44 40 .4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO+ .4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 .1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL .1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43 26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pi*n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pi*n/N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-pi*n/N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-j*pi*n/N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e^x</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">e</t>
     </r>
     <r>
       <rPr>
@@ -294,52 +881,24 @@
         <family val="3"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(n)/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">∑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">w(n)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">∑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">w</t>
+      <t xml:space="preserve">-j*pi*n/N</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">45 .7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL .7</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">w(n)e</t>
     </r>
     <r>
       <rPr>
@@ -349,33 +908,114 @@
         <family val="3"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(n)/(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">∑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">w(n))</t>
+      <t xml:space="preserve">-j*pi*n/N</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">44 40 .5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO+ .5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42 30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re&lt;&gt;Im</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 40 .6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO+ .6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 40 .1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL+ .1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n+1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43 30 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x!=y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 .1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GTO .1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42 21 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LBL 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rectangular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42 21 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LBL 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Triangular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N/2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n-N/2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(n-N/2)/N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(n/2)/N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2*(n-N/2)/N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">|2*(n-N/2)/N|</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-|2*(n-N/2)/N|</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42 21 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LBL 2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">cos</t>
     </r>
     <r>
       <rPr>
@@ -385,32 +1025,117 @@
         <family val="3"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">45 20 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RCL* 3</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">N*∑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">w</t>
+      <t xml:space="preserve">alpha</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(n)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">n-N/2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)/N</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pi*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">(n-N/2)/N</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">COS</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">cos(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">pi*(n-N/2)/N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">45 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alpha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">y^x</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">cos</t>
     </r>
     <r>
       <rPr>
@@ -420,807 +1145,6 @@
         <family val="3"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(n)/(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">∑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">w(n))</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Store EQNBW E[2]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/x</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">1/(N*∑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">w</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(n)/(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">∑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">w(n))</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Store PG E[3]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45 .5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RCL .5</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">Re[ ∑w(n)e</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">jw </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">]</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">45 .6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RCL .6</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">Im[ ∑w(n)e</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">jw </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">]</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">42 25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">[ ∑w(n)e</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">jw </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">]</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">43 16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABS</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">|∑w(n)e</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">jw</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve"> ∑w(n)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">|∑w(n)e</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">jw</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">| / ∑w(n)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Store SCALLOP E[4]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43 11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x^2</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">(|∑w(n)e</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">jw</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">| / ∑w(n))</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">*</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">∑w(n)e</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">jw</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> / ∑w(n)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">44 15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STO E</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">[∑w(n)e</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">jw</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> / ∑w(n)]*[∑w(n)/∑w</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">(n)]</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Store WORSTCASE E[5]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32 14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSB D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43 32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RTN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42 21 .0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LBL .0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parameter calculation program</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44 .1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STO .1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Store N-1 in .6 for ISG instruction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44 .3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STO .3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44 .4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STO .4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44 .5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STO .5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44 .6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STO .6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RCL 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">window selected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44 25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STO I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Point to weighting function</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42 21 .1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LBL .1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Top of calculation loop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32 25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSB I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w(n)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44 40 .3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STO+ .3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">∑w(n)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44 .7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STO .7</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">w</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(n)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">44 40 .4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STO+ .4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45 .1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RCL .1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43 26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pi*n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pi*n/N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-pi*n/N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-j*pi*n/N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">e^x</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">e</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-j*pi*n/N</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">45 .7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RCL .7</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">w(n)e</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-j*pi*n/N</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">44 40 .5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STO+ .5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42 30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Re&lt;&gt;Im</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44 40 .6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STO+ .6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45 40 .1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RCL+ .1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n+1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RCL 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43 30 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x!=y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 .1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GTO .1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42 21 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LBL 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rectangular</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42 21 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LBL 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Triangular</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n-N/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(n-N/2)/N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(n/2)/N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2*(n-N/2)/N</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">2*(n-N/2)/N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1-|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">2*(n-N/2)/N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">42 21 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LBL 2</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">cos</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
       <t xml:space="preserve">alpha</t>
     </r>
     <r>
@@ -1230,98 +1154,53 @@
         <family val="3"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(n)</t>
-    </r>
+      <t xml:space="preserve">(pi*n/N)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">42 21 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LBL 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamming</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 30 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-(1-alpha)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n/(N-1)</t>
   </si>
   <si>
     <t xml:space="preserve">n/N</t>
   </si>
   <si>
-    <t xml:space="preserve">PI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cos(pi*n/N)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RCL 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">alpha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">y^x</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">cos</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">alpha</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(pi*n/N)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">42 21 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LBL 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamming</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45 30 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RCL- 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1-alpha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2*pi*n/N</t>
+    <t xml:space="preserve">pi*n/(N-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2*pi*n/(N-1)</t>
   </si>
   <si>
     <t xml:space="preserve">cos</t>
   </si>
   <si>
-    <t xml:space="preserve">cos(2*pi*n/N)</t>
+    <t xml:space="preserve">cos(2*pi*n/(N-1))</t>
   </si>
   <si>
     <t xml:space="preserve">(1-alpha)(cos(2*pi*n/N)</t>
   </si>
   <si>
-    <t xml:space="preserve">+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1-a)(cos(2*pi*n/N)+a</t>
+    <t xml:space="preserve">45 40 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL+ 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-(1-a)(cos(2*pi*n/N)+a</t>
   </si>
   <si>
     <t xml:space="preserve">42 21 14</t>
@@ -1818,7 +1697,7 @@
     <numFmt numFmtId="165" formatCode="000"/>
     <numFmt numFmtId="166" formatCode="@"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="32">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2006,11 +1885,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Courier New"/>
-      <family val="3"/>
-    </font>
-    <font>
       <vertAlign val="superscript"/>
       <sz val="10"/>
       <name val="Courier New"/>
@@ -2018,7 +1892,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <vertAlign val="superscript"/>
       <sz val="10"/>
       <name val="Courier New"/>
       <family val="3"/>
@@ -2491,7 +2364,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2540,10 +2413,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="22" fillId="19" borderId="14" xfId="61" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2564,14 +2433,6 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="18" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2588,6 +2449,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2620,7 +2485,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2921,7 +2786,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H335"/>
+  <dimension ref="A1:H1048576"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="14.65" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.76"/>
@@ -2988,152 +2853,239 @@
     </row>
     <row r="3" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="10" t="n">
-        <v>2</v>
+      <c r="C3" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" s="10" t="n">
-        <v>3</v>
+        <v>14</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="10" t="n">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="10" t="s">
         <v>16</v>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B8" s="9" t="n">
-        <v>48</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>17</v>
+        <v>36</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B9" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="11" t="n">
         <v>5</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="C10" s="10" t="n">
-        <v>4</v>
+        <v>19</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>19</v>
+        <v>26</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>21</v>
+        <v>28</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>10</v>
@@ -3145,21 +3097,21 @@
         <v>10</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>10</v>
@@ -3169,23 +3121,20 @@
       </c>
       <c r="G15" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>10</v>
@@ -3199,78 +3148,93 @@
     </row>
     <row r="17" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>1</v>
+        <v>26</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="9" t="n">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>44</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>1</v>
+        <v>45</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="C19" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>1</v>
+        <v>28</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>34</v>
+        <v>29</v>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>15</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>1</v>
+        <v>48</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>10</v>
@@ -3280,23 +3244,26 @@
       </c>
       <c r="G21" s="2" t="s">
         <v>10</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>40</v>
+        <v>52</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>10</v>
@@ -3307,85 +3274,73 @@
     </row>
     <row r="23" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>43</v>
+        <v>55</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>43</v>
+        <v>58</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>52</v>
+        <v>29</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>10</v>
@@ -3393,73 +3348,79 @@
     </row>
     <row r="27" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>50</v>
+        <v>36</v>
+      </c>
+      <c r="B27" s="9" t="n">
+        <v>10</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>53</v>
+        <v>64</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>56</v>
+        <v>35</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>56</v>
+        <v>68</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B30" s="9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>59</v>
+        <v>70</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>10</v>
@@ -3470,19 +3431,16 @@
     </row>
     <row r="31" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>10</v>
+        <v>73</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>10</v>
@@ -3491,101 +3449,98 @@
         <v>10</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E32" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="E33" s="12" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="E34" s="12" t="s">
-        <v>59</v>
+        <v>78</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" s="13" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="E35" s="12" t="s">
-        <v>59</v>
+        <v>80</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D36" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="E36" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="F36" s="12" t="s">
-        <v>59</v>
+        <v>45</v>
+      </c>
+      <c r="B36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>10</v>
@@ -3593,79 +3548,91 @@
     </row>
     <row r="37" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="9" t="n">
-        <v>10</v>
+        <v>46</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>83</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E37" s="12" t="s">
-        <v>59</v>
+        <v>84</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E38" s="12" t="s">
-        <v>59</v>
+        <v>87</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E39" s="12" t="s">
-        <v>59</v>
+        <v>89</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="9" t="n">
-        <v>20</v>
+        <v>49</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>90</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="E40" s="12" t="s">
-        <v>59</v>
+        <v>91</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>10</v>
@@ -3676,61 +3643,79 @@
     </row>
     <row r="41" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>84</v>
+        <v>93</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>87</v>
+        <v>95</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>37</v>
+        <v>98</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C44" s="13" t="s">
-        <v>89</v>
+        <v>100</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>101</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="E44" s="14" t="s">
         <v>10</v>
@@ -3740,46 +3725,46 @@
       </c>
       <c r="G44" s="14" t="s">
         <v>10</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="D45" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G45" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>92</v>
+        <v>103</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="2" t="n">
-        <v>0</v>
+        <v>55</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>10</v>
@@ -3789,49 +3774,38 @@
       </c>
       <c r="G46" s="2" t="s">
         <v>10</v>
+      </c>
+      <c r="H46" s="16" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="C47" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="D47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>95</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="C47" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="H47" s="16"/>
     </row>
     <row r="48" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="C48" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="D48" s="2" t="n">
-        <v>0</v>
+        <v>57</v>
+      </c>
+      <c r="B48" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>10</v>
+        <v>105</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>10</v>
@@ -3842,16 +3816,16 @@
     </row>
     <row r="49" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" s="9" t="s">
-        <v>98</v>
+        <v>58</v>
+      </c>
+      <c r="B49" s="9" t="n">
+        <v>20</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="D49" s="2" t="n">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>10</v>
@@ -3865,16 +3839,16 @@
     </row>
     <row r="50" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="D50" s="2" t="n">
-        <v>0</v>
+        <v>112</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>10</v>
@@ -3884,721 +3858,732 @@
       </c>
       <c r="G50" s="2" t="s">
         <v>10</v>
+      </c>
+      <c r="H50" s="16" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="C51" s="11" t="s">
-        <v>103</v>
+        <v>60</v>
+      </c>
+      <c r="B51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D51" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="H51" s="16"/>
     </row>
     <row r="52" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>10</v>
+        <v>115</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H53" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B54" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C54" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="D54" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="E54" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G54" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H54" s="4" t="s">
-        <v>112</v>
+      <c r="G54" s="2" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C55" s="16" t="s">
-        <v>114</v>
+        <v>31</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>10</v>
+        <v>119</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>10</v>
+        <v>110</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="C56" s="16" t="s">
-        <v>117</v>
+        <v>65</v>
+      </c>
+      <c r="B56" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>120</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>10</v>
+        <v>121</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H56" s="17" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="C57" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="H57" s="17"/>
+        <v>57</v>
+      </c>
+      <c r="C57" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="B58" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="C58" s="16" t="s">
-        <v>33</v>
+        <v>12</v>
+      </c>
+      <c r="C58" s="11" t="s">
+        <v>123</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>10</v>
+        <v>110</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="9" t="n">
-        <v>20</v>
+        <v>68</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>125</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>10</v>
+        <v>105</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>10</v>
+        <v>110</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="9" t="s">
-        <v>122</v>
+        <v>69</v>
+      </c>
+      <c r="B60" s="9" t="n">
+        <v>20</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H60" s="18" t="s">
-        <v>49</v>
+        <v>127</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C61" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E61" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C61" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H61" s="17"/>
+      <c r="F61" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H62" s="19"/>
+        <v>110</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B63" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="D63" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C63" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="F63" s="2" t="n">
+      <c r="E63" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="F63" s="2" t="s">
+        <v>110</v>
+      </c>
       <c r="G63" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H63" s="19"/>
+        <v>110</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B64" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="C64" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F64" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="G64" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H64" s="19"/>
+        <v>110</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="8" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>41</v>
+        <v>134</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>42</v>
+        <v>135</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E65" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F65" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="G65" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H65" s="19"/>
+        <v>110</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="8" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" s="9" t="n">
-        <v>16</v>
+        <v>75</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>83</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>131</v>
+        <v>84</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E66" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F66" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="G66" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H66" s="19"/>
+        <v>110</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C67" s="16" t="s">
-        <v>68</v>
+        <v>137</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>138</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="E67" s="2" t="n">
-        <v>0</v>
+        <v>139</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H67" s="19"/>
+        <v>110</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" s="9" t="n">
-        <v>12</v>
+        <v>77</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>140</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="E68" s="2" t="n">
-        <v>0</v>
+        <v>139</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H68" s="19"/>
+        <v>110</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="B69" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C69" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E69" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C69" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E69" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="F69" s="2" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H69" s="19"/>
+        <v>110</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="C70" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C70" s="15" t="s">
+        <v>79</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="H70" s="19"/>
+        <v>139</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="C71" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="G71" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H71" s="19"/>
+        <v>144</v>
+      </c>
+      <c r="C71" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="D71" s="14"/>
+      <c r="E71" s="14"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="14"/>
+      <c r="H71" s="17" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="8" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="C72" s="11" t="s">
-        <v>142</v>
+        <v>81</v>
+      </c>
+      <c r="B72" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" s="15" t="n">
+        <v>1</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E72" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H72" s="19"/>
+        <v>10</v>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="8" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="C73" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H73" s="19"/>
+        <v>78</v>
+      </c>
+      <c r="C73" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="D73" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E73" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F73" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G73" s="13" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C74" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D74" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>121</v>
+        <v>83</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D74" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E74" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F74" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G74" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H74" s="17" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="C75" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>147</v>
+        <v>84</v>
+      </c>
+      <c r="B75" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F75" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>121</v>
+        <v>10</v>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="8" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="C76" s="11" t="s">
-        <v>94</v>
+        <v>113</v>
+      </c>
+      <c r="C76" s="15" t="s">
+        <v>114</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F76" s="2" t="n">
-        <v>0</v>
+        <v>115</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>121</v>
+        <v>10</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="8" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="C77" s="11" t="s">
-        <v>149</v>
+        <v>137</v>
+      </c>
+      <c r="C77" s="15" t="s">
+        <v>138</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>121</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="8" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="C78" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>150</v>
+        <v>87</v>
+      </c>
+      <c r="B78" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C78" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="G78" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="8" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="C79" s="11" t="s">
-        <v>154</v>
+        <v>88</v>
+      </c>
+      <c r="B79" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="C79" s="15" t="s">
+        <v>64</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>121</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="8" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C80" s="16" t="s">
         <v>89</v>
       </c>
+      <c r="B80" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C80" s="15" t="s">
+        <v>10</v>
+      </c>
       <c r="D80" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>147</v>
+        <v>152</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>121</v>
+        <v>10</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="8" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="C81" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="D81" s="15"/>
-      <c r="E81" s="15"/>
-      <c r="F81" s="15"/>
-      <c r="G81" s="15"/>
-      <c r="H81" s="20" t="s">
-        <v>157</v>
+        <v>31</v>
+      </c>
+      <c r="C81" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H81" s="4" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="8" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="B82" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C82" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F82" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="C82" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>10</v>
@@ -4606,65 +4591,62 @@
     </row>
     <row r="83" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="8" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C83" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="D83" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="E83" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F83" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G83" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="B83" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C83" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G83" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="8" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="C84" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="D84" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="E84" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F84" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G84" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H84" s="20" t="s">
-        <v>160</v>
+        <v>60</v>
+      </c>
+      <c r="C84" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="8" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B85" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C85" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D85" s="2" t="n">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="C85" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>157</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>10</v>
@@ -4674,308 +4656,229 @@
       </c>
       <c r="G85" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="H85" s="4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="8" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C86" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E86" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G86" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H86" s="4" t="s">
-        <v>161</v>
+        <v>78</v>
+      </c>
+      <c r="C86" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D86" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="E86" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F86" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G86" s="20" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="8" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="C87" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="F87" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G87" s="2" t="s">
-        <v>10</v>
+        <v>158</v>
+      </c>
+      <c r="C87" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="D87" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E87" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F87" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G87" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="8" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" s="9" t="n">
+        <v>97</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C88" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="8"/>
+      <c r="B89" s="9"/>
+      <c r="C89" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="8"/>
+      <c r="B90" s="9"/>
+      <c r="C90" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="C88" s="16" t="n">
+      <c r="D90" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D88" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G88" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="8" t="n">
-        <v>88</v>
-      </c>
-      <c r="B89" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="C89" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="F89" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="8" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="C90" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E90" s="2" t="n">
-        <v>1</v>
+      <c r="E90" s="2" t="s">
+        <v>139</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G90" s="2" t="s">
-        <v>10</v>
+        <v>115</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="8" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C91" s="16" t="s">
-        <v>42</v>
+      <c r="A91" s="8"/>
+      <c r="B91" s="9"/>
+      <c r="C91" s="15" t="s">
+        <v>64</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="E91" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G91" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H91" s="4" t="s">
-        <v>165</v>
+        <v>151</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="8" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C92" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D92" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F92" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" s="2" t="s">
-        <v>10</v>
+      <c r="A92" s="8"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="8" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="C93" s="16" t="s">
-        <v>80</v>
+        <v>98</v>
+      </c>
+      <c r="B93" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C93" s="21" t="s">
+        <v>32</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="E93" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G93" s="2" t="s">
-        <v>10</v>
+        <v>161</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="8" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C94" s="16" t="s">
-        <v>71</v>
+        <v>116</v>
+      </c>
+      <c r="C94" s="15" t="s">
+        <v>117</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E94" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G94" s="2" t="s">
-        <v>10</v>
+        <v>117</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="8" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B95" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="C95" s="16" t="s">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="C95" s="15" t="s">
+        <v>70</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>10</v>
+        <v>162</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="8" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C96" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="D96" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="E96" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F96" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="G96" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="B96" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="C96" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G96" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="8" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C97" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D97" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="E97" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F97" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G97" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H97" s="4" t="s">
-        <v>171</v>
+        <v>165</v>
+      </c>
+      <c r="C97" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="8" t="n">
-        <v>97</v>
-      </c>
-      <c r="B98" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C98" s="16" t="s">
-        <v>125</v>
+        <v>108</v>
+      </c>
+      <c r="B98" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="C98" s="15" t="s">
+        <v>168</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>126</v>
+        <v>169</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>10</v>
@@ -4989,56 +4892,65 @@
     </row>
     <row r="99" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="8" t="n">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C99" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G99" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C99" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D99" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="E99" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F99" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G99" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="8" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="B100" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="C100" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E100" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C100" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="D100" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E100" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F100" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G100" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H100" s="17" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="B101" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="C101" s="16" t="s">
-        <v>80</v>
+        <v>111</v>
+      </c>
+      <c r="B101" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C101" s="15" t="s">
+        <v>166</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>10</v>
@@ -5052,16 +4964,16 @@
     </row>
     <row r="102" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="8" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="B102" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="C102" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>175</v>
+        <v>1</v>
+      </c>
+      <c r="C102" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>10</v>
@@ -5075,36 +4987,42 @@
     </row>
     <row r="103" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="8" t="n">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="C103" s="16" t="s">
-        <v>177</v>
+        <v>173</v>
+      </c>
+      <c r="C103" s="15" t="s">
+        <v>10</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>175</v>
+        <v>10</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="8" t="n">
-        <v>103</v>
-      </c>
-      <c r="B104" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="C104" s="16" t="s">
-        <v>179</v>
+        <v>114</v>
+      </c>
+      <c r="B104" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C104" s="15" t="s">
+        <v>114</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>180</v>
+        <v>115</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>10</v>
+        <v>174</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>10</v>
@@ -5115,71 +5033,68 @@
     </row>
     <row r="105" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="8" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C105" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="D105" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E105" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F105" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="G105" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="C105" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G105" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="8" t="n">
-        <v>105</v>
-      </c>
-      <c r="B106" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="C106" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="D106" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="E106" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F106" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G106" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H106" s="20" t="s">
-        <v>183</v>
+        <v>118</v>
+      </c>
+      <c r="B106" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="C106" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="8" t="n">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="B107" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C107" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E107" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="C107" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="F107" s="2" t="s">
-        <v>10</v>
+        <v>174</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>10</v>
@@ -5187,19 +5102,19 @@
     </row>
     <row r="108" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="8" t="n">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="B108" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C108" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D108" s="2" t="n">
-        <v>1</v>
+        <v>20</v>
+      </c>
+      <c r="C108" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>177</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>10</v>
@@ -5207,25 +5122,26 @@
       <c r="G108" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="H108" s="22"/>
     </row>
     <row r="109" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="8" t="n">
-        <v>108</v>
-      </c>
-      <c r="B109" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="C109" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>186</v>
+        <v>121</v>
+      </c>
+      <c r="B109" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C109" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>178</v>
+        <v>119</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>10</v>
+        <v>174</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>10</v>
@@ -5233,22 +5149,22 @@
     </row>
     <row r="110" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="8" t="n">
-        <v>109</v>
-      </c>
-      <c r="B110" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C110" s="16" t="s">
-        <v>125</v>
+        <v>122</v>
+      </c>
+      <c r="B110" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C110" s="15" t="s">
+        <v>70</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>178</v>
+        <v>10</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>10</v>
@@ -5256,22 +5172,22 @@
     </row>
     <row r="111" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="8" t="n">
-        <v>110</v>
-      </c>
-      <c r="B111" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C111" s="16" t="s">
-        <v>42</v>
+        <v>123</v>
+      </c>
+      <c r="B111" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="C111" s="15" t="s">
+        <v>179</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>178</v>
+        <v>10</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>10</v>
@@ -5279,1036 +5195,943 @@
     </row>
     <row r="112" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="8" t="n">
-        <v>111</v>
-      </c>
-      <c r="B112" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="C112" s="16" t="s">
-        <v>128</v>
+        <v>124</v>
+      </c>
+      <c r="B112" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C112" s="15" t="s">
+        <v>70</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>128</v>
+        <v>181</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>186</v>
+        <v>10</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>178</v>
+        <v>10</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="8" t="n">
-        <v>112</v>
-      </c>
-      <c r="B113" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="C113" s="16" t="s">
-        <v>80</v>
+        <v>125</v>
+      </c>
+      <c r="B113" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="C113" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>130</v>
+        <v>184</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>186</v>
+        <v>10</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>178</v>
+        <v>10</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H113" s="24"/>
     </row>
     <row r="114" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="8" t="n">
-        <v>113</v>
-      </c>
-      <c r="B114" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C114" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D114" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="F114" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="G114" s="2" t="s">
-        <v>178</v>
+        <v>126</v>
+      </c>
+      <c r="B114" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C114" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D114" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="E114" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F114" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G114" s="20" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="8" t="n">
-        <v>114</v>
-      </c>
-      <c r="B115" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="C115" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="E115" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B115" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C115" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="F115" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="G115" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="H115" s="23"/>
     </row>
     <row r="116" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="8" t="n">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="B116" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="C116" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E116" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="F116" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="G116" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C116" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H116" s="23"/>
     </row>
     <row r="117" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="8" t="n">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="B117" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="C117" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F117" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G117" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C117" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" s="23"/>
     </row>
     <row r="118" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="8" t="n">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="B118" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="C118" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F118" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G118" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="C118" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="H118" s="23"/>
     </row>
     <row r="119" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="8" t="n">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C119" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="D119" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E119" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F119" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="G119" s="23" t="s">
-        <v>10</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="C119" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="H119" s="23"/>
     </row>
     <row r="120" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="8" t="n">
-        <v>119</v>
-      </c>
-      <c r="B120" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="C120" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="H120" s="25"/>
+        <v>132</v>
+      </c>
+      <c r="B120" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C120" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H120" s="23"/>
     </row>
     <row r="121" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="8" t="n">
-        <v>120</v>
-      </c>
-      <c r="B121" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C121" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H121" s="25"/>
+        <v>133</v>
+      </c>
+      <c r="B121" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="C121" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="H121" s="23"/>
     </row>
     <row r="122" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="8" t="n">
-        <v>121</v>
-      </c>
-      <c r="B122" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C122" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H122" s="25"/>
+        <v>134</v>
+      </c>
+      <c r="B122" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="C122" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="H122" s="23"/>
     </row>
     <row r="123" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="8" t="n">
-        <v>122</v>
-      </c>
-      <c r="B123" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="C123" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="H123" s="25"/>
+        <v>135</v>
+      </c>
+      <c r="B123" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="C123" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="H123" s="23"/>
     </row>
     <row r="124" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="8" t="n">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="B124" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="C124" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="H124" s="25"/>
+        <v>193</v>
+      </c>
+      <c r="C124" s="15" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="125" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="8" t="n">
-        <v>124</v>
-      </c>
-      <c r="B125" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C125" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="H125" s="25"/>
+        <v>137</v>
+      </c>
+      <c r="B125" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C125" s="15" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="126" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="8" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="B126" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="C126" s="16" t="s">
-        <v>196</v>
-      </c>
-      <c r="H126" s="25"/>
+        <v>189</v>
+      </c>
+      <c r="C126" s="15" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="127" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="8" t="n">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="B127" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="C127" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="H127" s="25"/>
+        <v>191</v>
+      </c>
+      <c r="C127" s="15" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="128" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="8" t="n">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="B128" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="C128" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="H128" s="25"/>
+        <v>193</v>
+      </c>
+      <c r="C128" s="15" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="129" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="8" t="n">
-        <v>128</v>
-      </c>
-      <c r="B129" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="C129" s="16" t="s">
-        <v>202</v>
+        <v>141</v>
+      </c>
+      <c r="B129" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C129" s="15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="8" t="n">
-        <v>129</v>
-      </c>
-      <c r="B130" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C130" s="16" t="s">
-        <v>45</v>
+        <v>142</v>
+      </c>
+      <c r="B130" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C130" s="15" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="8" t="n">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="B131" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="C131" s="16" t="s">
-        <v>198</v>
+        <v>34</v>
+      </c>
+      <c r="C131" s="15" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="8" t="n">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="B132" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="C132" s="16" t="s">
-        <v>200</v>
+        <v>189</v>
+      </c>
+      <c r="C132" s="15" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="8" t="n">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="B133" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="C133" s="16" t="s">
-        <v>202</v>
+        <v>191</v>
+      </c>
+      <c r="C133" s="15" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="8" t="n">
-        <v>133</v>
-      </c>
-      <c r="B134" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C134" s="16" t="n">
-        <v>2</v>
+        <v>146</v>
+      </c>
+      <c r="B134" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="C134" s="15" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="8" t="n">
-        <v>134</v>
-      </c>
-      <c r="B135" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="C135" s="16" t="s">
-        <v>80</v>
+        <v>147</v>
+      </c>
+      <c r="B135" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C135" s="15" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="8" t="n">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="B136" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C136" s="16" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="137" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="8" t="n">
-        <v>136</v>
-      </c>
-      <c r="B137" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="C137" s="16" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="138" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="8" t="n">
-        <v>137</v>
-      </c>
-      <c r="B138" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="C138" s="16" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="139" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="8" t="n">
-        <v>138</v>
-      </c>
-      <c r="B139" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="C139" s="16" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="140" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="8" t="n">
-        <v>139</v>
-      </c>
-      <c r="B140" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="C140" s="16" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="141" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="8" t="n">
-        <v>140</v>
-      </c>
-      <c r="B141" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C141" s="16" t="s">
-        <v>89</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="C136" s="15" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="24"/>
+      <c r="C137" s="15"/>
+    </row>
+    <row r="138" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="24"/>
+      <c r="C138" s="15"/>
+    </row>
+    <row r="139" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="24"/>
+      <c r="C139" s="15"/>
+    </row>
+    <row r="140" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="24"/>
+      <c r="C140" s="15"/>
+    </row>
+    <row r="141" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="24"/>
+      <c r="C141" s="15"/>
     </row>
     <row r="142" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="26"/>
-      <c r="C142" s="16"/>
+      <c r="A142" s="24"/>
+      <c r="C142" s="15"/>
     </row>
     <row r="143" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="26"/>
-      <c r="C143" s="16"/>
+      <c r="A143" s="24"/>
+      <c r="C143" s="15"/>
     </row>
     <row r="144" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="26"/>
-      <c r="C144" s="16"/>
+      <c r="A144" s="24"/>
+      <c r="C144" s="15"/>
     </row>
     <row r="145" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="26"/>
-      <c r="C145" s="16"/>
+      <c r="A145" s="24"/>
+      <c r="C145" s="15"/>
     </row>
     <row r="146" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="26"/>
-      <c r="C146" s="16"/>
+      <c r="A146" s="24"/>
+      <c r="B146" s="25"/>
+      <c r="C146" s="15"/>
     </row>
     <row r="147" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="26"/>
-      <c r="C147" s="16"/>
-    </row>
-    <row r="148" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="26"/>
-      <c r="C148" s="16"/>
-    </row>
-    <row r="149" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="26"/>
-      <c r="C149" s="16"/>
-    </row>
-    <row r="150" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="26"/>
-      <c r="C150" s="16"/>
-    </row>
-    <row r="151" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="26"/>
-      <c r="B151" s="27"/>
-      <c r="C151" s="16"/>
-    </row>
-    <row r="152" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="26"/>
-      <c r="C152" s="16"/>
+      <c r="A147" s="24"/>
+      <c r="C147" s="15"/>
+    </row>
+    <row r="148" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C148" s="15"/>
+    </row>
+    <row r="149" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C149" s="15"/>
+    </row>
+    <row r="150" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C150" s="15"/>
+    </row>
+    <row r="151" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C151" s="15"/>
+    </row>
+    <row r="152" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C152" s="15"/>
     </row>
     <row r="153" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C153" s="16"/>
+      <c r="C153" s="15"/>
     </row>
     <row r="154" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C154" s="16"/>
+      <c r="C154" s="15"/>
     </row>
     <row r="155" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C155" s="16"/>
+      <c r="C155" s="15"/>
     </row>
     <row r="156" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C156" s="16"/>
+      <c r="C156" s="15"/>
     </row>
     <row r="157" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C157" s="16"/>
+      <c r="C157" s="15"/>
     </row>
     <row r="158" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C158" s="16"/>
+      <c r="C158" s="15"/>
     </row>
     <row r="159" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C159" s="16"/>
+      <c r="C159" s="15"/>
     </row>
     <row r="160" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C160" s="16"/>
+      <c r="C160" s="15"/>
     </row>
     <row r="161" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C161" s="16"/>
+      <c r="C161" s="15"/>
     </row>
     <row r="162" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C162" s="16"/>
+      <c r="C162" s="15"/>
     </row>
     <row r="163" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C163" s="16"/>
+      <c r="C163" s="15"/>
     </row>
     <row r="164" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C164" s="16"/>
+      <c r="C164" s="15"/>
     </row>
     <row r="165" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C165" s="16"/>
+      <c r="C165" s="15"/>
     </row>
     <row r="166" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C166" s="16"/>
+      <c r="C166" s="15"/>
     </row>
     <row r="167" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C167" s="16"/>
+      <c r="C167" s="15"/>
     </row>
     <row r="168" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C168" s="16"/>
+      <c r="C168" s="15"/>
     </row>
     <row r="169" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C169" s="16"/>
+      <c r="C169" s="15"/>
     </row>
     <row r="170" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C170" s="16"/>
+      <c r="C170" s="15"/>
     </row>
     <row r="171" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C171" s="16"/>
+      <c r="C171" s="15"/>
     </row>
     <row r="172" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C172" s="16"/>
+      <c r="C172" s="15"/>
     </row>
     <row r="173" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C173" s="16"/>
+      <c r="C173" s="15"/>
     </row>
     <row r="174" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C174" s="16"/>
+      <c r="C174" s="15"/>
     </row>
     <row r="175" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C175" s="16"/>
+      <c r="C175" s="15"/>
     </row>
     <row r="176" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C176" s="16"/>
+      <c r="C176" s="15"/>
     </row>
     <row r="177" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C177" s="16"/>
+      <c r="C177" s="15"/>
     </row>
     <row r="178" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C178" s="16"/>
+      <c r="C178" s="15"/>
     </row>
     <row r="179" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C179" s="16"/>
+      <c r="C179" s="15"/>
     </row>
     <row r="180" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C180" s="16"/>
+      <c r="C180" s="15"/>
     </row>
     <row r="181" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C181" s="16"/>
+      <c r="C181" s="15"/>
     </row>
     <row r="182" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C182" s="16"/>
+      <c r="C182" s="15"/>
     </row>
     <row r="183" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C183" s="16"/>
+      <c r="C183" s="15"/>
     </row>
     <row r="184" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C184" s="16"/>
+      <c r="C184" s="15"/>
     </row>
     <row r="185" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C185" s="16"/>
+      <c r="C185" s="15"/>
     </row>
     <row r="186" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C186" s="16"/>
+      <c r="C186" s="15"/>
     </row>
     <row r="187" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C187" s="16"/>
+      <c r="C187" s="15"/>
     </row>
     <row r="188" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C188" s="16"/>
+      <c r="C188" s="15"/>
     </row>
     <row r="189" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C189" s="16"/>
+      <c r="C189" s="15"/>
     </row>
     <row r="190" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C190" s="16"/>
+      <c r="C190" s="15"/>
     </row>
     <row r="191" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C191" s="16"/>
+      <c r="C191" s="15"/>
     </row>
     <row r="192" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C192" s="16"/>
+      <c r="C192" s="15"/>
     </row>
     <row r="193" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C193" s="16"/>
+      <c r="C193" s="15"/>
     </row>
     <row r="194" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C194" s="16"/>
+      <c r="C194" s="15"/>
     </row>
     <row r="195" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C195" s="16"/>
+      <c r="C195" s="15"/>
     </row>
     <row r="196" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C196" s="16"/>
+      <c r="C196" s="15"/>
     </row>
     <row r="197" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C197" s="16"/>
+      <c r="C197" s="15"/>
     </row>
     <row r="198" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C198" s="16"/>
+      <c r="C198" s="15"/>
     </row>
     <row r="199" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C199" s="16"/>
+      <c r="C199" s="15"/>
     </row>
     <row r="200" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C200" s="16"/>
+      <c r="C200" s="15"/>
     </row>
     <row r="201" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C201" s="16"/>
+      <c r="C201" s="15"/>
     </row>
     <row r="202" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C202" s="16"/>
+      <c r="C202" s="15"/>
     </row>
     <row r="203" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C203" s="16"/>
+      <c r="C203" s="15"/>
     </row>
     <row r="204" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C204" s="16"/>
+      <c r="C204" s="15"/>
     </row>
     <row r="205" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C205" s="16"/>
+      <c r="C205" s="15"/>
     </row>
     <row r="206" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C206" s="16"/>
+      <c r="C206" s="15"/>
     </row>
     <row r="207" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C207" s="16"/>
+      <c r="C207" s="15"/>
     </row>
     <row r="208" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C208" s="16"/>
+      <c r="C208" s="15"/>
     </row>
     <row r="209" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C209" s="16"/>
+      <c r="C209" s="15"/>
     </row>
     <row r="210" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C210" s="16"/>
+      <c r="C210" s="15"/>
     </row>
     <row r="211" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C211" s="16"/>
+      <c r="C211" s="15"/>
     </row>
     <row r="212" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C212" s="16"/>
+      <c r="C212" s="15"/>
     </row>
     <row r="213" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C213" s="16"/>
+      <c r="C213" s="15"/>
     </row>
     <row r="214" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C214" s="16"/>
+      <c r="C214" s="15"/>
     </row>
     <row r="215" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C215" s="16"/>
+      <c r="C215" s="15"/>
     </row>
     <row r="216" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C216" s="16"/>
+      <c r="C216" s="15"/>
     </row>
     <row r="217" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C217" s="16"/>
+      <c r="C217" s="15"/>
     </row>
     <row r="218" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C218" s="16"/>
+      <c r="C218" s="15"/>
     </row>
     <row r="219" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C219" s="16"/>
+      <c r="C219" s="15"/>
     </row>
     <row r="220" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C220" s="16"/>
+      <c r="C220" s="15"/>
     </row>
     <row r="221" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C221" s="16"/>
+      <c r="C221" s="15"/>
     </row>
     <row r="222" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C222" s="16"/>
+      <c r="C222" s="15"/>
     </row>
     <row r="223" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C223" s="16"/>
+      <c r="C223" s="15"/>
     </row>
     <row r="224" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C224" s="16"/>
+      <c r="C224" s="15"/>
     </row>
     <row r="225" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C225" s="16"/>
+      <c r="C225" s="15"/>
     </row>
     <row r="226" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C226" s="16"/>
+      <c r="C226" s="15"/>
     </row>
     <row r="227" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C227" s="16"/>
+      <c r="C227" s="15"/>
     </row>
     <row r="228" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C228" s="16"/>
+      <c r="C228" s="15"/>
     </row>
     <row r="229" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C229" s="16"/>
+      <c r="C229" s="15"/>
     </row>
     <row r="230" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C230" s="16"/>
+      <c r="C230" s="15"/>
     </row>
     <row r="231" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C231" s="16"/>
+      <c r="C231" s="15"/>
     </row>
     <row r="232" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C232" s="16"/>
+      <c r="C232" s="15"/>
     </row>
     <row r="233" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C233" s="16"/>
+      <c r="C233" s="15"/>
     </row>
     <row r="234" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C234" s="16"/>
+      <c r="C234" s="15"/>
     </row>
     <row r="235" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C235" s="16"/>
+      <c r="C235" s="15"/>
     </row>
     <row r="236" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C236" s="16"/>
+      <c r="C236" s="15"/>
     </row>
     <row r="237" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C237" s="16"/>
+      <c r="C237" s="15"/>
     </row>
     <row r="238" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C238" s="16"/>
+      <c r="C238" s="15"/>
     </row>
     <row r="239" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C239" s="16"/>
+      <c r="C239" s="15"/>
     </row>
     <row r="240" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C240" s="16"/>
+      <c r="C240" s="15"/>
     </row>
     <row r="241" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C241" s="16"/>
+      <c r="C241" s="15"/>
     </row>
     <row r="242" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C242" s="16"/>
+      <c r="C242" s="15"/>
     </row>
     <row r="243" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C243" s="16"/>
+      <c r="C243" s="15"/>
     </row>
     <row r="244" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C244" s="16"/>
+      <c r="C244" s="15"/>
     </row>
     <row r="245" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C245" s="16"/>
+      <c r="C245" s="15"/>
     </row>
     <row r="246" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C246" s="16"/>
+      <c r="C246" s="15"/>
     </row>
     <row r="247" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C247" s="16"/>
+      <c r="C247" s="15"/>
     </row>
     <row r="248" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C248" s="16"/>
+      <c r="C248" s="15"/>
     </row>
     <row r="249" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C249" s="16"/>
+      <c r="C249" s="15"/>
     </row>
     <row r="250" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C250" s="16"/>
+      <c r="C250" s="15"/>
     </row>
     <row r="251" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C251" s="16"/>
+      <c r="C251" s="15"/>
     </row>
     <row r="252" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C252" s="16"/>
+      <c r="C252" s="15"/>
     </row>
     <row r="253" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C253" s="16"/>
+      <c r="C253" s="15"/>
     </row>
     <row r="254" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C254" s="16"/>
+      <c r="C254" s="15"/>
     </row>
     <row r="255" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C255" s="16"/>
+      <c r="C255" s="15"/>
     </row>
     <row r="256" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C256" s="16"/>
+      <c r="C256" s="15"/>
     </row>
     <row r="257" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C257" s="16"/>
+      <c r="C257" s="15"/>
     </row>
     <row r="258" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C258" s="16"/>
+      <c r="C258" s="15"/>
     </row>
     <row r="259" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C259" s="16"/>
+      <c r="C259" s="15"/>
     </row>
     <row r="260" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C260" s="16"/>
+      <c r="C260" s="15"/>
     </row>
     <row r="261" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C261" s="16"/>
+      <c r="C261" s="15"/>
     </row>
     <row r="262" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C262" s="16"/>
+      <c r="C262" s="15"/>
     </row>
     <row r="263" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C263" s="16"/>
+      <c r="C263" s="15"/>
     </row>
     <row r="264" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C264" s="16"/>
+      <c r="C264" s="15"/>
     </row>
     <row r="265" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C265" s="16"/>
+      <c r="C265" s="15"/>
     </row>
     <row r="266" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C266" s="16"/>
+      <c r="C266" s="15"/>
     </row>
     <row r="267" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C267" s="16"/>
+      <c r="C267" s="15"/>
     </row>
     <row r="268" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C268" s="16"/>
+      <c r="C268" s="15"/>
     </row>
     <row r="269" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C269" s="16"/>
+      <c r="C269" s="15"/>
     </row>
     <row r="270" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C270" s="16"/>
+      <c r="C270" s="15"/>
     </row>
     <row r="271" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C271" s="16"/>
+      <c r="C271" s="15"/>
     </row>
     <row r="272" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C272" s="16"/>
+      <c r="C272" s="15"/>
     </row>
     <row r="273" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C273" s="16"/>
+      <c r="C273" s="15"/>
     </row>
     <row r="274" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C274" s="16"/>
+      <c r="C274" s="15"/>
     </row>
     <row r="275" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C275" s="16"/>
+      <c r="C275" s="15"/>
     </row>
     <row r="276" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C276" s="16"/>
+      <c r="C276" s="15"/>
     </row>
     <row r="277" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C277" s="16"/>
+      <c r="C277" s="15"/>
     </row>
     <row r="278" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C278" s="16"/>
+      <c r="C278" s="15"/>
     </row>
     <row r="279" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C279" s="16"/>
+      <c r="C279" s="15"/>
     </row>
     <row r="280" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C280" s="16"/>
+      <c r="C280" s="15"/>
     </row>
     <row r="281" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C281" s="16"/>
+      <c r="C281" s="15"/>
     </row>
     <row r="282" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C282" s="16"/>
+      <c r="C282" s="15"/>
     </row>
     <row r="283" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C283" s="16"/>
+      <c r="C283" s="15"/>
     </row>
     <row r="284" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C284" s="16"/>
+      <c r="C284" s="15"/>
     </row>
     <row r="285" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C285" s="16"/>
+      <c r="C285" s="15"/>
     </row>
     <row r="286" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C286" s="16"/>
+      <c r="C286" s="15"/>
     </row>
     <row r="287" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C287" s="16"/>
+      <c r="C287" s="15"/>
     </row>
     <row r="288" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C288" s="16"/>
+      <c r="C288" s="15"/>
     </row>
     <row r="289" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C289" s="16"/>
+      <c r="C289" s="15"/>
     </row>
     <row r="290" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C290" s="16"/>
+      <c r="C290" s="15"/>
     </row>
     <row r="291" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C291" s="16"/>
+      <c r="C291" s="15"/>
     </row>
     <row r="292" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C292" s="16"/>
+      <c r="C292" s="15"/>
     </row>
     <row r="293" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C293" s="16"/>
+      <c r="C293" s="15"/>
     </row>
     <row r="294" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C294" s="16"/>
+      <c r="C294" s="15"/>
     </row>
     <row r="295" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C295" s="16"/>
+      <c r="C295" s="15"/>
     </row>
     <row r="296" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C296" s="16"/>
+      <c r="C296" s="15"/>
     </row>
     <row r="297" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C297" s="16"/>
+      <c r="C297" s="15"/>
     </row>
     <row r="298" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C298" s="16"/>
+      <c r="C298" s="15"/>
     </row>
     <row r="299" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C299" s="16"/>
+      <c r="C299" s="15"/>
     </row>
     <row r="300" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C300" s="16"/>
+      <c r="C300" s="15"/>
     </row>
     <row r="301" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C301" s="16"/>
+      <c r="C301" s="15"/>
     </row>
     <row r="302" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C302" s="16"/>
+      <c r="C302" s="15"/>
     </row>
     <row r="303" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C303" s="16"/>
+      <c r="C303" s="15"/>
     </row>
     <row r="304" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C304" s="16"/>
+      <c r="C304" s="15"/>
     </row>
     <row r="305" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C305" s="16"/>
+      <c r="C305" s="15"/>
     </row>
     <row r="306" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C306" s="16"/>
+      <c r="C306" s="15"/>
     </row>
     <row r="307" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C307" s="16"/>
+      <c r="C307" s="15"/>
     </row>
     <row r="308" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C308" s="16"/>
+      <c r="C308" s="15"/>
     </row>
     <row r="309" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C309" s="16"/>
+      <c r="C309" s="15"/>
     </row>
     <row r="310" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C310" s="16"/>
+      <c r="C310" s="15"/>
     </row>
     <row r="311" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C311" s="16"/>
+      <c r="C311" s="15"/>
     </row>
     <row r="312" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C312" s="16"/>
+      <c r="C312" s="15"/>
     </row>
     <row r="313" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C313" s="16"/>
+      <c r="C313" s="15"/>
     </row>
     <row r="314" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C314" s="16"/>
+      <c r="C314" s="15"/>
     </row>
     <row r="315" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C315" s="16"/>
+      <c r="C315" s="15"/>
     </row>
     <row r="316" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C316" s="16"/>
+      <c r="C316" s="15"/>
     </row>
     <row r="317" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C317" s="16"/>
+      <c r="C317" s="15"/>
     </row>
     <row r="318" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C318" s="16"/>
+      <c r="C318" s="15"/>
     </row>
     <row r="319" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C319" s="16"/>
+      <c r="C319" s="15"/>
     </row>
     <row r="320" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C320" s="16"/>
+      <c r="C320" s="15"/>
     </row>
     <row r="321" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C321" s="16"/>
+      <c r="C321" s="15"/>
     </row>
     <row r="322" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C322" s="16"/>
+      <c r="C322" s="15"/>
     </row>
     <row r="323" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C323" s="16"/>
+      <c r="C323" s="15"/>
     </row>
     <row r="324" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C324" s="16"/>
+      <c r="C324" s="15"/>
     </row>
     <row r="325" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C325" s="16"/>
+      <c r="C325" s="15"/>
     </row>
     <row r="326" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C326" s="16"/>
+      <c r="C326" s="15"/>
     </row>
     <row r="327" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C327" s="16"/>
+      <c r="C327" s="15"/>
     </row>
     <row r="328" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C328" s="16"/>
+      <c r="C328" s="15"/>
     </row>
     <row r="329" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C329" s="16"/>
+      <c r="C329" s="15"/>
     </row>
     <row r="330" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C330" s="16"/>
-    </row>
-    <row r="331" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C331" s="16"/>
-    </row>
-    <row r="332" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C332" s="16"/>
-    </row>
-    <row r="333" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C333" s="16"/>
-    </row>
-    <row r="334" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C334" s="16"/>
-    </row>
-    <row r="335" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C335" s="16"/>
-    </row>
+      <c r="C330" s="15"/>
+    </row>
+    <row r="1048554" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048555" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048556" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048557" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048558" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <conditionalFormatting sqref="C1:C12 C54:C58 C45 C67 C80:C798">
+  <conditionalFormatting sqref="C1:C2 C44:C48 C35 C57 C70:C793">
     <cfRule type="containsText" priority="2" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO C" dxfId="0">
       <formula>NOT(ISERROR(SEARCH("uSTO C",C1)))</formula>
     </cfRule>
@@ -6319,12 +6142,12 @@
       <formula>NOT(ISERROR(SEARCH("uSTO B",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C12 C54:C58 C45 C67 C80:C807">
+  <conditionalFormatting sqref="C1:C2 C44:C48 C35 C57 C70:C802">
     <cfRule type="containsText" priority="5" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO A" dxfId="0">
       <formula>NOT(ISERROR(SEARCH("uSTO A",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C26 C27:C335">
+  <conditionalFormatting sqref="C2:C330">
     <cfRule type="containsText" priority="6" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO C" dxfId="0">
       <formula>NOT(ISERROR(SEARCH("uSTO C",C2)))</formula>
     </cfRule>
@@ -6356,88 +6179,88 @@
   <dimension ref="A1:L1048576"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="14.65" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="28" width="36.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="28" width="12.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="28" width="16.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="28" width="10.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="29" width="10.01"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="29" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="26" width="36.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="26" width="12.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="26" width="16.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="26" width="10.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="27" width="10.01"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="27" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+    </row>
+    <row r="2" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+    </row>
+    <row r="3" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>198</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="30" t="s">
+        <v>201</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="30" t="s">
         <v>203</v>
       </c>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-    </row>
-    <row r="2" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="28" t="s">
+      <c r="C5" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-    </row>
-    <row r="3" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="28" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="30" t="s">
         <v>205</v>
       </c>
-      <c r="B3" s="28" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="26" t="s">
         <v>206</v>
       </c>
-      <c r="C3" s="28" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="26" t="s">
         <v>207</v>
       </c>
-      <c r="D3" s="28" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="26" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="32" t="s">
+    <row r="11" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="26" t="s">
         <v>209</v>
-      </c>
-      <c r="C4" s="28" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="32" t="s">
-        <v>211</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="32" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="28" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="28" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="28" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="28" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -6468,104 +6291,104 @@
   <dimension ref="A1:L1048576"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="14.65" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="28" width="36.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="28" width="12.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="28" width="19.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="28" width="10.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="29" width="10.01"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="29" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="26" width="36.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="26" width="12.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="26" width="19.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="26" width="10.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="27" width="10.01"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="27" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+    </row>
+    <row r="2" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="26" t="s">
+        <v>211</v>
+      </c>
+      <c r="C2" s="31"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+    </row>
+    <row r="3" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>198</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>199</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="26" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="26" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="26" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="26" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="26" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="32" t="s">
         <v>218</v>
       </c>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-    </row>
-    <row r="2" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="28" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="C2" s="33"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-    </row>
-    <row r="3" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="28" t="s">
-        <v>205</v>
-      </c>
-      <c r="B3" s="28" t="s">
-        <v>206</v>
-      </c>
-      <c r="C3" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="D3" s="33" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="28" t="s">
+    </row>
+    <row r="14" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="31" t="s">
         <v>220</v>
-      </c>
-      <c r="C4" s="33" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="28" t="s">
-        <v>221</v>
-      </c>
-      <c r="C5" s="33" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="28" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="28" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="28" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="28" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="28" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="34" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="33" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="33" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/engineering_basics/dsp_windows/dsp_windows.xlsx
+++ b/engineering_basics/dsp_windows/dsp_windows.xlsx
@@ -19,6 +19,28 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="D68" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Inset a e^(2*k) to calculate dft at k on the fly</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -44,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="236">
   <si>
     <t xml:space="preserve">Line Num</t>
   </si>
@@ -635,20 +657,198 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[∑w(n)e</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">jw</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> / ∑w(n)]*[∑w(n)/∑w</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(n)]</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Store WORSTCASE E[5]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 .8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL .8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 .9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL .9</t>
+  </si>
+  <si>
     <t xml:space="preserve">44 15</t>
   </si>
   <si>
     <t xml:space="preserve">STO E</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[∑w(n)e</t>
+    <t xml:space="preserve">32 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSB D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43 32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42 21 .0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LBL .0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parameter calculation program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 .1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO .1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Store N-1 in .6 for ISG instruction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 .3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO .3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 .4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO .4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 .5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO .5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 .6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO .6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 .7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO .7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 .8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO .8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 .9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO .9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">window selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Point to weighting function</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42 21 .1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LBL .1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top of calculation loop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSB I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w(n)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 40 .3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO+ .3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">w</t>
     </r>
     <r>
       <rPr>
@@ -658,16 +858,66 @@
         <family val="3"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">jw</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> / ∑w(n)]*[∑w(n)/∑w</t>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(n)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">44 40 .4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO+ .4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 .1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL .1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43 26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pi*n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pi*n/N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-pi*n/N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-j*pi*n/N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e^x</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">e</t>
     </r>
     <r>
       <rPr>
@@ -677,132 +927,24 @@
         <family val="3"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(n)]</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Store WORSTCASE E[5]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32 14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSB D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43 32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RTN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42 21 .0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LBL .0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parameter calculation program</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44 .1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STO .1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Store N-1 in .6 for ISG instruction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44 .3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STO .3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44 .4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STO .4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44 .5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STO .5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44 .6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STO .6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RCL 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">window selected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44 25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STO I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Point to weighting function</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42 21 .1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LBL .1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Top of calculation loop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32 25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSB I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w(n)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44 40 .3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STO+ .3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44 .7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STO .7</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">w</t>
+      <t xml:space="preserve">-j*pi*n/N</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">45 .7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL .7</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">w(n)e</t>
     </r>
     <r>
       <rPr>
@@ -812,56 +954,38 @@
         <family val="3"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(n)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">44 40 .4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STO+ .4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45 .1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RCL .1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43 26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pi*n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pi*n/N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-pi*n/N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-j*pi*n/N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">e^x</t>
+      <t xml:space="preserve">-j*pi*n/N</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">44 40 .5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO+ .5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42 30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re&lt;&gt;Im</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 40 .6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO+ .6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 20 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL* 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2*k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">y^x</t>
   </si>
   <si>
     <r>
@@ -881,14 +1005,8 @@
         <family val="3"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">-j*pi*n/N</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">45 .7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RCL .7</t>
+      <t xml:space="preserve">-j*2*pi*n*k/N</t>
+    </r>
   </si>
   <si>
     <r>
@@ -908,26 +1026,20 @@
         <family val="3"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">-j*pi*n/N</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">44 40 .5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STO+ .5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42 30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Re&lt;&gt;Im</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44 40 .6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STO+ .6</t>
+      <t xml:space="preserve">-j*2*pi*n*k/N</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">44 40 .8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO+ .8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 40 .9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO+ .9</t>
   </si>
   <si>
     <t xml:space="preserve">45 40 .1</t>
@@ -1034,86 +1146,17 @@
         <family val="3"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(n)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">n-N/2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)/N</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">pi*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">(n-N/2)/N</t>
-    </r>
+      <t xml:space="preserve">(n) (Hann is alpha=2)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">pi*(n-N/2)/N</t>
   </si>
   <si>
     <t xml:space="preserve">COS</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">cos(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">pi*(n-N/2)/N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">cos(pi*(n-N/2)/N)</t>
   </si>
   <si>
     <t xml:space="preserve">45 4</t>
@@ -1125,9 +1168,6 @@
     <t xml:space="preserve">alpha</t>
   </si>
   <si>
-    <t xml:space="preserve">y^x</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -1165,9 +1205,6 @@
   </si>
   <si>
     <t xml:space="preserve">Hamming</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45 30 4</t>
   </si>
   <si>
     <t xml:space="preserve">-(1-alpha)</t>
@@ -1697,7 +1734,7 @@
     <numFmt numFmtId="165" formatCode="000"/>
     <numFmt numFmtId="166" formatCode="@"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="31">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1893,8 +1930,8 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Courier New"/>
-      <family val="3"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i val="true"/>
@@ -1910,11 +1947,6 @@
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="21">
@@ -2364,7 +2396,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2447,10 +2479,6 @@
     </xf>
     <xf numFmtId="164" fontId="22" fillId="20" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -2853,7 +2881,7 @@
     </row>
     <row r="3" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>12</v>
@@ -2879,7 +2907,7 @@
     </row>
     <row r="4" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>15</v>
@@ -2905,7 +2933,7 @@
     </row>
     <row r="5" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>18</v>
@@ -2931,7 +2959,7 @@
     </row>
     <row r="6" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>21</v>
@@ -2954,7 +2982,7 @@
     </row>
     <row r="7" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B7" s="9" t="n">
         <v>1</v>
@@ -2968,7 +2996,7 @@
     </row>
     <row r="8" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B8" s="9" t="n">
         <v>36</v>
@@ -2982,16 +3010,16 @@
     </row>
     <row r="9" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B9" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
@@ -2999,7 +3027,7 @@
     </row>
     <row r="10" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>24</v>
@@ -3008,7 +3036,7 @@
         <v>25</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>1</v>
@@ -3016,7 +3044,7 @@
     </row>
     <row r="11" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>26</v>
@@ -3039,7 +3067,7 @@
     </row>
     <row r="12" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>28</v>
@@ -3062,7 +3090,7 @@
     </row>
     <row r="13" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>31</v>
@@ -3076,7 +3104,7 @@
     </row>
     <row r="14" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>34</v>
@@ -3102,7 +3130,7 @@
     </row>
     <row r="15" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>37</v>
@@ -3125,7 +3153,7 @@
     </row>
     <row r="16" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>40</v>
@@ -3148,7 +3176,7 @@
     </row>
     <row r="17" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>40</v>
@@ -3162,7 +3190,7 @@
     </row>
     <row r="18" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>44</v>
@@ -3176,7 +3204,7 @@
     </row>
     <row r="19" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>34</v>
@@ -3202,7 +3230,7 @@
     </row>
     <row r="20" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B20" s="9" t="n">
         <v>15</v>
@@ -3225,7 +3253,7 @@
     </row>
     <row r="21" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>34</v>
@@ -3251,7 +3279,7 @@
     </row>
     <row r="22" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>51</v>
@@ -3274,7 +3302,7 @@
     </row>
     <row r="23" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>54</v>
@@ -3291,7 +3319,7 @@
     </row>
     <row r="24" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>57</v>
@@ -3308,7 +3336,7 @@
     </row>
     <row r="25" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>60</v>
@@ -3325,7 +3353,7 @@
     </row>
     <row r="26" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>28</v>
@@ -3348,7 +3376,7 @@
     </row>
     <row r="27" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B27" s="9" t="n">
         <v>10</v>
@@ -3365,7 +3393,7 @@
     </row>
     <row r="28" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>34</v>
@@ -3391,7 +3419,7 @@
     </row>
     <row r="29" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>67</v>
@@ -3408,7 +3436,7 @@
     </row>
     <row r="30" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="B30" s="9" t="n">
         <v>20</v>
@@ -3431,265 +3459,199 @@
     </row>
     <row r="31" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B31" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="F31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H31" s="4" t="s">
         <v>73</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G34" s="13" t="s">
-        <v>10</v>
+        <v>57</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="D35" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="E35" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G35" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>82</v>
+        <v>60</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="n">
-        <v>45</v>
-      </c>
-      <c r="B36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>10</v>
+        <v>35</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>10</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>88</v>
+        <v>26</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G40" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G40" s="13" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="D41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>10</v>
+        <v>84</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D41" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G41" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="n">
-        <v>51</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>96</v>
+        <v>41</v>
+      </c>
+      <c r="B42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>96</v>
+        <v>88</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>10</v>
@@ -3701,47 +3663,44 @@
         <v>10</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="D44" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="E44" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G44" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>102</v>
+        <v>90</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C45" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>105</v>
+        <v>92</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>10</v>
@@ -3755,16 +3714,16 @@
     </row>
     <row r="46" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="C46" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>105</v>
+        <v>94</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>10</v>
@@ -3774,38 +3733,46 @@
       </c>
       <c r="G46" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="H46" s="16" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C47" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="H47" s="16"/>
+        <v>96</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="n">
-        <v>57</v>
-      </c>
-      <c r="B48" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="C48" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>105</v>
+        <v>47</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>105</v>
+        <v>10</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>10</v>
@@ -3816,16 +3783,16 @@
     </row>
     <row r="49" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="B49" s="9" t="n">
-        <v>20</v>
+        <v>48</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>100</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>10</v>
@@ -3839,16 +3806,16 @@
     </row>
     <row r="50" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>10</v>
@@ -3858,1128 +3825,1211 @@
       </c>
       <c r="G50" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="H50" s="16" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="B51" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E51" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C51" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H51" s="16"/>
+      <c r="F51" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E52" s="2" t="n">
-        <v>0</v>
+        <v>106</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>110</v>
+        <v>10</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="2" t="s">
         <v>110</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D53" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="E53" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F53" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G53" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="n">
-        <v>63</v>
-      </c>
-      <c r="B54" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="C54" s="11" t="s">
-        <v>70</v>
+        <v>53</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>114</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E54" s="2" t="n">
-        <v>0</v>
+        <v>115</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>110</v>
+        <v>10</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>110</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C55" s="11" t="s">
-        <v>32</v>
+        <v>116</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>117</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E55" s="2" t="n">
-        <v>0</v>
+        <v>115</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>110</v>
+        <v>10</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>110</v>
+        <v>10</v>
+      </c>
+      <c r="H55" s="16" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="n">
-        <v>65</v>
-      </c>
-      <c r="B56" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="C56" s="11" t="s">
-        <v>120</v>
+        <v>55</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C56" s="15" t="s">
+        <v>99</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E56" s="2" t="n">
-        <v>0</v>
+        <v>115</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>110</v>
+        <v>10</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>110</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="H56" s="16"/>
     </row>
     <row r="57" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="n">
-        <v>66</v>
-      </c>
-      <c r="B57" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
+      </c>
+      <c r="B57" s="9" t="n">
+        <v>36</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E57" s="2" t="n">
-        <v>0</v>
+        <v>115</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>110</v>
+        <v>10</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>110</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B58" s="9" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E58" s="2" t="n">
-        <v>0</v>
+        <v>118</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>110</v>
+        <v>10</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>110</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E59" s="2" t="n">
-        <v>0</v>
+        <v>118</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>110</v>
+        <v>10</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>110</v>
+        <v>10</v>
+      </c>
+      <c r="H59" s="16" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B60" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="C60" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>127</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C60" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H60" s="16"/>
     </row>
     <row r="61" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>110</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="n">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E62" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F62" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F62" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="G62" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="n">
-        <v>72</v>
-      </c>
-      <c r="B63" s="9" t="s">
-        <v>132</v>
+        <v>62</v>
+      </c>
+      <c r="B63" s="9" t="n">
+        <v>20</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>133</v>
+        <v>70</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E63" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="n">
-        <v>73</v>
-      </c>
-      <c r="B64" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C64" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D64" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="F64" s="2" t="n">
+      <c r="E64" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="F64" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="G64" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="8" t="n">
-        <v>74</v>
-      </c>
-      <c r="B65" s="9" t="s">
-        <v>134</v>
+        <v>64</v>
+      </c>
+      <c r="B65" s="9" t="n">
+        <v>16</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F65" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="E65" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="F65" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="G65" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="8" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="C66" s="11" t="s">
-        <v>84</v>
+        <v>57</v>
+      </c>
+      <c r="C66" s="15" t="s">
+        <v>58</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F66" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="E66" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="F66" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="G66" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="n">
-        <v>76</v>
-      </c>
-      <c r="B67" s="9" t="s">
-        <v>137</v>
+        <v>66</v>
+      </c>
+      <c r="B67" s="9" t="n">
+        <v>12</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="n">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>136</v>
+        <v>115</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="n">
-        <v>78</v>
-      </c>
-      <c r="B69" s="9" t="s">
-        <v>142</v>
+        <v>68</v>
+      </c>
+      <c r="B69" s="9" t="n">
+        <v>20</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>143</v>
+        <v>70</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C70" s="15" t="s">
-        <v>79</v>
+        <v>136</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>137</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C71" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="17" t="s">
-        <v>146</v>
+        <v>138</v>
+      </c>
+      <c r="C71" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="8" t="n">
-        <v>81</v>
-      </c>
-      <c r="B72" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C72" s="15" t="n">
-        <v>1</v>
+        <v>71</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>141</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>10</v>
+        <v>135</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>10</v>
+        <v>118</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>10</v>
+        <v>118</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="8" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C73" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="D73" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E73" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F73" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G73" s="13" t="s">
-        <v>10</v>
+        <v>138</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="C74" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="D74" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="E74" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F74" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G74" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="H74" s="17" t="s">
-        <v>149</v>
+        <v>133</v>
+      </c>
+      <c r="C74" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B75" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C75" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D75" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>10</v>
+        <v>118</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H75" s="4" t="n">
-        <v>1</v>
+        <v>118</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="8" t="n">
-        <v>85</v>
-      </c>
-      <c r="B76" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C76" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E76" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>10</v>
+        <v>75</v>
+      </c>
+      <c r="B76" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C76" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H76" s="4" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="8" t="n">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="C77" s="15" t="s">
-        <v>138</v>
+        <v>142</v>
+      </c>
+      <c r="C77" s="11" t="s">
+        <v>143</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>10</v>
+        <v>118</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="8" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B78" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C78" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D78" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>139</v>
+        <v>14</v>
+      </c>
+      <c r="C78" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="G78" s="2" t="n">
-        <v>1</v>
+        <v>118</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="8" t="n">
-        <v>88</v>
-      </c>
-      <c r="B79" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="C79" s="15" t="s">
-        <v>64</v>
+        <v>78</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>134</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>151</v>
+        <v>115</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>10</v>
+        <v>118</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="8" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="B80" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="C80" s="15" t="s">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="C80" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>10</v>
+        <v>118</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>10</v>
+        <v>118</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="8" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="15" t="s">
-        <v>32</v>
+        <v>148</v>
+      </c>
+      <c r="C81" s="11" t="s">
+        <v>149</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>10</v>
+        <v>118</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H81" s="4" t="s">
-        <v>154</v>
+        <v>118</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="8" t="n">
-        <v>91</v>
-      </c>
-      <c r="B82" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C82" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D82" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F82" s="2" t="n">
-        <v>1</v>
+        <v>81</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C82" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>10</v>
+        <v>118</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="8" t="n">
-        <v>92</v>
-      </c>
-      <c r="B83" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="C83" s="15" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="C83" s="11" t="s">
+        <v>151</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>10</v>
+        <v>118</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>10</v>
+        <v>118</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="8" t="n">
-        <v>93</v>
-      </c>
-      <c r="B84" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C84" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="E84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F84" s="2" t="s">
-        <v>10</v>
+      <c r="C84" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>10</v>
+        <v>118</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="8" t="n">
-        <v>94</v>
-      </c>
-      <c r="B85" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="C85" s="15" t="s">
-        <v>10</v>
+        <v>84</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="C85" s="11" t="s">
+        <v>153</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>10</v>
+        <v>135</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>10</v>
+        <v>118</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="8" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C86" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="D86" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="E86" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F86" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="G86" s="20" t="s">
-        <v>10</v>
+        <v>87</v>
+      </c>
+      <c r="C86" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="8" t="n">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="C87" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="D87" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="E87" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F87" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G87" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="H87" s="4" t="s">
-        <v>160</v>
+        <v>155</v>
+      </c>
+      <c r="C87" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="8" t="n">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C88" s="15" t="s">
-        <v>114</v>
+        <v>158</v>
+      </c>
+      <c r="C88" s="11" t="s">
+        <v>159</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>115</v>
+        <v>157</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>10</v>
+        <v>118</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>10</v>
+        <v>118</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="8"/>
-      <c r="B89" s="9"/>
-      <c r="C89" s="15" t="s">
-        <v>138</v>
+      <c r="A89" s="8" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="C89" s="11" t="s">
+        <v>161</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>115</v>
+        <v>154</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="8"/>
-      <c r="B90" s="9"/>
-      <c r="C90" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D90" s="2" t="n">
-        <v>2</v>
+      <c r="A90" s="8" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C90" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>157</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="8"/>
-      <c r="B91" s="9"/>
-      <c r="C91" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>115</v>
+      <c r="A91" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C91" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="D91" s="14"/>
+      <c r="E91" s="14"/>
+      <c r="F91" s="14"/>
+      <c r="G91" s="14"/>
+      <c r="H91" s="17" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="8"/>
-      <c r="B92" s="9"/>
-      <c r="C92" s="15" t="s">
-        <v>10</v>
+      <c r="A92" s="8" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" s="15" t="n">
+        <v>1</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>152</v>
+        <v>10</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="8" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="C93" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>161</v>
+        <v>82</v>
+      </c>
+      <c r="C93" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="D93" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E93" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F93" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G93" s="13" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="8" t="n">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="C94" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
+      </c>
+      <c r="C94" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="D94" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E94" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F94" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G94" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H94" s="17" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="8" t="n">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="B95" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="C95" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>162</v>
+        <v>1</v>
+      </c>
+      <c r="C95" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H95" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="8" t="n">
-        <v>106</v>
-      </c>
-      <c r="B96" s="9" t="n">
-        <v>24</v>
+        <v>95</v>
+      </c>
+      <c r="B96" s="9" t="s">
+        <v>121</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>163</v>
+        <v>122</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>10</v>
+        <v>123</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>10</v>
+      </c>
+      <c r="H96" s="4" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="8" t="n">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C97" s="15" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>164</v>
+        <v>123</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="8" t="n">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="B98" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="C98" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>169</v>
+        <v>2</v>
+      </c>
+      <c r="C98" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>10</v>
+        <v>157</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G98" s="2" t="s">
-        <v>10</v>
+        <v>123</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="8" t="n">
-        <v>109</v>
-      </c>
-      <c r="B99" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C99" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="D99" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="E99" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F99" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="G99" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="B99" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="C99" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="8" t="n">
-        <v>110</v>
-      </c>
-      <c r="B100" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B100" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C100" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D100" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C100" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="D100" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="E100" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F100" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G100" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="H100" s="17" t="s">
-        <v>172</v>
+      <c r="E100" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="8" t="n">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>165</v>
+        <v>31</v>
       </c>
       <c r="C101" s="15" t="s">
-        <v>166</v>
+        <v>32</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>10</v>
+        <v>171</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>10</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="8" t="n">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B102" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C102" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F102" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="C102" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D102" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>10</v>
@@ -4987,19 +5037,19 @@
     </row>
     <row r="103" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="8" t="n">
-        <v>113</v>
-      </c>
-      <c r="B103" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B103" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C103" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D103" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C103" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>10</v>
+      <c r="E103" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>10</v>
@@ -5010,19 +5060,19 @@
     </row>
     <row r="104" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="8" t="n">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>113</v>
+        <v>60</v>
       </c>
       <c r="C104" s="15" t="s">
-        <v>114</v>
+        <v>61</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E104" s="2" t="s">
         <v>174</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>10</v>
@@ -5033,22 +5083,22 @@
     </row>
     <row r="105" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="8" t="n">
-        <v>115</v>
-      </c>
-      <c r="B105" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="C105" s="21" t="s">
-        <v>138</v>
+        <v>104</v>
+      </c>
+      <c r="B105" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C105" s="15" t="s">
+        <v>10</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>139</v>
+        <v>175</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>115</v>
+        <v>10</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>174</v>
+        <v>10</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>10</v>
@@ -5056,65 +5106,68 @@
     </row>
     <row r="106" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="8" t="n">
-        <v>118</v>
-      </c>
-      <c r="B106" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="C106" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="D106" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B106" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C106" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="D106" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="E106" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F106" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G106" s="2" t="s">
+      <c r="E106" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F106" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G106" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="8" t="n">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="C107" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E107" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="F107" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G107" s="2" t="s">
-        <v>10</v>
+      <c r="C107" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="D107" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E107" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F107" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G107" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H107" s="4" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="8" t="n">
-        <v>120</v>
-      </c>
-      <c r="B108" s="9" t="n">
-        <v>20</v>
+        <v>107</v>
+      </c>
+      <c r="B108" s="9" t="s">
+        <v>121</v>
       </c>
       <c r="C108" s="15" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>177</v>
+        <v>123</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>174</v>
+        <v>10</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>10</v>
@@ -5122,312 +5175,420 @@
       <c r="G108" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H108" s="22"/>
     </row>
     <row r="109" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="8" t="n">
-        <v>121</v>
-      </c>
-      <c r="B109" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C109" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D109" s="2" t="n">
-        <v>2</v>
+        <v>108</v>
+      </c>
+      <c r="B109" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="C109" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>157</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="F109" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G109" s="2" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="8" t="n">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="B110" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="C110" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>178</v>
+        <v>2</v>
+      </c>
+      <c r="C110" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G110" s="2" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="8" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="C111" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E111" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="B111" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="C111" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F111" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G111" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="8" t="n">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="B112" s="9" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F112" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G112" s="2" t="s">
-        <v>10</v>
+        <v>170</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="8" t="n">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="B113" s="9" t="s">
-        <v>182</v>
+        <v>31</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>183</v>
+        <v>32</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="E113" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F113" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G113" s="2" t="s">
-        <v>10</v>
+        <v>171</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="8" t="n">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="B114" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C114" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="D114" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="E114" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F114" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="G114" s="20" t="s">
-        <v>10</v>
+        <v>124</v>
+      </c>
+      <c r="C114" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="8" t="n">
-        <v>127</v>
-      </c>
-      <c r="B115" s="9" t="s">
-        <v>185</v>
+        <v>114</v>
+      </c>
+      <c r="B115" s="9" t="n">
+        <v>20</v>
       </c>
       <c r="C115" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="H115" s="23"/>
+        <v>70</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="116" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="8" t="n">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="B116" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C116" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H116" s="23"/>
+        <v>24</v>
+      </c>
+      <c r="C116" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="117" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="8" t="n">
-        <v>129</v>
-      </c>
-      <c r="B117" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C117" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H117" s="23"/>
+        <v>116</v>
+      </c>
+      <c r="B117" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="C117" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="118" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="8" t="n">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="B118" s="9" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="H118" s="23"/>
+        <v>145</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="119" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="8" t="n">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C119" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="H119" s="23"/>
+        <v>82</v>
+      </c>
+      <c r="C119" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="D119" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="E119" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F119" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G119" s="20" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="120" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="8" t="n">
-        <v>132</v>
-      </c>
-      <c r="B120" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C120" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H120" s="23"/>
+        <v>119</v>
+      </c>
+      <c r="B120" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="C120" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="D120" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E120" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F120" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G120" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H120" s="17" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="121" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="8" t="n">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>188</v>
-      </c>
-      <c r="H121" s="23"/>
+        <v>183</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="122" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="8" t="n">
-        <v>134</v>
-      </c>
-      <c r="B122" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="C122" s="15" t="s">
-        <v>190</v>
-      </c>
-      <c r="H122" s="23"/>
+        <v>121</v>
+      </c>
+      <c r="B122" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C122" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="123" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="8" t="n">
-        <v>135</v>
-      </c>
-      <c r="B123" s="9" t="s">
-        <v>191</v>
+        <v>122</v>
+      </c>
+      <c r="B123" s="9" t="n">
+        <v>30</v>
       </c>
       <c r="C123" s="15" t="s">
-        <v>192</v>
-      </c>
-      <c r="H123" s="23"/>
+        <v>10</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="124" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="8" t="n">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="B124" s="9" t="s">
-        <v>193</v>
+        <v>121</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>194</v>
+        <v>122</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="8" t="n">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="B125" s="9" t="s">
-        <v>34</v>
+        <v>155</v>
       </c>
       <c r="C125" s="15" t="s">
-        <v>35</v>
+        <v>156</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="8" t="n">
-        <v>138</v>
-      </c>
-      <c r="B126" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B126" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="C126" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E126" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C126" s="15" t="s">
-        <v>190</v>
+      <c r="F126" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="8" t="n">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="B127" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C127" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E127" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C127" s="15" t="s">
-        <v>192</v>
+      <c r="F127" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="8" t="n">
-        <v>140</v>
-      </c>
-      <c r="B128" s="9" t="s">
-        <v>193</v>
+        <v>127</v>
+      </c>
+      <c r="B128" s="9" t="n">
+        <v>20</v>
       </c>
       <c r="C128" s="15" t="s">
-        <v>194</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H128" s="21"/>
     </row>
     <row r="129" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="8" t="n">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="B129" s="9" t="n">
         <v>2</v>
@@ -5435,10 +5596,22 @@
       <c r="C129" s="15" t="n">
         <v>2</v>
       </c>
+      <c r="D129" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="130" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="8" t="n">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="B130" s="9" t="n">
         <v>20</v>
@@ -5446,182 +5619,455 @@
       <c r="C130" s="15" t="s">
         <v>70</v>
       </c>
+      <c r="D130" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="131" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="8" t="n">
-        <v>143</v>
-      </c>
-      <c r="B131" s="9" t="s">
-        <v>34</v>
+        <v>130</v>
+      </c>
+      <c r="B131" s="9" t="n">
+        <v>24</v>
       </c>
       <c r="C131" s="15" t="s">
-        <v>35</v>
+        <v>194</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="8" t="n">
-        <v>144</v>
-      </c>
-      <c r="B132" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="B132" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C132" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E132" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C132" s="15" t="s">
-        <v>190</v>
+      <c r="F132" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="8" t="n">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="B133" s="9" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="C133" s="15" t="s">
-        <v>192</v>
+        <v>198</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="8" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="B134" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="C134" s="15" t="s">
-        <v>194</v>
+        <v>82</v>
+      </c>
+      <c r="C134" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="D134" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="E134" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F134" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G134" s="20" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="8" t="n">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="B135" s="9" t="s">
-        <v>72</v>
+        <v>200</v>
       </c>
       <c r="C135" s="15" t="s">
-        <v>73</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="H135" s="22"/>
     </row>
     <row r="136" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="8" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C136" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H136" s="22"/>
+    </row>
+    <row r="137" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="8" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C137" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" s="22"/>
+    </row>
+    <row r="138" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="8" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="C138" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="H138" s="22"/>
+    </row>
+    <row r="139" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="8" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C139" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="H139" s="22"/>
+    </row>
+    <row r="140" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="8" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C140" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H140" s="22"/>
+    </row>
+    <row r="141" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="8" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="C141" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="H141" s="22"/>
+    </row>
+    <row r="142" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="8" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="C142" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="H142" s="22"/>
+    </row>
+    <row r="143" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="8" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="C143" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="H143" s="22"/>
+    </row>
+    <row r="144" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="8" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C144" s="15" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="8" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C145" s="15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="8" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="C146" s="15" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="8" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="C147" s="15" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="8" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C148" s="15" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="8" t="n">
         <v>148</v>
       </c>
-      <c r="B136" s="9" t="s">
+      <c r="B149" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C149" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="8" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C150" s="15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C151" s="15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="8" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="C152" s="15" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="8" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="C153" s="15" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="8" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C154" s="15" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="8" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C155" s="15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="8" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="C156" s="15" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="8" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="C157" s="15" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="8" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C158" s="15" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="8" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C159" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="8" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C160" s="15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="8" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="C136" s="15" t="s">
+      <c r="C161" s="15" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="24"/>
-      <c r="C137" s="15"/>
-    </row>
-    <row r="138" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="24"/>
-      <c r="C138" s="15"/>
-    </row>
-    <row r="139" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="24"/>
-      <c r="C139" s="15"/>
-    </row>
-    <row r="140" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="24"/>
-      <c r="C140" s="15"/>
-    </row>
-    <row r="141" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="24"/>
-      <c r="C141" s="15"/>
-    </row>
-    <row r="142" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="24"/>
-      <c r="C142" s="15"/>
-    </row>
-    <row r="143" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="24"/>
-      <c r="C143" s="15"/>
-    </row>
-    <row r="144" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="24"/>
-      <c r="C144" s="15"/>
-    </row>
-    <row r="145" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="24"/>
-      <c r="C145" s="15"/>
-    </row>
-    <row r="146" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="24"/>
-      <c r="B146" s="25"/>
-      <c r="C146" s="15"/>
-    </row>
-    <row r="147" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="24"/>
-      <c r="C147" s="15"/>
-    </row>
-    <row r="148" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C148" s="15"/>
-    </row>
-    <row r="149" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C149" s="15"/>
-    </row>
-    <row r="150" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C150" s="15"/>
-    </row>
-    <row r="151" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C151" s="15"/>
-    </row>
-    <row r="152" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C152" s="15"/>
-    </row>
-    <row r="153" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C153" s="15"/>
-    </row>
-    <row r="154" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C154" s="15"/>
-    </row>
-    <row r="155" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C155" s="15"/>
-    </row>
-    <row r="156" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C156" s="15"/>
-    </row>
-    <row r="157" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C157" s="15"/>
-    </row>
-    <row r="158" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C158" s="15"/>
-    </row>
-    <row r="159" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C159" s="15"/>
-    </row>
-    <row r="160" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C160" s="15"/>
-    </row>
-    <row r="161" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C161" s="15"/>
-    </row>
-    <row r="162" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C162" s="15"/>
-    </row>
-    <row r="163" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="8" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C162" s="15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="23"/>
       <c r="C163" s="15"/>
     </row>
-    <row r="164" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="23"/>
       <c r="C164" s="15"/>
     </row>
-    <row r="165" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="23"/>
       <c r="C165" s="15"/>
     </row>
-    <row r="166" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="23"/>
       <c r="C166" s="15"/>
     </row>
-    <row r="167" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="23"/>
       <c r="C167" s="15"/>
     </row>
-    <row r="168" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="23"/>
+      <c r="B168" s="24"/>
       <c r="C168" s="15"/>
     </row>
-    <row r="169" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="23"/>
       <c r="C169" s="15"/>
     </row>
     <row r="170" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6107,31 +6553,75 @@
     <row r="330" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C330" s="15"/>
     </row>
-    <row r="1048554" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048555" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048556" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048557" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048558" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="331" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C331" s="15"/>
+    </row>
+    <row r="332" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C332" s="15"/>
+    </row>
+    <row r="333" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C333" s="15"/>
+    </row>
+    <row r="334" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C334" s="15"/>
+    </row>
+    <row r="335" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C335" s="15"/>
+    </row>
+    <row r="336" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C336" s="15"/>
+    </row>
+    <row r="337" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C337" s="15"/>
+    </row>
+    <row r="338" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C338" s="15"/>
+    </row>
+    <row r="339" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C339" s="15"/>
+    </row>
+    <row r="340" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C340" s="15"/>
+    </row>
+    <row r="341" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C341" s="15"/>
+    </row>
+    <row r="342" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C342" s="15"/>
+    </row>
+    <row r="343" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C343" s="15"/>
+    </row>
+    <row r="344" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C344" s="15"/>
+    </row>
+    <row r="345" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C345" s="15"/>
+    </row>
+    <row r="346" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C346" s="15"/>
+    </row>
+    <row r="347" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C347" s="15"/>
+    </row>
+    <row r="348" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C348" s="15"/>
+    </row>
+    <row r="349" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C349" s="15"/>
+    </row>
+    <row r="350" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C350" s="15"/>
+    </row>
+    <row r="351" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C351" s="15"/>
+    </row>
+    <row r="352" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C352" s="15"/>
+    </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <conditionalFormatting sqref="C1:C2 C44:C48 C35 C57 C70:C793">
+  <conditionalFormatting sqref="C1:C2 C53:C57 C41 C66 C165:C815 C90:C161">
     <cfRule type="containsText" priority="2" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO C" dxfId="0">
       <formula>NOT(ISERROR(SEARCH("uSTO C",C1)))</formula>
     </cfRule>
@@ -6142,12 +6632,12 @@
       <formula>NOT(ISERROR(SEARCH("uSTO B",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C2 C44:C48 C35 C57 C70:C802">
+  <conditionalFormatting sqref="C1:C2 C53:C57 C41 C66 C165:C824 C90:C161">
     <cfRule type="containsText" priority="5" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO A" dxfId="0">
       <formula>NOT(ISERROR(SEARCH("uSTO A",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C330">
+  <conditionalFormatting sqref="C165:C352 C2:C161">
     <cfRule type="containsText" priority="6" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO C" dxfId="0">
       <formula>NOT(ISERROR(SEARCH("uSTO C",C2)))</formula>
     </cfRule>
@@ -6161,6 +6651,36 @@
       <formula>NOT(ISERROR(SEARCH("uSTO A",C2)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C162:C164">
+    <cfRule type="containsText" priority="10" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO C" dxfId="0">
+      <formula>NOT(ISERROR(SEARCH("uSTO C",C162)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="11" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO B" dxfId="1">
+      <formula>NOT(ISERROR(SEARCH("uSTO B",C162)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="12" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO B" dxfId="2">
+      <formula>NOT(ISERROR(SEARCH("uSTO B",C162)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C162:C164">
+    <cfRule type="containsText" priority="13" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO A" dxfId="0">
+      <formula>NOT(ISERROR(SEARCH("uSTO A",C162)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C162:C164">
+    <cfRule type="containsText" priority="14" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO C" dxfId="0">
+      <formula>NOT(ISERROR(SEARCH("uSTO C",C162)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="15" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO B" dxfId="1">
+      <formula>NOT(ISERROR(SEARCH("uSTO B",C162)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="16" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO B" dxfId="2">
+      <formula>NOT(ISERROR(SEARCH("uSTO B",C162)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="17" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO A" dxfId="0">
+      <formula>NOT(ISERROR(SEARCH("uSTO A",C162)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -6168,6 +6688,7 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -6179,88 +6700,88 @@
   <dimension ref="A1:L1048576"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="14.65" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="26" width="36.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="26" width="12.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="26" width="16.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="26" width="10.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="27" width="10.01"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="27" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="25" width="36.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="25" width="12.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="25" width="16.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="25" width="10.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="26" width="10.01"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="26" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="28" t="s">
-        <v>195</v>
-      </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
+      <c r="A1" s="27" t="s">
+        <v>210</v>
+      </c>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
+      <c r="A2" s="25" t="s">
+        <v>211</v>
+      </c>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
     </row>
     <row r="3" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>200</v>
+      <c r="A3" s="25" t="s">
+        <v>212</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="30" t="s">
-        <v>201</v>
-      </c>
-      <c r="C4" s="26" t="s">
-        <v>202</v>
+      <c r="A4" s="29" t="s">
+        <v>216</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="30" t="s">
-        <v>203</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>204</v>
+      <c r="A5" s="29" t="s">
+        <v>218</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="30" t="s">
-        <v>205</v>
+      <c r="A6" s="29" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="26" t="s">
-        <v>206</v>
+      <c r="A8" s="25" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="26" t="s">
-        <v>207</v>
+      <c r="A9" s="25" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="26" t="s">
-        <v>208</v>
+      <c r="A10" s="25" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="26" t="s">
-        <v>209</v>
+      <c r="A11" s="25" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -6291,104 +6812,104 @@
   <dimension ref="A1:L1048576"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="14.65" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="26" width="36.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="26" width="12.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="26" width="19.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="26" width="10.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="27" width="10.01"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="27" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="25" width="36.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="25" width="12.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="25" width="19.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="25" width="10.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="26" width="10.01"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="26" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="28" t="s">
-        <v>210</v>
-      </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
+      <c r="A1" s="27" t="s">
+        <v>225</v>
+      </c>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="26" t="s">
-        <v>211</v>
-      </c>
-      <c r="C2" s="31"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
+      <c r="A2" s="25" t="s">
+        <v>226</v>
+      </c>
+      <c r="C2" s="30"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
     </row>
     <row r="3" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="C3" s="31" t="s">
-        <v>199</v>
-      </c>
-      <c r="D3" s="31" t="s">
-        <v>200</v>
+      <c r="A3" s="25" t="s">
+        <v>212</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="C3" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="C4" s="31" t="s">
-        <v>202</v>
+      <c r="A4" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="26" t="s">
-        <v>213</v>
-      </c>
-      <c r="C5" s="31" t="s">
-        <v>214</v>
+      <c r="A5" s="25" t="s">
+        <v>228</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="26" t="s">
-        <v>215</v>
+      <c r="A6" s="25" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="26" t="s">
-        <v>206</v>
+      <c r="A8" s="25" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="26" t="s">
-        <v>207</v>
+      <c r="A9" s="25" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="26" t="s">
-        <v>216</v>
+      <c r="A10" s="25" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="26" t="s">
-        <v>217</v>
+      <c r="A11" s="25" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="32" t="s">
-        <v>218</v>
+      <c r="B12" s="31" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="31" t="s">
-        <v>219</v>
+      <c r="B13" s="30" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="31" t="s">
-        <v>220</v>
+      <c r="B14" s="30" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/engineering_basics/dsp_windows/dsp_windows.xlsx
+++ b/engineering_basics/dsp_windows/dsp_windows.xlsx
@@ -8,9 +8,8 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Windows" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="DSP Windows" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Sanity" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Insanity" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -27,7 +26,7 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="D68" authorId="0">
+    <comment ref="D74" authorId="0">
       <text>
         <r>
           <rPr>
@@ -43,30 +42,8 @@
 </comments>
 </file>
 
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <authors>
-    <author>Unknown Author</author>
-  </authors>
-  <commentList>
-    <comment ref="C4" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">NOTE: THIS PROGRAM WORKS AS EXPECTED ON THE HP15C CALCULATOR.  HOWEVER, SOME OF THE SIMULATORS TEND TO FIND THE ROOTS ON THE REVERSE ORDER OR YIELD A  COMPLETELY ERRONEOUS SOLUTION. </t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="319">
   <si>
     <t xml:space="preserve">Line Num</t>
   </si>
@@ -119,22 +96,28 @@
     <t xml:space="preserve">RAD</t>
   </si>
   <si>
+    <t xml:space="preserve">Set to radians</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32 .0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSB .0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kick off calculations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42 16 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATRIX 0</t>
+  </si>
+  <si>
     <t xml:space="preserve">Clear matrices</t>
   </si>
   <si>
-    <t xml:space="preserve">32 .0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSB .0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kick off calculations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42 16 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MATRIX 0</t>
+    <t xml:space="preserve">Dimension output Matrix E</t>
   </si>
   <si>
     <t xml:space="preserve">ENTER</t>
@@ -152,6 +135,9 @@
     <t xml:space="preserve">MATRIX 1</t>
   </si>
   <si>
+    <t xml:space="preserve">Set R0/R1 to 0</t>
+  </si>
+  <si>
     <t xml:space="preserve">45 .3</t>
   </si>
   <si>
@@ -161,6 +147,9 @@
     <t xml:space="preserve">∑w(n)</t>
   </si>
   <si>
+    <t xml:space="preserve">Get sum of w(n)</t>
+  </si>
+  <si>
     <t xml:space="preserve">45 10 3</t>
   </si>
   <si>
@@ -170,6 +159,9 @@
     <t xml:space="preserve">∑w(n)/N</t>
   </si>
   <si>
+    <t xml:space="preserve">Take average</t>
+  </si>
+  <si>
     <t xml:space="preserve">44 15 u</t>
   </si>
   <si>
@@ -215,6 +207,36 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Get sum w</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(n)</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">45 10 .3</t>
   </si>
   <si>
@@ -251,6 +273,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">Divide by w(n)</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -291,6 +316,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">Divide by w(n) again</t>
+  </si>
+  <si>
     <t xml:space="preserve">45 20 3</t>
   </si>
   <si>
@@ -337,6 +365,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">Multiply by N</t>
+  </si>
+  <si>
     <t xml:space="preserve">Store EQNBW E[2]</t>
   </si>
   <si>
@@ -392,6 +423,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">Invert</t>
+  </si>
+  <si>
     <t xml:space="preserve">Store PG E[3]</t>
   </si>
   <si>
@@ -431,6 +465,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">Get real of scallop</t>
+  </si>
+  <si>
     <t xml:space="preserve">45 .6</t>
   </si>
   <si>
@@ -467,6 +504,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">Get imag of scallop</t>
+  </si>
+  <si>
     <t xml:space="preserve">42 25</t>
   </si>
   <si>
@@ -503,6 +543,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">Form complex scallop</t>
+  </si>
+  <si>
     <t xml:space="preserve">43 16</t>
   </si>
   <si>
@@ -539,6 +582,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">Take abs value</t>
+  </si>
+  <si>
     <t xml:space="preserve"> ∑w(n)</t>
   </si>
   <si>
@@ -575,23 +621,72 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">Take ratio to get loss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x^2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(|∑w(n)e</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">jw</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">| / ∑w(n))</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Get SCALLOP power</t>
+  </si>
+  <si>
     <t xml:space="preserve">Store SCALLOP E[4]</t>
   </si>
   <si>
-    <t xml:space="preserve">43 11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x^2</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(|∑w(n)e</t>
+    <t xml:space="preserve">*</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">∑w(n)e</t>
     </r>
     <r>
       <rPr>
@@ -610,7 +705,21 @@
         <family val="3"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">| / ∑w(n))</t>
+      <t xml:space="preserve"> / ∑w(n)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiply with PL</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[∑w(n)e</t>
     </r>
     <r>
       <rPr>
@@ -620,21 +729,91 @@
         <family val="3"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">jw</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> / ∑w(n)]*[∑w(n)/∑w</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">2</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">*</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">∑w(n)e</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(n)]</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Store WORSTCASE E[5]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 .8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL .8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real W(f)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Get real DFT at k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 .9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL .9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imag W(f)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Get imag DFT at k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complx W(f) rect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Make complex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work on getting power</t>
+  </si>
+  <si>
+    <t xml:space="preserve">|W(f)|</t>
+  </si>
+  <si>
+    <t xml:space="preserve">|W(f)|/N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X^2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(|W(f)|/N)</t>
     </r>
     <r>
       <rPr>
@@ -644,27 +823,18 @@
         <family val="3"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">jw</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> / ∑w(n)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[∑w(n)e</t>
+      <t xml:space="preserve">2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">STORE ABS W(f)</t>
     </r>
     <r>
       <rPr>
@@ -674,16 +844,66 @@
         <family val="3"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">jw</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> / ∑w(n)]*[∑w(n)/∑w</t>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> in E[6]</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">x&lt;&gt;y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work on getting angle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&gt;P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complx W(f) polar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set to polar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42 30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re&lt;&gt;Im</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> arg(W(f)/N)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swap R and I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO E</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> |W(f)/N| + arg</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">STORE ABS W(f)</t>
     </r>
     <r>
       <rPr>
@@ -702,29 +922,8 @@
         <family val="3"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(n)]</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Store WORSTCASE E[5]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45 .8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RCL .8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45 .9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RCL .9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44 15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STO E</t>
+      <t xml:space="preserve"> in E[7]</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">32 14</t>
@@ -733,12 +932,21 @@
     <t xml:space="preserve">GSB D</t>
   </si>
   <si>
+    <t xml:space="preserve">Put things in dB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Courtesy reset of R0/R1</t>
+  </si>
+  <si>
     <t xml:space="preserve">43 32</t>
   </si>
   <si>
     <t xml:space="preserve">RTN</t>
   </si>
   <si>
+    <t xml:space="preserve">DONE!</t>
+  </si>
+  <si>
     <t xml:space="preserve">42 21 .0</t>
   </si>
   <si>
@@ -748,13 +956,16 @@
     <t xml:space="preserve">Parameter calculation program</t>
   </si>
   <si>
+    <t xml:space="preserve">Start clearing</t>
+  </si>
+  <si>
     <t xml:space="preserve">44 .1</t>
   </si>
   <si>
     <t xml:space="preserve">STO .1</t>
   </si>
   <si>
-    <t xml:space="preserve">Store N-1 in .6 for ISG instruction</t>
+    <t xml:space="preserve">Clear registers</t>
   </si>
   <si>
     <t xml:space="preserve">44 .3</t>
@@ -808,6 +1019,9 @@
     <t xml:space="preserve">window selected</t>
   </si>
   <si>
+    <t xml:space="preserve">Get selected window</t>
+  </si>
+  <si>
     <t xml:space="preserve">44 25</t>
   </si>
   <si>
@@ -835,12 +1049,18 @@
     <t xml:space="preserve">w(n)</t>
   </si>
   <si>
+    <t xml:space="preserve">Get next w(n)</t>
+  </si>
+  <si>
     <t xml:space="preserve">44 40 .3</t>
   </si>
   <si>
     <t xml:space="preserve">STO+ .3</t>
   </si>
   <si>
+    <t xml:space="preserve">Part of coherent loss calculation</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -877,6 +1097,9 @@
     <t xml:space="preserve">STO+ .4</t>
   </si>
   <si>
+    <t xml:space="preserve">Part of eqnbw loss calculation</t>
+  </si>
+  <si>
     <t xml:space="preserve">45 .1</t>
   </si>
   <si>
@@ -958,18 +1181,15 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">Part of scalloping loss calculation</t>
+  </si>
+  <si>
     <t xml:space="preserve">44 40 .5</t>
   </si>
   <si>
     <t xml:space="preserve">STO+ .5</t>
   </si>
   <si>
-    <t xml:space="preserve">42 30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Re&lt;&gt;Im</t>
-  </si>
-  <si>
     <t xml:space="preserve">44 40 .6</t>
   </si>
   <si>
@@ -982,7 +1202,10 @@
     <t xml:space="preserve">RCL* 5</t>
   </si>
   <si>
-    <t xml:space="preserve">2*k</t>
+    <t xml:space="preserve">2*f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here f = (fo/Fs)*N – See docs</t>
   </si>
   <si>
     <t xml:space="preserve">y^x</t>
@@ -1005,8 +1228,11 @@
         <family val="3"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">-j*2*pi*n*k/N</t>
-    </r>
+      <t xml:space="preserve">-j*2*pi*n*f/N</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Sneaky single point DFT</t>
   </si>
   <si>
     <r>
@@ -1026,7 +1252,7 @@
         <family val="3"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">-j*2*pi*n*k/N</t>
+      <t xml:space="preserve">-j*2*pi*n*f/N</t>
     </r>
   </si>
   <si>
@@ -1066,12 +1292,21 @@
     <t xml:space="preserve">x!=y</t>
   </si>
   <si>
+    <t xml:space="preserve">Check if we need to get w(n+1)</t>
+  </si>
+  <si>
     <t xml:space="preserve">22 .1</t>
   </si>
   <si>
     <t xml:space="preserve">GTO .1</t>
   </si>
   <si>
+    <t xml:space="preserve">Jump to LBL .1 if we have to</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return</t>
+  </si>
+  <si>
     <t xml:space="preserve">42 21 0</t>
   </si>
   <si>
@@ -1123,6 +1358,7 @@
     <r>
       <rPr>
         <sz val="10"/>
+        <color rgb="FFC5000B"/>
         <rFont val="Courier New"/>
         <family val="3"/>
         <charset val="1"/>
@@ -1133,6 +1369,7 @@
       <rPr>
         <vertAlign val="superscript"/>
         <sz val="10"/>
+        <color rgb="FFC5000B"/>
         <rFont val="Courier New"/>
         <family val="3"/>
         <charset val="1"/>
@@ -1142,6 +1379,7 @@
     <r>
       <rPr>
         <sz val="10"/>
+        <color rgb="FFC5000B"/>
         <rFont val="Courier New"/>
         <family val="3"/>
         <charset val="1"/>
@@ -1246,483 +1484,196 @@
     <t xml:space="preserve">LBL D</t>
   </si>
   <si>
+    <t xml:space="preserve">Optional: Put things in dB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value converted are E[3-6] below</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROCESSING LOSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCALLOPING LOSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WORST-CASE LOSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DFT at ppoint f</t>
+  </si>
+  <si>
     <t xml:space="preserve">44 1</t>
   </si>
   <si>
     <t xml:space="preserve">STO 1</t>
   </si>
   <si>
+    <t xml:space="preserve">42 21 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LBL E</t>
+  </si>
+  <si>
     <t xml:space="preserve">45 15</t>
   </si>
   <si>
     <t xml:space="preserve">RCL E</t>
   </si>
   <si>
+    <t xml:space="preserve">Get value</t>
+  </si>
+  <si>
     <t xml:space="preserve">43 13</t>
   </si>
   <si>
     <t xml:space="preserve">LOG</t>
   </si>
   <si>
+    <t xml:space="preserve">take log10</t>
+  </si>
+  <si>
     <t xml:space="preserve">45 20 .7</t>
   </si>
   <si>
     <t xml:space="preserve">RCL* .7</t>
   </si>
   <si>
+    <t xml:space="preserve">mutiple by 10 to get dB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">save it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">set up check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(last E element is not dB’ed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43 30 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">check if done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GTO E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">go back if not done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User-defined windows can be placed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">here using LABELS 4-9, B-C &amp; .2-.9 </t>
+  </si>
+  <si>
     <t xml:space="preserve">PROGRAM A</t>
   </si>
   <si>
-    <t xml:space="preserve">EASY WAY – PLUG AND CHUG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equations to Solve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Example</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L = 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c = 1</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">w = –c + √(c</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> + L</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">y = 3.8385</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">y = 0.5(w + √(w</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> – 4c</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">))</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">x = 0.2652</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">x = 0.5(w – √(w</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> – 4c</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)) </t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">L is the ladder length</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c is the width of the box</t>
-  </si>
-  <si>
-    <t xml:space="preserve">y is the lengtg to top</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x is the length to bottom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROGRAM B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HARD WAY</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">y</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+2cy</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+(2c</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-L</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)+2c</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">y+c</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> = 0</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">HORNER’s METHOD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x = 1/y = 0.2652</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">{[(y+2c)y+(2c</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-L</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)]y+2c</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">}y+c</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> = 0</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">y is the length to top</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x is by defintion 1/y</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">NOTE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: THIS PROGRAM WORKS AS EXPECTED ON THE HP15C CALCULATOR.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">HOWEVER, SOME OF THE SIMULATORS TEND TO FIND THE ROOTS IN THE REVERSE ORDER,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OR YIELD A COMPLETELY ERRONEOUS SOLUTION. </t>
+    <t xml:space="preserve">Parameter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Window ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Num Points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXAMPLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Middle point between FFT bin 0 and 1 (of 32)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESULTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matrix Elements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coherent Gain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E[1]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">linear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENBW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E[2]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">power</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Processing Loss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E[3]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scalloping Loss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E[4]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worst-Case Loss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E[5]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">|H(f)|</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E[6]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">arg H(f)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E[7]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">radians</t>
   </si>
 </sst>
 </file>
@@ -1739,6 +1690,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1853,12 +1805,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FF333333"/>
@@ -1911,8 +1857,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Consolas"/>
+      <name val="Courier New"/>
       <family val="3"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1929,9 +1876,24 @@
       <charset val="1"/>
     </font>
     <font>
+      <vertAlign val="superscript"/>
+      <sz val="10"/>
+      <color rgb="FFC5000B"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
@@ -1940,16 +1902,8 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
-    <font>
-      <i val="true"/>
-      <vertAlign val="superscript"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="21">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1983,7 +1937,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC0C0C0"/>
-        <bgColor rgb="FFDDDDDD"/>
+        <bgColor rgb="FFB3B3B3"/>
       </patternFill>
     </fill>
     <fill>
@@ -2013,7 +1967,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF339966"/>
-        <bgColor rgb="FF5C8526"/>
+        <bgColor rgb="FF008080"/>
       </patternFill>
     </fill>
     <fill>
@@ -2060,14 +2014,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF7DA647"/>
-        <bgColor rgb="FF969696"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5C8526"/>
-        <bgColor rgb="FF7DA647"/>
+        <fgColor rgb="FFB3B3B3"/>
+        <bgColor rgb="FFC0C0C0"/>
       </patternFill>
     </fill>
   </fills>
@@ -2215,9 +2163,7 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FF0000FF"/>
-      </left>
+      <left style="thin"/>
       <right style="thin">
         <color rgb="FF0000FF"/>
       </right>
@@ -2373,26 +2319,26 @@
     <xf numFmtId="164" fontId="16" fillId="7" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="4" borderId="7" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="7" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="4" borderId="7" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="7" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="15" borderId="8" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="15" borderId="8" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="9" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="9" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
@@ -2401,7 +2347,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2409,120 +2359,116 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="18" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="23" fillId="18" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="2" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="18" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="18" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="25" fillId="18" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="14" xfId="61" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="19" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="19" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="18" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="18" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="18" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="18" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="18" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="14" xfId="61" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="19" borderId="14" xfId="61" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="19" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="18" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="18" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="19" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="20" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="20" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2653,7 +2599,7 @@
       <rgbColor rgb="FFC5000B"/>
       <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF5C8526"/>
+      <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFC0C0C0"/>
@@ -2680,11 +2626,11 @@
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFB3B3B3"/>
       <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF7DA647"/>
+      <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
@@ -2853,7 +2799,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="n">
         <v>1</v>
       </c>
@@ -2875,18 +2821,18 @@
       <c r="G2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -2905,14 +2851,14 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="12" t="s">
         <v>16</v>
       </c>
       <c r="D4" s="2" t="s">
@@ -2931,14 +2877,14 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="12" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="2" t="s">
@@ -2957,14 +2903,14 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>22</v>
       </c>
       <c r="D6" s="2" t="s">
@@ -2979,78 +2925,123 @@
       <c r="G6" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H6" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="9" t="n">
         <v>36</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>23</v>
+      <c r="C8" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="C9" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>7</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>29</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>10</v>
@@ -3064,19 +3055,22 @@
       <c r="G11" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H11" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>32</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>10</v>
@@ -3087,33 +3081,42 @@
       <c r="G12" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H12" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>32</v>
+        <v>35</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>36</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>37</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>35</v>
+        <v>39</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>40</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>10</v>
@@ -3125,21 +3128,21 @@
         <v>10</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>38</v>
+        <v>42</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>10</v>
@@ -3150,19 +3153,22 @@
       <c r="G15" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H15" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>41</v>
+        <v>46</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>10</v>
@@ -3173,47 +3179,74 @@
       <c r="G16" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H16" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>41</v>
+        <v>46</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>50</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>45</v>
+        <v>52</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>53</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>54</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>35</v>
+        <v>39</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>40</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>10</v>
@@ -3225,21 +3258,21 @@
         <v>10</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="C20" s="11" t="s">
-        <v>48</v>
+      <c r="C20" s="12" t="s">
+        <v>57</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>10</v>
@@ -3250,19 +3283,22 @@
       <c r="G20" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H20" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>35</v>
+        <v>39</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>40</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>10</v>
@@ -3274,24 +3310,24 @@
         <v>10</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>10</v>
@@ -3299,113 +3335,155 @@
       <c r="G22" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H22" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>55</v>
+        <v>65</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>66</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>58</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C24" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>61</v>
+        <v>73</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>58</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>32</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H26" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="C27" s="11" t="s">
-        <v>64</v>
+      <c r="C27" s="12" t="s">
+        <v>78</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>58</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>35</v>
+        <v>81</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>10</v>
@@ -3414,41 +3492,50 @@
         <v>10</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
         <v>28</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>68</v>
+        <v>39</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>40</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>58</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="C30" s="11" t="s">
-        <v>70</v>
+      <c r="C30" s="12" t="s">
+        <v>86</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>10</v>
@@ -3456,19 +3543,25 @@
       <c r="G30" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H30" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>35</v>
+        <v>39</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>40</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>72</v>
+        <v>89</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>10</v>
@@ -3477,161 +3570,278 @@
         <v>10</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>91</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
         <v>32</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>95</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="n">
         <v>33</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>69</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>73</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>35</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="n">
         <v>37</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="C38" s="11" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="39" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C38" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>39</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="9" t="s">
-        <v>82</v>
+      <c r="B40" s="9" t="n">
+        <v>34</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="D40" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E40" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G40" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>107</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="D41" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="E41" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G41" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G41" s="2" t="s">
         <v>10</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="2" t="n">
-        <v>0</v>
+      <c r="B42" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>10</v>
@@ -3639,45 +3849,48 @@
       <c r="G42" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="43" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H42" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="C43" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="D43" s="2" t="n">
-        <v>0</v>
+        <v>117</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>10</v>
+        <v>119</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>10</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="D44" s="2" t="n">
-        <v>0</v>
+        <v>121</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>10</v>
@@ -3688,19 +3901,22 @@
       <c r="G44" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="45" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H44" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="n">
         <v>44</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="C45" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="D45" s="2" t="n">
-        <v>0</v>
+        <v>28</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>10</v>
@@ -3711,62 +3927,63 @@
       <c r="G45" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H45" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C46" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>125</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="D46" s="14"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="C47" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="D47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>128</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H47" s="16" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="C48" s="11" t="s">
-        <v>99</v>
+      <c r="B48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="D48" s="2" t="n">
         <v>0</v>
@@ -3780,16 +3997,19 @@
       <c r="G48" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="49" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H48" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="C49" s="11" t="s">
-        <v>101</v>
+        <v>132</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>133</v>
       </c>
       <c r="D49" s="2" t="n">
         <v>0</v>
@@ -3803,16 +4023,19 @@
       <c r="G49" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="50" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H49" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="n">
         <v>49</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>103</v>
+        <v>135</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>136</v>
       </c>
       <c r="D50" s="2" t="n">
         <v>0</v>
@@ -3826,42 +4049,48 @@
       <c r="G50" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="51" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H50" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="n">
         <v>50</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="C51" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E51" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="D51" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="E51" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="F51" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="52" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H51" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="n">
         <v>51</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="C52" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>106</v>
+        <v>139</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>10</v>
@@ -3873,47 +4102,47 @@
         <v>10</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C53" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="D53" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="E53" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F53" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G53" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G53" s="2" t="s">
         <v>10</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="n">
         <v>53</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C54" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>115</v>
+        <v>143</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>10</v>
@@ -3924,19 +4153,22 @@
       <c r="G54" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="55" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H54" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="n">
         <v>54</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="C55" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>115</v>
+        <v>145</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>10</v>
@@ -3947,22 +4179,22 @@
       <c r="G55" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H55" s="16" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H55" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="n">
         <v>55</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="C56" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>115</v>
+        <v>147</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>10</v>
@@ -3973,23 +4205,25 @@
       <c r="G56" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H56" s="16"/>
-    </row>
-    <row r="57" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H56" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="C57" s="15" t="s">
-        <v>23</v>
+      <c r="B57" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>150</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>115</v>
+        <v>151</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>10</v>
@@ -3997,19 +4231,22 @@
       <c r="G57" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="58" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H57" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="C58" s="11" t="s">
-        <v>70</v>
+      <c r="B58" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>154</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>118</v>
+        <v>151</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>10</v>
@@ -4020,48 +4257,51 @@
       <c r="G58" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="59" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H58" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="n">
         <v>58</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="C59" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G59" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="D59" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="E59" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F59" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G59" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H59" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C60" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" s="2" t="n">
-        <v>0</v>
+      <c r="B60" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C60" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>161</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>118</v>
+        <v>10</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>10</v>
@@ -4069,1278 +4309,1350 @@
       <c r="G60" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H60" s="16"/>
-    </row>
-    <row r="61" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H60" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="n">
         <v>60</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="C61" s="11" t="s">
-        <v>122</v>
+        <v>163</v>
+      </c>
+      <c r="C61" s="17" t="s">
+        <v>164</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E61" s="2" t="n">
-        <v>0</v>
+        <v>161</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>118</v>
+        <v>10</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="62" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H61" s="18" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="n">
         <v>61</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C62" s="11" t="s">
-        <v>125</v>
+        <v>143</v>
+      </c>
+      <c r="C62" s="17" t="s">
+        <v>144</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F62" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>10</v>
+      </c>
+      <c r="H62" s="18"/>
+    </row>
+    <row r="63" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="n">
         <v>62</v>
       </c>
       <c r="B63" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>70</v>
+        <v>36</v>
+      </c>
+      <c r="C63" s="17" t="s">
+        <v>25</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E63" s="2" t="n">
-        <v>0</v>
+        <v>161</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>161</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>118</v>
+        <v>10</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="11" t="s">
-        <v>32</v>
+      <c r="B64" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>86</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E64" s="2" t="n">
-        <v>0</v>
+        <v>166</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>118</v>
+        <v>10</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="8" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>128</v>
+      <c r="B65" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>168</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E65" s="2" t="n">
-        <v>0</v>
+        <v>166</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>118</v>
+        <v>10</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>10</v>
+      </c>
+      <c r="H65" s="18" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="8" t="n">
         <v>65</v>
       </c>
-      <c r="B66" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C66" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E66" s="2" t="n">
+      <c r="B66" s="9" t="n">
         <v>0</v>
       </c>
+      <c r="C66" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>166</v>
+      </c>
       <c r="F66" s="2" t="s">
-        <v>118</v>
+        <v>10</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>10</v>
+      </c>
+      <c r="H66" s="18"/>
+    </row>
+    <row r="67" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="C67" s="11" t="s">
-        <v>131</v>
+      <c r="B67" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>171</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>132</v>
+        <v>172</v>
       </c>
       <c r="E67" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>118</v>
+        <v>166</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="n">
         <v>67</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="C68" s="11" t="s">
-        <v>134</v>
+        <v>173</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>174</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E68" s="2" t="n">
+        <v>174</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F68" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F68" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="G68" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="n">
         <v>68</v>
       </c>
       <c r="B69" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="C69" s="11" t="s">
-        <v>70</v>
+      <c r="C69" s="12" t="s">
+        <v>86</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>175</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="n">
         <v>69</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="C70" s="11" t="s">
-        <v>137</v>
+        <v>35</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>36</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="E70" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>118</v>
+        <v>166</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="C71" s="11" t="s">
-        <v>139</v>
+      <c r="B71" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>177</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>135</v>
+        <v>178</v>
       </c>
       <c r="E71" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>118</v>
+        <v>166</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="8" t="n">
         <v>71</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="C72" s="11" t="s">
-        <v>141</v>
+        <v>69</v>
+      </c>
+      <c r="C72" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>135</v>
+        <v>179</v>
       </c>
       <c r="E72" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>118</v>
+        <v>166</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="8" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="C73" s="11" t="s">
-        <v>139</v>
+      <c r="B73" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>180</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>135</v>
+        <v>181</v>
       </c>
       <c r="E73" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>118</v>
+        <v>166</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="n">
         <v>73</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="C74" s="11" t="s">
-        <v>134</v>
+        <v>182</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>183</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F74" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="E74" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="F74" s="2" t="s">
+        <v>166</v>
+      </c>
       <c r="G74" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="n">
         <v>74</v>
       </c>
       <c r="B75" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="C75" s="11" t="s">
-        <v>64</v>
+        <v>20</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>86</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>132</v>
+        <v>184</v>
       </c>
       <c r="E75" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>118</v>
+        <v>166</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>166</v>
+      </c>
+      <c r="H75" s="18" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="8" t="n">
         <v>75</v>
       </c>
-      <c r="B76" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C76" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D76" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F76" s="2" t="n">
+      <c r="B76" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E76" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="F76" s="2" t="s">
+        <v>166</v>
+      </c>
       <c r="G76" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="8" t="n">
         <v>76</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="C77" s="11" t="s">
-        <v>143</v>
+        <v>113</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>114</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F77" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="E77" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="F77" s="2" t="s">
+        <v>166</v>
+      </c>
       <c r="G77" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="8" t="n">
         <v>77</v>
       </c>
-      <c r="B78" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="C78" s="11" t="s">
-        <v>145</v>
+      <c r="B78" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>189</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>146</v>
+        <v>184</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>118</v>
+        <v>166</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="8" t="n">
         <v>78</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="C79" s="11" t="s">
-        <v>134</v>
+        <v>113</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>114</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F79" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="E79" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="F79" s="2" t="s">
+        <v>166</v>
+      </c>
       <c r="G79" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="8" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="C80" s="11" t="s">
-        <v>70</v>
+      <c r="B80" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>183</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E80" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F80" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F80" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="G80" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="8" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="C81" s="11" t="s">
-        <v>149</v>
+      <c r="B81" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>78</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>147</v>
+        <v>181</v>
       </c>
       <c r="E81" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>118</v>
+        <v>166</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="8" t="n">
         <v>81</v>
       </c>
-      <c r="B82" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="C82" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E82" s="2" t="n">
+      <c r="B82" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C82" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="F82" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F82" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="G82" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="8" t="n">
         <v>82</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="C83" s="11" t="s">
-        <v>151</v>
+        <v>190</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>191</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E83" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="F83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F83" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="G83" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>166</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="8" t="n">
         <v>83</v>
       </c>
       <c r="B84" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C84" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D84" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F84" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E84" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="F84" s="2" t="s">
+        <v>166</v>
+      </c>
       <c r="G84" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>166</v>
+      </c>
+      <c r="H84" s="18" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="8" t="n">
         <v>84</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="C85" s="11" t="s">
-        <v>153</v>
+        <v>182</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>183</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>135</v>
+        <v>195</v>
       </c>
       <c r="F85" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="8" t="n">
         <v>85</v>
       </c>
-      <c r="B86" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="C86" s="11" t="s">
-        <v>88</v>
+      <c r="B86" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C86" s="12" t="s">
+        <v>86</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F86" s="2" t="n">
+        <v>197</v>
+      </c>
+      <c r="E86" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="F86" s="2" t="s">
+        <v>166</v>
+      </c>
       <c r="G86" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="8" t="n">
         <v>86</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="C87" s="11" t="s">
-        <v>156</v>
+        <v>198</v>
+      </c>
+      <c r="C87" s="12" t="s">
+        <v>199</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>154</v>
+        <v>197</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>118</v>
+        <v>166</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="8" t="n">
         <v>87</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="C88" s="11" t="s">
-        <v>159</v>
+        <v>113</v>
+      </c>
+      <c r="C88" s="12" t="s">
+        <v>114</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>154</v>
+        <v>197</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>118</v>
+        <v>166</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="8" t="n">
         <v>88</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C89" s="11" t="s">
-        <v>161</v>
+        <v>200</v>
+      </c>
+      <c r="C89" s="12" t="s">
+        <v>201</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>154</v>
+        <v>197</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>118</v>
+        <v>166</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="8" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="C90" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>157</v>
+      <c r="B90" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>118</v>
+        <v>197</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="8" t="n">
         <v>90</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="C91" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="D91" s="14"/>
-      <c r="E91" s="14"/>
-      <c r="F91" s="14"/>
-      <c r="G91" s="14"/>
-      <c r="H91" s="17" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>202</v>
+      </c>
+      <c r="C91" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="8" t="n">
         <v>91</v>
       </c>
-      <c r="B92" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C92" s="15" t="n">
-        <v>1</v>
+      <c r="B92" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C92" s="12" t="s">
+        <v>133</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>10</v>
+        <v>204</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>10</v>
+        <v>197</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="8" t="n">
         <v>92</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="C93" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="D93" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E93" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F93" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G93" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>205</v>
+      </c>
+      <c r="C93" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="8" t="n">
         <v>93</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="C94" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="D94" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="E94" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F94" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G94" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="H94" s="17" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>208</v>
+      </c>
+      <c r="C94" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="8" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C95" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D95" s="2" t="n">
-        <v>1</v>
+      <c r="B95" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="C95" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>10</v>
+        <v>204</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H95" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>197</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="8" t="n">
         <v>95</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="C96" s="15" t="s">
-        <v>122</v>
+        <v>125</v>
+      </c>
+      <c r="C96" s="17" t="s">
+        <v>126</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E96" s="2" t="n">
-        <v>1</v>
+        <v>207</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>204</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G96" s="2" t="s">
-        <v>10</v>
+        <v>197</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="8" t="n">
         <v>96</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="C97" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F97" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G97" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>215</v>
+      </c>
+      <c r="C97" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="D97" s="15"/>
+      <c r="E97" s="15"/>
+      <c r="F97" s="15"/>
+      <c r="G97" s="15"/>
+      <c r="H97" s="19" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="8" t="n">
         <v>97</v>
       </c>
       <c r="B98" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C98" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D98" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="C98" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>157</v>
+        <v>10</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G98" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>10</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="8" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="C99" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F99" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G99" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B99" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C99" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="D99" s="14"/>
+      <c r="E99" s="14"/>
+      <c r="F99" s="14"/>
+      <c r="G99" s="14"/>
+    </row>
+    <row r="100" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="B100" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="C100" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E100" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G100" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B100" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="C100" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="D100" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E100" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F100" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G100" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H100" s="19" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="B101" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C101" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="E101" s="2" t="n">
+      <c r="B101" s="9" t="n">
         <v>1</v>
       </c>
+      <c r="C101" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="F101" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H101" s="4" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H101" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="8" t="n">
         <v>101</v>
       </c>
-      <c r="B102" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C102" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D102" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E102" s="2" t="s">
+      <c r="B102" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C102" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="F102" s="2" t="n">
+      <c r="D102" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E102" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="F102" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="G102" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="103" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H102" s="4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="8" t="n">
         <v>102</v>
       </c>
-      <c r="B103" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="C103" s="15" t="s">
-        <v>70</v>
+      <c r="B103" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="C103" s="17" t="s">
+        <v>206</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="E103" s="2" t="n">
+        <v>207</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F103" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F103" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="G103" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="8" t="n">
         <v>103</v>
       </c>
-      <c r="B104" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C104" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="E104" s="2" t="n">
+      <c r="B104" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C104" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="G104" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F104" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G104" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="105" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="8" t="n">
         <v>104</v>
       </c>
       <c r="B105" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="C105" s="15" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="C105" s="17" t="s">
+        <v>78</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>175</v>
+        <v>222</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F105" s="2" t="s">
-        <v>10</v>
+        <v>172</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="8" t="n">
         <v>105</v>
       </c>
-      <c r="B106" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="C106" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="D106" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="E106" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F106" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="G106" s="20" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B106" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C106" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="8" t="n">
         <v>106</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="C107" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="D107" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="E107" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F107" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G107" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C107" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G107" s="2" t="s">
         <v>10</v>
       </c>
       <c r="H107" s="4" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="8" t="n">
         <v>107</v>
       </c>
-      <c r="B108" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="C108" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>123</v>
+      <c r="B108" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C108" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>10</v>
+        <v>224</v>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="8" t="n">
         <v>108</v>
       </c>
-      <c r="B109" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="C109" s="15" t="s">
-        <v>156</v>
+      <c r="B109" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C109" s="17" t="s">
+        <v>86</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>226</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="8" t="n">
         <v>109</v>
       </c>
-      <c r="B110" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C110" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D110" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>157</v>
+      <c r="B110" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C110" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>10</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="8" t="n">
         <v>110</v>
       </c>
       <c r="B111" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="C111" s="15" t="s">
-        <v>64</v>
+        <v>30</v>
+      </c>
+      <c r="C111" s="17" t="s">
+        <v>10</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>169</v>
+        <v>228</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>10</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="8" t="n">
         <v>111</v>
       </c>
-      <c r="B112" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="C112" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B112" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C112" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="D112" s="14"/>
+      <c r="E112" s="14"/>
+      <c r="F112" s="14"/>
+      <c r="G112" s="14"/>
+    </row>
+    <row r="113" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="8" t="n">
         <v>112</v>
       </c>
       <c r="B113" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C113" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>229</v>
+      </c>
+      <c r="C113" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="D113" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E113" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F113" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G113" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H113" s="19" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="8" t="n">
         <v>113</v>
       </c>
       <c r="B114" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C114" s="15" t="s">
-        <v>125</v>
+        <v>170</v>
+      </c>
+      <c r="C114" s="17" t="s">
+        <v>171</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>125</v>
+        <v>172</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>10</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="8" t="n">
         <v>114</v>
       </c>
-      <c r="B115" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="C115" s="15" t="s">
-        <v>70</v>
+      <c r="B115" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="C115" s="17" t="s">
+        <v>206</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>207</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="8" t="n">
         <v>115</v>
       </c>
       <c r="B116" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="C116" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>181</v>
+        <v>2</v>
+      </c>
+      <c r="C116" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>10</v>
+        <v>207</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G116" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="8" t="n">
         <v>116</v>
       </c>
-      <c r="B117" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="C117" s="15" t="s">
-        <v>183</v>
+      <c r="B117" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="C117" s="17" t="s">
+        <v>78</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>184</v>
+        <v>222</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>172</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="8" t="n">
         <v>117</v>
       </c>
       <c r="B118" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="C118" s="15" t="s">
-        <v>145</v>
+        <v>30</v>
+      </c>
+      <c r="C118" s="17" t="s">
+        <v>10</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>185</v>
+        <v>223</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>10</v>
@@ -5352,67 +5664,64 @@
         <v>10</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="8" t="n">
         <v>118</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="C119" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="D119" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="E119" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F119" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="G119" s="20" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>35</v>
+      </c>
+      <c r="C119" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="8" t="n">
         <v>119</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="C120" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="D120" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="E120" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F120" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G120" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="H120" s="17" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>173</v>
+      </c>
+      <c r="C120" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="8" t="n">
         <v>120</v>
       </c>
-      <c r="B121" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="C121" s="15" t="s">
-        <v>183</v>
+      <c r="B121" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C121" s="17" t="s">
+        <v>86</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>184</v>
+        <v>232</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>10</v>
@@ -5424,18 +5733,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="8" t="n">
         <v>121</v>
       </c>
       <c r="B122" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C122" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D122" s="2" t="n">
-        <v>1</v>
+        <v>24</v>
+      </c>
+      <c r="C122" s="17" t="s">
+        <v>233</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>234</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>10</v>
@@ -5447,21 +5756,21 @@
         <v>10</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="8" t="n">
         <v>122</v>
       </c>
-      <c r="B123" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="C123" s="15" t="s">
-        <v>10</v>
+      <c r="B123" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="C123" s="17" t="s">
+        <v>236</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>189</v>
+        <v>237</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>10</v>
+        <v>234</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>10</v>
@@ -5470,21 +5779,21 @@
         <v>10</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="8" t="n">
         <v>123</v>
       </c>
-      <c r="B124" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="C124" s="15" t="s">
-        <v>122</v>
+      <c r="B124" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="C124" s="17" t="s">
+        <v>194</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>123</v>
+        <v>238</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>189</v>
+        <v>10</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>10</v>
@@ -5493,90 +5802,85 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="8" t="n">
         <v>124</v>
       </c>
       <c r="B125" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="C125" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F125" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="G125" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="126" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>125</v>
+      </c>
+      <c r="C125" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="D125" s="14"/>
+      <c r="E125" s="14"/>
+      <c r="F125" s="14"/>
+      <c r="G125" s="14"/>
+    </row>
+    <row r="126" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="8" t="n">
         <v>125</v>
       </c>
-      <c r="B126" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="C126" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E126" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="F126" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G126" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="127" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B126" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="C126" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="D126" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E126" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F126" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G126" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H126" s="19" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="8" t="n">
         <v>126</v>
       </c>
       <c r="B127" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C127" s="15" t="s">
-        <v>125</v>
+        <v>235</v>
+      </c>
+      <c r="C127" s="17" t="s">
+        <v>236</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>125</v>
+        <v>237</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>191</v>
+        <v>10</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>189</v>
+        <v>10</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="8" t="n">
         <v>127</v>
       </c>
       <c r="B128" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="C128" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>192</v>
+        <v>1</v>
+      </c>
+      <c r="C128" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>189</v>
+        <v>10</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>10</v>
@@ -5584,46 +5888,45 @@
       <c r="G128" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H128" s="21"/>
-    </row>
-    <row r="129" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="129" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="8" t="n">
         <v>128</v>
       </c>
       <c r="B129" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C129" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D129" s="2" t="n">
-        <v>2</v>
+        <v>30</v>
+      </c>
+      <c r="C129" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>242</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>127</v>
+        <v>10</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>189</v>
+        <v>10</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="8" t="n">
         <v>129</v>
       </c>
-      <c r="B130" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="C130" s="15" t="s">
-        <v>70</v>
+      <c r="B130" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C130" s="17" t="s">
+        <v>171</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>189</v>
+        <v>242</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>10</v>
@@ -5632,44 +5935,44 @@
         <v>10</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="8" t="n">
         <v>130</v>
       </c>
-      <c r="B131" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="C131" s="15" t="s">
-        <v>194</v>
+      <c r="B131" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="C131" s="17" t="s">
+        <v>206</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>10</v>
+        <v>242</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="8" t="n">
         <v>131</v>
       </c>
       <c r="B132" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="C132" s="15" t="s">
-        <v>70</v>
+        <v>10</v>
+      </c>
+      <c r="C132" s="17" t="s">
+        <v>78</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>196</v>
+        <v>243</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>189</v>
+        <v>242</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>10</v>
@@ -5678,950 +5981,997 @@
         <v>10</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="8" t="n">
         <v>132</v>
       </c>
       <c r="B133" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="C133" s="15" t="s">
-        <v>198</v>
+        <v>173</v>
+      </c>
+      <c r="C133" s="17" t="s">
+        <v>174</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>199</v>
+        <v>174</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>10</v>
+        <v>244</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>10</v>
+        <v>242</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="8" t="n">
         <v>133</v>
       </c>
-      <c r="B134" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="C134" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="D134" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="E134" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F134" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="G134" s="20" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="135" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B134" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C134" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H134" s="20"/>
+    </row>
+    <row r="135" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="8" t="n">
         <v>134</v>
       </c>
-      <c r="B135" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="C135" s="15" t="s">
-        <v>201</v>
-      </c>
-      <c r="H135" s="22"/>
-    </row>
-    <row r="136" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B135" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C135" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="8" t="n">
         <v>135</v>
       </c>
       <c r="B136" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C136" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H136" s="22"/>
-    </row>
-    <row r="137" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>20</v>
+      </c>
+      <c r="C136" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="8" t="n">
         <v>136</v>
       </c>
       <c r="B137" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C137" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H137" s="22"/>
-    </row>
-    <row r="138" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>24</v>
+      </c>
+      <c r="C137" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="8" t="n">
         <v>137</v>
       </c>
       <c r="B138" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="C138" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="H138" s="22"/>
-    </row>
-    <row r="139" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>20</v>
+      </c>
+      <c r="C138" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="8" t="n">
         <v>138</v>
       </c>
       <c r="B139" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="C139" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="H139" s="22"/>
-    </row>
-    <row r="140" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>250</v>
+      </c>
+      <c r="C139" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="8" t="n">
         <v>139</v>
       </c>
-      <c r="B140" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C140" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H140" s="22"/>
-    </row>
-    <row r="141" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B140" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C140" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="D140" s="14"/>
+      <c r="E140" s="14"/>
+      <c r="F140" s="14"/>
+      <c r="G140" s="14"/>
+    </row>
+    <row r="141" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="8" t="n">
         <v>140</v>
       </c>
       <c r="B141" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="C141" s="15" t="s">
-        <v>203</v>
-      </c>
-      <c r="H141" s="22"/>
-    </row>
-    <row r="142" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>253</v>
+      </c>
+      <c r="C141" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="D141" s="15"/>
+      <c r="E141" s="15"/>
+      <c r="F141" s="15"/>
+      <c r="G141" s="15"/>
+      <c r="H141" s="11" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="8" t="n">
         <v>141</v>
       </c>
-      <c r="B142" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="C142" s="15" t="s">
-        <v>205</v>
-      </c>
-      <c r="H142" s="22"/>
-    </row>
-    <row r="143" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B142" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C142" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H142" s="21" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="8" t="n">
         <v>142</v>
       </c>
-      <c r="B143" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="C143" s="15" t="s">
-        <v>207</v>
-      </c>
-      <c r="H143" s="22"/>
-    </row>
-    <row r="144" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B143" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C143" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" s="21" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="8" t="n">
         <v>143</v>
       </c>
-      <c r="B144" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="C144" s="15" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="145" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B144" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="C144" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="H144" s="21" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="8" t="n">
         <v>144</v>
       </c>
       <c r="B145" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C145" s="15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="146" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>143</v>
+      </c>
+      <c r="C145" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="H145" s="21" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="8" t="n">
         <v>145</v>
       </c>
-      <c r="B146" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="C146" s="15" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="147" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B146" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C146" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H146" s="21" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="8" t="n">
         <v>146</v>
       </c>
       <c r="B147" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="C147" s="15" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="148" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>261</v>
+      </c>
+      <c r="C147" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="H147" s="21"/>
+    </row>
+    <row r="148" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="8" t="n">
         <v>147</v>
       </c>
       <c r="B148" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="C148" s="15" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="149" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>263</v>
+      </c>
+      <c r="C148" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="H148" s="21"/>
+    </row>
+    <row r="149" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="8" t="n">
         <v>148</v>
       </c>
-      <c r="B149" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C149" s="15" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="150" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B149" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="C149" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="H149" s="21" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="8" t="n">
         <v>149</v>
       </c>
-      <c r="B150" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="C150" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="151" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B150" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="C150" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="H150" s="21" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="8" t="n">
         <v>150</v>
       </c>
       <c r="B151" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C151" s="15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="152" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>271</v>
+      </c>
+      <c r="C151" s="17" t="s">
+        <v>272</v>
+      </c>
+      <c r="H151" s="4" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="8" t="n">
         <v>151</v>
       </c>
       <c r="B152" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="C152" s="15" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="153" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>39</v>
+      </c>
+      <c r="C152" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="H152" s="4" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="8" t="n">
         <v>152</v>
       </c>
       <c r="B153" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="C153" s="15" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="154" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>275</v>
+      </c>
+      <c r="C153" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="H153" s="4" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="8" t="n">
         <v>153</v>
       </c>
-      <c r="B154" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="C154" s="15" t="s">
+      <c r="B154" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C154" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H154" s="4" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="8" t="n">
+        <v>155</v>
+      </c>
+      <c r="B155" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="C155" s="17" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="155" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="8" t="n">
-        <v>154</v>
-      </c>
-      <c r="B155" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C155" s="15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="156" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H155" s="4" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="8" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B156" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="C156" s="15" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="157" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>281</v>
+      </c>
+      <c r="C156" s="17" t="s">
+        <v>282</v>
+      </c>
+      <c r="H156" s="4" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="8" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B157" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="C157" s="15" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="158" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="8" t="n">
-        <v>157</v>
-      </c>
-      <c r="B158" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="C158" s="15" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="159" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="8" t="n">
-        <v>158</v>
-      </c>
-      <c r="B159" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C159" s="15" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="160" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="8" t="n">
-        <v>159</v>
-      </c>
-      <c r="B160" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="C160" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="161" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="8" t="n">
-        <v>160</v>
-      </c>
-      <c r="B161" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C161" s="15" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="162" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="8" t="n">
-        <v>161</v>
-      </c>
-      <c r="B162" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="C162" s="15" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="163" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="23"/>
-      <c r="C163" s="15"/>
-    </row>
-    <row r="164" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="23"/>
-      <c r="C164" s="15"/>
-    </row>
-    <row r="165" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="23"/>
-      <c r="C165" s="15"/>
-    </row>
-    <row r="166" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="23"/>
-      <c r="C166" s="15"/>
-    </row>
-    <row r="167" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="23"/>
-      <c r="C167" s="15"/>
-    </row>
-    <row r="168" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="23"/>
-      <c r="B168" s="24"/>
-      <c r="C168" s="15"/>
-    </row>
-    <row r="169" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="23"/>
-      <c r="C169" s="15"/>
+        <v>125</v>
+      </c>
+      <c r="C157" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="D157" s="14"/>
+      <c r="E157" s="14"/>
+      <c r="F157" s="14"/>
+      <c r="G157" s="14"/>
+    </row>
+    <row r="158" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="22"/>
+      <c r="C158" s="17"/>
+      <c r="H158" s="23" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C159" s="17"/>
+      <c r="H159" s="23" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C160" s="17"/>
+    </row>
+    <row r="161" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C161" s="17"/>
+    </row>
+    <row r="162" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C162" s="17"/>
+    </row>
+    <row r="163" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C163" s="17"/>
+    </row>
+    <row r="164" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C164" s="17"/>
+    </row>
+    <row r="165" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C165" s="17"/>
+    </row>
+    <row r="166" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C166" s="17"/>
+    </row>
+    <row r="167" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C167" s="17"/>
+    </row>
+    <row r="168" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C168" s="17"/>
+    </row>
+    <row r="169" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C169" s="17"/>
     </row>
     <row r="170" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C170" s="15"/>
+      <c r="C170" s="17"/>
     </row>
     <row r="171" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C171" s="15"/>
+      <c r="C171" s="17"/>
     </row>
     <row r="172" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C172" s="15"/>
+      <c r="C172" s="17"/>
     </row>
     <row r="173" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C173" s="15"/>
+      <c r="C173" s="17"/>
     </row>
     <row r="174" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C174" s="15"/>
+      <c r="C174" s="17"/>
     </row>
     <row r="175" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C175" s="15"/>
+      <c r="C175" s="17"/>
     </row>
     <row r="176" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C176" s="15"/>
+      <c r="C176" s="17"/>
     </row>
     <row r="177" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C177" s="15"/>
+      <c r="C177" s="17"/>
     </row>
     <row r="178" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C178" s="15"/>
+      <c r="C178" s="17"/>
     </row>
     <row r="179" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C179" s="15"/>
+      <c r="C179" s="17"/>
     </row>
     <row r="180" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C180" s="15"/>
+      <c r="C180" s="17"/>
     </row>
     <row r="181" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C181" s="15"/>
+      <c r="C181" s="17"/>
     </row>
     <row r="182" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C182" s="15"/>
+      <c r="C182" s="17"/>
     </row>
     <row r="183" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C183" s="15"/>
+      <c r="C183" s="17"/>
     </row>
     <row r="184" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C184" s="15"/>
+      <c r="C184" s="17"/>
     </row>
     <row r="185" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C185" s="15"/>
+      <c r="C185" s="17"/>
     </row>
     <row r="186" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C186" s="15"/>
+      <c r="C186" s="17"/>
     </row>
     <row r="187" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C187" s="15"/>
+      <c r="C187" s="17"/>
     </row>
     <row r="188" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C188" s="15"/>
+      <c r="C188" s="17"/>
     </row>
     <row r="189" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C189" s="15"/>
+      <c r="C189" s="17"/>
     </row>
     <row r="190" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C190" s="15"/>
+      <c r="C190" s="17"/>
     </row>
     <row r="191" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C191" s="15"/>
+      <c r="C191" s="17"/>
     </row>
     <row r="192" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C192" s="15"/>
+      <c r="C192" s="17"/>
     </row>
     <row r="193" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C193" s="15"/>
+      <c r="C193" s="17"/>
     </row>
     <row r="194" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C194" s="15"/>
+      <c r="C194" s="17"/>
     </row>
     <row r="195" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C195" s="15"/>
+      <c r="C195" s="17"/>
     </row>
     <row r="196" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C196" s="15"/>
+      <c r="C196" s="17"/>
     </row>
     <row r="197" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C197" s="15"/>
+      <c r="C197" s="17"/>
     </row>
     <row r="198" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C198" s="15"/>
+      <c r="C198" s="17"/>
     </row>
     <row r="199" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C199" s="15"/>
+      <c r="C199" s="17"/>
     </row>
     <row r="200" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C200" s="15"/>
+      <c r="C200" s="17"/>
     </row>
     <row r="201" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C201" s="15"/>
+      <c r="C201" s="17"/>
     </row>
     <row r="202" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C202" s="15"/>
+      <c r="C202" s="17"/>
     </row>
     <row r="203" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C203" s="15"/>
+      <c r="C203" s="17"/>
     </row>
     <row r="204" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C204" s="15"/>
+      <c r="C204" s="17"/>
     </row>
     <row r="205" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C205" s="15"/>
+      <c r="C205" s="17"/>
     </row>
     <row r="206" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C206" s="15"/>
+      <c r="C206" s="17"/>
     </row>
     <row r="207" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C207" s="15"/>
+      <c r="C207" s="17"/>
     </row>
     <row r="208" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C208" s="15"/>
+      <c r="C208" s="17"/>
     </row>
     <row r="209" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C209" s="15"/>
+      <c r="C209" s="17"/>
     </row>
     <row r="210" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C210" s="15"/>
+      <c r="C210" s="17"/>
     </row>
     <row r="211" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C211" s="15"/>
+      <c r="C211" s="17"/>
     </row>
     <row r="212" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C212" s="15"/>
+      <c r="C212" s="17"/>
     </row>
     <row r="213" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C213" s="15"/>
+      <c r="C213" s="17"/>
     </row>
     <row r="214" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C214" s="15"/>
+      <c r="C214" s="17"/>
     </row>
     <row r="215" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C215" s="15"/>
+      <c r="C215" s="17"/>
     </row>
     <row r="216" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C216" s="15"/>
+      <c r="C216" s="17"/>
     </row>
     <row r="217" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C217" s="15"/>
+      <c r="C217" s="17"/>
     </row>
     <row r="218" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C218" s="15"/>
+      <c r="C218" s="17"/>
     </row>
     <row r="219" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C219" s="15"/>
+      <c r="C219" s="17"/>
     </row>
     <row r="220" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C220" s="15"/>
+      <c r="C220" s="17"/>
     </row>
     <row r="221" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C221" s="15"/>
+      <c r="C221" s="17"/>
     </row>
     <row r="222" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C222" s="15"/>
+      <c r="C222" s="17"/>
     </row>
     <row r="223" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C223" s="15"/>
+      <c r="C223" s="17"/>
     </row>
     <row r="224" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C224" s="15"/>
+      <c r="C224" s="17"/>
     </row>
     <row r="225" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C225" s="15"/>
+      <c r="C225" s="17"/>
     </row>
     <row r="226" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C226" s="15"/>
+      <c r="C226" s="17"/>
     </row>
     <row r="227" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C227" s="15"/>
+      <c r="C227" s="17"/>
     </row>
     <row r="228" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C228" s="15"/>
+      <c r="C228" s="17"/>
     </row>
     <row r="229" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C229" s="15"/>
+      <c r="C229" s="17"/>
     </row>
     <row r="230" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C230" s="15"/>
+      <c r="C230" s="17"/>
     </row>
     <row r="231" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C231" s="15"/>
+      <c r="C231" s="17"/>
     </row>
     <row r="232" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C232" s="15"/>
+      <c r="C232" s="17"/>
     </row>
     <row r="233" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C233" s="15"/>
+      <c r="C233" s="17"/>
     </row>
     <row r="234" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C234" s="15"/>
+      <c r="C234" s="17"/>
     </row>
     <row r="235" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C235" s="15"/>
+      <c r="C235" s="17"/>
     </row>
     <row r="236" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C236" s="15"/>
+      <c r="C236" s="17"/>
     </row>
     <row r="237" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C237" s="15"/>
+      <c r="C237" s="17"/>
     </row>
     <row r="238" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C238" s="15"/>
+      <c r="C238" s="17"/>
     </row>
     <row r="239" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C239" s="15"/>
+      <c r="C239" s="17"/>
     </row>
     <row r="240" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C240" s="15"/>
+      <c r="C240" s="17"/>
     </row>
     <row r="241" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C241" s="15"/>
+      <c r="C241" s="17"/>
     </row>
     <row r="242" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C242" s="15"/>
+      <c r="C242" s="17"/>
     </row>
     <row r="243" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C243" s="15"/>
+      <c r="C243" s="17"/>
     </row>
     <row r="244" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C244" s="15"/>
+      <c r="C244" s="17"/>
     </row>
     <row r="245" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C245" s="15"/>
+      <c r="C245" s="17"/>
     </row>
     <row r="246" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C246" s="15"/>
+      <c r="C246" s="17"/>
     </row>
     <row r="247" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C247" s="15"/>
+      <c r="C247" s="17"/>
     </row>
     <row r="248" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C248" s="15"/>
+      <c r="C248" s="17"/>
     </row>
     <row r="249" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C249" s="15"/>
+      <c r="C249" s="17"/>
     </row>
     <row r="250" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C250" s="15"/>
+      <c r="C250" s="17"/>
     </row>
     <row r="251" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C251" s="15"/>
+      <c r="C251" s="17"/>
     </row>
     <row r="252" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C252" s="15"/>
+      <c r="C252" s="17"/>
     </row>
     <row r="253" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C253" s="15"/>
+      <c r="C253" s="17"/>
     </row>
     <row r="254" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C254" s="15"/>
+      <c r="C254" s="17"/>
     </row>
     <row r="255" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C255" s="15"/>
+      <c r="C255" s="17"/>
     </row>
     <row r="256" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C256" s="15"/>
+      <c r="C256" s="17"/>
     </row>
     <row r="257" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C257" s="15"/>
+      <c r="C257" s="17"/>
     </row>
     <row r="258" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C258" s="15"/>
+      <c r="C258" s="17"/>
     </row>
     <row r="259" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C259" s="15"/>
+      <c r="C259" s="17"/>
     </row>
     <row r="260" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C260" s="15"/>
+      <c r="C260" s="17"/>
     </row>
     <row r="261" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C261" s="15"/>
+      <c r="C261" s="17"/>
     </row>
     <row r="262" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C262" s="15"/>
+      <c r="C262" s="17"/>
     </row>
     <row r="263" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C263" s="15"/>
+      <c r="C263" s="17"/>
     </row>
     <row r="264" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C264" s="15"/>
+      <c r="C264" s="17"/>
     </row>
     <row r="265" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C265" s="15"/>
+      <c r="C265" s="17"/>
     </row>
     <row r="266" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C266" s="15"/>
+      <c r="C266" s="17"/>
     </row>
     <row r="267" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C267" s="15"/>
+      <c r="C267" s="17"/>
     </row>
     <row r="268" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C268" s="15"/>
+      <c r="C268" s="17"/>
     </row>
     <row r="269" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C269" s="15"/>
+      <c r="C269" s="17"/>
     </row>
     <row r="270" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C270" s="15"/>
+      <c r="C270" s="17"/>
     </row>
     <row r="271" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C271" s="15"/>
+      <c r="C271" s="17"/>
     </row>
     <row r="272" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C272" s="15"/>
+      <c r="C272" s="17"/>
     </row>
     <row r="273" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C273" s="15"/>
+      <c r="C273" s="17"/>
     </row>
     <row r="274" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C274" s="15"/>
+      <c r="C274" s="17"/>
     </row>
     <row r="275" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C275" s="15"/>
+      <c r="C275" s="17"/>
     </row>
     <row r="276" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C276" s="15"/>
+      <c r="C276" s="17"/>
     </row>
     <row r="277" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C277" s="15"/>
+      <c r="C277" s="17"/>
     </row>
     <row r="278" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C278" s="15"/>
+      <c r="C278" s="17"/>
     </row>
     <row r="279" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C279" s="15"/>
+      <c r="C279" s="17"/>
     </row>
     <row r="280" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C280" s="15"/>
+      <c r="C280" s="17"/>
     </row>
     <row r="281" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C281" s="15"/>
+      <c r="C281" s="17"/>
     </row>
     <row r="282" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C282" s="15"/>
+      <c r="C282" s="17"/>
     </row>
     <row r="283" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C283" s="15"/>
+      <c r="C283" s="17"/>
     </row>
     <row r="284" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C284" s="15"/>
+      <c r="C284" s="17"/>
     </row>
     <row r="285" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C285" s="15"/>
+      <c r="C285" s="17"/>
     </row>
     <row r="286" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C286" s="15"/>
+      <c r="C286" s="17"/>
     </row>
     <row r="287" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C287" s="15"/>
+      <c r="C287" s="17"/>
     </row>
     <row r="288" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C288" s="15"/>
+      <c r="C288" s="17"/>
     </row>
     <row r="289" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C289" s="15"/>
+      <c r="C289" s="17"/>
     </row>
     <row r="290" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C290" s="15"/>
+      <c r="C290" s="17"/>
     </row>
     <row r="291" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C291" s="15"/>
+      <c r="C291" s="17"/>
     </row>
     <row r="292" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C292" s="15"/>
+      <c r="C292" s="17"/>
     </row>
     <row r="293" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C293" s="15"/>
+      <c r="C293" s="17"/>
     </row>
     <row r="294" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C294" s="15"/>
+      <c r="C294" s="17"/>
     </row>
     <row r="295" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C295" s="15"/>
+      <c r="C295" s="17"/>
     </row>
     <row r="296" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C296" s="15"/>
+      <c r="C296" s="17"/>
     </row>
     <row r="297" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C297" s="15"/>
+      <c r="C297" s="17"/>
     </row>
     <row r="298" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C298" s="15"/>
+      <c r="C298" s="17"/>
     </row>
     <row r="299" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C299" s="15"/>
+      <c r="C299" s="17"/>
     </row>
     <row r="300" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C300" s="15"/>
+      <c r="C300" s="17"/>
     </row>
     <row r="301" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C301" s="15"/>
+      <c r="C301" s="17"/>
     </row>
     <row r="302" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C302" s="15"/>
+      <c r="C302" s="17"/>
     </row>
     <row r="303" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C303" s="15"/>
+      <c r="C303" s="17"/>
     </row>
     <row r="304" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C304" s="15"/>
+      <c r="C304" s="17"/>
     </row>
     <row r="305" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C305" s="15"/>
+      <c r="C305" s="17"/>
     </row>
     <row r="306" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C306" s="15"/>
+      <c r="C306" s="17"/>
     </row>
     <row r="307" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C307" s="15"/>
+      <c r="C307" s="17"/>
     </row>
     <row r="308" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C308" s="15"/>
+      <c r="C308" s="17"/>
     </row>
     <row r="309" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C309" s="15"/>
+      <c r="C309" s="17"/>
     </row>
     <row r="310" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C310" s="15"/>
+      <c r="C310" s="17"/>
     </row>
     <row r="311" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C311" s="15"/>
+      <c r="C311" s="17"/>
     </row>
     <row r="312" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C312" s="15"/>
+      <c r="C312" s="17"/>
     </row>
     <row r="313" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C313" s="15"/>
+      <c r="C313" s="17"/>
     </row>
     <row r="314" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C314" s="15"/>
+      <c r="C314" s="17"/>
     </row>
     <row r="315" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C315" s="15"/>
+      <c r="C315" s="17"/>
     </row>
     <row r="316" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C316" s="15"/>
+      <c r="C316" s="17"/>
     </row>
     <row r="317" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C317" s="15"/>
+      <c r="C317" s="17"/>
     </row>
     <row r="318" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C318" s="15"/>
+      <c r="C318" s="17"/>
     </row>
     <row r="319" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C319" s="15"/>
+      <c r="C319" s="17"/>
     </row>
     <row r="320" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C320" s="15"/>
+      <c r="C320" s="17"/>
     </row>
     <row r="321" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C321" s="15"/>
+      <c r="C321" s="17"/>
     </row>
     <row r="322" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C322" s="15"/>
+      <c r="C322" s="17"/>
     </row>
     <row r="323" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C323" s="15"/>
+      <c r="C323" s="17"/>
     </row>
     <row r="324" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C324" s="15"/>
+      <c r="C324" s="17"/>
     </row>
     <row r="325" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C325" s="15"/>
+      <c r="C325" s="17"/>
     </row>
     <row r="326" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C326" s="15"/>
+      <c r="C326" s="17"/>
     </row>
     <row r="327" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C327" s="15"/>
+      <c r="C327" s="17"/>
     </row>
     <row r="328" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C328" s="15"/>
+      <c r="C328" s="17"/>
     </row>
     <row r="329" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C329" s="15"/>
+      <c r="C329" s="17"/>
     </row>
     <row r="330" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C330" s="15"/>
+      <c r="C330" s="17"/>
     </row>
     <row r="331" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C331" s="15"/>
+      <c r="C331" s="17"/>
     </row>
     <row r="332" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C332" s="15"/>
+      <c r="C332" s="17"/>
     </row>
     <row r="333" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C333" s="15"/>
+      <c r="C333" s="17"/>
     </row>
     <row r="334" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C334" s="15"/>
+      <c r="C334" s="17"/>
     </row>
     <row r="335" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C335" s="15"/>
+      <c r="C335" s="17"/>
     </row>
     <row r="336" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C336" s="15"/>
+      <c r="C336" s="17"/>
     </row>
     <row r="337" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C337" s="15"/>
+      <c r="C337" s="17"/>
     </row>
     <row r="338" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C338" s="15"/>
+      <c r="C338" s="17"/>
     </row>
     <row r="339" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C339" s="15"/>
+      <c r="C339" s="17"/>
     </row>
     <row r="340" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C340" s="15"/>
+      <c r="C340" s="17"/>
     </row>
     <row r="341" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C341" s="15"/>
-    </row>
-    <row r="342" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C342" s="15"/>
-    </row>
-    <row r="343" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C343" s="15"/>
-    </row>
-    <row r="344" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C344" s="15"/>
-    </row>
-    <row r="345" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C345" s="15"/>
-    </row>
-    <row r="346" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C346" s="15"/>
-    </row>
-    <row r="347" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C347" s="15"/>
-    </row>
-    <row r="348" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C348" s="15"/>
-    </row>
-    <row r="349" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C349" s="15"/>
-    </row>
-    <row r="350" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C350" s="15"/>
-    </row>
-    <row r="351" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C351" s="15"/>
-    </row>
-    <row r="352" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C352" s="15"/>
-    </row>
+      <c r="C341" s="17"/>
+    </row>
+    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <conditionalFormatting sqref="C1:C2 C53:C57 C41 C66 C165:C815 C90:C161">
+  <conditionalFormatting sqref="C1:C2 C59:C63 C46:C47 C72 H141 H2 C96:C804">
     <cfRule type="containsText" priority="2" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO C" dxfId="0">
       <formula>NOT(ISERROR(SEARCH("uSTO C",C1)))</formula>
     </cfRule>
@@ -6632,12 +6982,12 @@
       <formula>NOT(ISERROR(SEARCH("uSTO B",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C2 C53:C57 C41 C66 C165:C824 C90:C161">
+  <conditionalFormatting sqref="C1:C2 C59:C63 C46:C47 C72 H141 H2 C96:C813">
     <cfRule type="containsText" priority="5" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO A" dxfId="0">
       <formula>NOT(ISERROR(SEARCH("uSTO A",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C165:C352 C2:C161">
+  <conditionalFormatting sqref="H141 H2 C2:C341">
     <cfRule type="containsText" priority="6" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO C" dxfId="0">
       <formula>NOT(ISERROR(SEARCH("uSTO C",C2)))</formula>
     </cfRule>
@@ -6649,36 +6999,6 @@
     </cfRule>
     <cfRule type="containsText" priority="9" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO A" dxfId="0">
       <formula>NOT(ISERROR(SEARCH("uSTO A",C2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C162:C164">
-    <cfRule type="containsText" priority="10" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO C" dxfId="0">
-      <formula>NOT(ISERROR(SEARCH("uSTO C",C162)))</formula>
-    </cfRule>
-    <cfRule type="containsText" priority="11" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO B" dxfId="1">
-      <formula>NOT(ISERROR(SEARCH("uSTO B",C162)))</formula>
-    </cfRule>
-    <cfRule type="containsText" priority="12" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO B" dxfId="2">
-      <formula>NOT(ISERROR(SEARCH("uSTO B",C162)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C162:C164">
-    <cfRule type="containsText" priority="13" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO A" dxfId="0">
-      <formula>NOT(ISERROR(SEARCH("uSTO A",C162)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C162:C164">
-    <cfRule type="containsText" priority="14" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO C" dxfId="0">
-      <formula>NOT(ISERROR(SEARCH("uSTO C",C162)))</formula>
-    </cfRule>
-    <cfRule type="containsText" priority="15" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO B" dxfId="1">
-      <formula>NOT(ISERROR(SEARCH("uSTO B",C162)))</formula>
-    </cfRule>
-    <cfRule type="containsText" priority="16" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO B" dxfId="2">
-      <formula>NOT(ISERROR(SEARCH("uSTO B",C162)))</formula>
-    </cfRule>
-    <cfRule type="containsText" priority="17" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO A" dxfId="0">
-      <formula>NOT(ISERROR(SEARCH("uSTO A",C162)))</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -6697,102 +7017,257 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L1048576"/>
+  <dimension ref="A1:M1048576"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="14.65" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="25" width="36.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="25" width="12.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="25" width="16.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="25" width="10.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="26" width="10.01"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="26" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="24" width="18.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="25" width="18.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="25" width="12.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="25" width="50.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="25" width="10.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="24" width="10.01"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="24" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="27" t="s">
-        <v>210</v>
-      </c>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
+      <c r="A1" s="26" t="s">
+        <v>286</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
     </row>
     <row r="2" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="25" t="s">
-        <v>211</v>
-      </c>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-    </row>
-    <row r="3" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="28" t="s">
+        <v>287</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>288</v>
+      </c>
+      <c r="C2" s="29"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+    </row>
+    <row r="3" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
-        <v>212</v>
+        <v>289</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>213</v>
-      </c>
-      <c r="C3" s="25" t="s">
-        <v>214</v>
-      </c>
-      <c r="D3" s="25" t="s">
-        <v>215</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="C3" s="29"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="25"/>
     </row>
     <row r="4" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="29" t="s">
-        <v>216</v>
-      </c>
-      <c r="C4" s="25" t="s">
-        <v>217</v>
+      <c r="A4" s="25" t="s">
+        <v>291</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="29" t="s">
-        <v>218</v>
-      </c>
-      <c r="C5" s="25" t="s">
-        <v>219</v>
+      <c r="A5" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="29" t="s">
-        <v>220</v>
-      </c>
+      <c r="A6" s="25" t="s">
+        <v>294</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="25"/>
+      <c r="B7" s="30"/>
     </row>
     <row r="8" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="25" t="s">
-        <v>221</v>
+      <c r="A8" s="31" t="s">
+        <v>296</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>222</v>
+        <v>289</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>290</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>223</v>
+        <v>291</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>292</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+        <v>237</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>293</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="25" t="s">
+        <v>294</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>295</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="31" t="s">
+        <v>299</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>300</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="D14" s="31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="25" t="s">
+        <v>301</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>302</v>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>305</v>
+      </c>
+      <c r="C16" s="25" t="n">
+        <v>1.3628</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="25" t="s">
+        <v>307</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>308</v>
+      </c>
+      <c r="C17" s="25" t="n">
+        <v>-1.344</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="25" t="s">
+        <v>310</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>311</v>
+      </c>
+      <c r="C18" s="25" t="n">
+        <v>-1.7521</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="25" t="s">
+        <v>312</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>313</v>
+      </c>
+      <c r="C19" s="25" t="n">
+        <v>-3.0965</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="25" t="s">
+        <v>314</v>
+      </c>
+      <c r="B20" s="25" t="s">
+        <v>315</v>
+      </c>
+      <c r="C20" s="25" t="n">
+        <v>-7.1042</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="25" t="s">
+        <v>316</v>
+      </c>
+      <c r="B21" s="25" t="s">
+        <v>317</v>
+      </c>
+      <c r="C21" s="25" t="n">
+        <v>-1.5651</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="1048576" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -6802,133 +7277,4 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:L1048576"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="14.65" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="25" width="36.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="25" width="12.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="25" width="19.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="25" width="10.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="26" width="10.01"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="26" width="11.53"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="27" t="s">
-        <v>225</v>
-      </c>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-    </row>
-    <row r="2" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="C2" s="30"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-    </row>
-    <row r="3" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>213</v>
-      </c>
-      <c r="C3" s="30" t="s">
-        <v>214</v>
-      </c>
-      <c r="D3" s="30" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="25" t="s">
-        <v>227</v>
-      </c>
-      <c r="C4" s="30" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="25" t="s">
-        <v>228</v>
-      </c>
-      <c r="C5" s="30" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="25" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="25" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="25" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="25" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="25" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="31" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="30" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="30" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
-  </headerFooter>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
 </file>